--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="246">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -517,6 +517,12 @@
     <t>['6', '13', '17', '21', '76']</t>
   </si>
   <si>
+    <t>['49', '81']</t>
+  </si>
+  <si>
+    <t>['36', '61', '74']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -737,6 +743,15 @@
   </si>
   <si>
     <t>['88']</t>
+  </si>
+  <si>
+    <t>['51']</t>
+  </si>
+  <si>
+    <t>['46']</t>
+  </si>
+  <si>
+    <t>['42']</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP129"/>
+  <dimension ref="A1:BP133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1354,7 +1369,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1435,7 +1450,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ2">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1560,7 +1575,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1641,7 +1656,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ3">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1766,7 +1781,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1844,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ4">
         <v>2.38</v>
@@ -1972,7 +1987,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2178,7 +2193,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2256,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ6">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2462,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ7">
         <v>0.5</v>
@@ -2874,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3208,7 +3223,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3414,7 +3429,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4032,7 +4047,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4238,7 +4253,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4444,7 +4459,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4650,7 +4665,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4856,7 +4871,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5062,7 +5077,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5140,10 +5155,10 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ20">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR20">
         <v>0.71</v>
@@ -5268,7 +5283,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5346,7 +5361,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ21">
         <v>2.38</v>
@@ -5474,7 +5489,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5552,7 +5567,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ22">
         <v>1.38</v>
@@ -5758,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -5886,7 +5901,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5967,7 +5982,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ24">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR24">
         <v>1.2</v>
@@ -6092,7 +6107,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6173,7 +6188,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ25">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR25">
         <v>0.84</v>
@@ -6298,7 +6313,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6504,7 +6519,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6791,7 +6806,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR28">
         <v>1.55</v>
@@ -6916,7 +6931,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7122,7 +7137,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7328,7 +7343,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7946,7 +7961,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8152,7 +8167,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8230,7 +8245,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ35">
         <v>1.38</v>
@@ -8358,7 +8373,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8564,7 +8579,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8642,7 +8657,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ37">
         <v>0.89</v>
@@ -8770,7 +8785,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -8851,7 +8866,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR38">
         <v>0.95</v>
@@ -9054,7 +9069,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -9182,7 +9197,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9388,7 +9403,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9469,7 +9484,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ41">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR41">
         <v>0.9</v>
@@ -9594,7 +9609,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10006,7 +10021,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10212,7 +10227,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10290,7 +10305,7 @@
         <v>1.67</v>
       </c>
       <c r="AP45">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ45">
         <v>1.43</v>
@@ -10418,7 +10433,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10624,7 +10639,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10705,7 +10720,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ47">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR47">
         <v>1.13</v>
@@ -10830,7 +10845,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -10911,7 +10926,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ48">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR48">
         <v>1.3</v>
@@ -11114,7 +11129,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ49">
         <v>0.89</v>
@@ -11320,7 +11335,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ50">
         <v>1.33</v>
@@ -11448,7 +11463,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11654,7 +11669,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12066,7 +12081,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12147,7 +12162,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ54">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12350,7 +12365,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ55">
         <v>1.44</v>
@@ -12478,7 +12493,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12559,7 +12574,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ56">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR56">
         <v>1.26</v>
@@ -12684,7 +12699,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12890,7 +12905,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13508,7 +13523,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13586,7 +13601,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ61">
         <v>0.5</v>
@@ -13920,7 +13935,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14001,7 +14016,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ63">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14207,7 +14222,7 @@
         <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR64">
         <v>1.93</v>
@@ -14332,7 +14347,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14538,7 +14553,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14616,7 +14631,7 @@
         <v>3</v>
       </c>
       <c r="AP66">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ66">
         <v>2.38</v>
@@ -14744,7 +14759,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14950,7 +14965,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15237,7 +15252,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ69">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR69">
         <v>1.58</v>
@@ -15568,7 +15583,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15649,7 +15664,7 @@
         <v>2</v>
       </c>
       <c r="AQ71">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -16264,7 +16279,7 @@
         <v>3</v>
       </c>
       <c r="AP74">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ74">
         <v>2.38</v>
@@ -16392,7 +16407,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16598,7 +16613,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16676,7 +16691,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ76">
         <v>1.43</v>
@@ -16804,7 +16819,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16882,7 +16897,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ77">
         <v>1.38</v>
@@ -17010,7 +17025,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17091,7 +17106,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ78">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR78">
         <v>1.34</v>
@@ -17216,7 +17231,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17500,10 +17515,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ80">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR80">
         <v>1.44</v>
@@ -17628,7 +17643,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17915,7 +17930,7 @@
         <v>2</v>
       </c>
       <c r="AQ82">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18452,7 +18467,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18658,7 +18673,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19070,7 +19085,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19151,7 +19166,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ88">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR88">
         <v>1.25</v>
@@ -19276,7 +19291,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19354,7 +19369,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ89">
         <v>1.63</v>
@@ -19482,7 +19497,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19766,7 +19781,7 @@
         <v>2.6</v>
       </c>
       <c r="AP91">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ91">
         <v>2.38</v>
@@ -19894,7 +19909,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -19972,10 +19987,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ92">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR92">
         <v>1.32</v>
@@ -20100,7 +20115,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20306,7 +20321,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20512,7 +20527,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20796,7 +20811,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ96">
         <v>0.5</v>
@@ -20924,7 +20939,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21005,7 +21020,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ97">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR97">
         <v>1.11</v>
@@ -21336,7 +21351,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21414,10 +21429,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ99">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR99">
         <v>1.1</v>
@@ -21542,7 +21557,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21623,7 +21638,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ100">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR100">
         <v>1.75</v>
@@ -21748,7 +21763,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22160,7 +22175,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22366,7 +22381,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22778,7 +22793,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22856,7 +22871,7 @@
         <v>0.83</v>
       </c>
       <c r="AP106">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ106">
         <v>1.38</v>
@@ -22984,7 +22999,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23065,7 +23080,7 @@
         <v>2</v>
       </c>
       <c r="AQ107">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -23190,7 +23205,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23271,7 +23286,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR108">
         <v>1.76</v>
@@ -23396,7 +23411,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24092,7 +24107,7 @@
         <v>2.17</v>
       </c>
       <c r="AP112">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AQ112">
         <v>1.63</v>
@@ -24220,7 +24235,7 @@
         <v>137</v>
       </c>
       <c r="P113" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24298,7 +24313,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AQ113">
         <v>0.5</v>
@@ -24838,7 +24853,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -24916,7 +24931,7 @@
         <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="AQ116">
         <v>1.38</v>
@@ -25456,7 +25471,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25537,7 +25552,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ119">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR119">
         <v>1.62</v>
@@ -25949,7 +25964,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ121">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AR121">
         <v>1.76</v>
@@ -26074,7 +26089,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26486,7 +26501,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26692,7 +26707,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26898,7 +26913,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27104,7 +27119,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27310,7 +27325,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27516,7 +27531,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27673,6 +27688,830 @@
       </c>
       <c r="BP129">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="130" spans="1:68">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>7484669</v>
+      </c>
+      <c r="C130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D130" t="s">
+        <v>69</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F130">
+        <v>17</v>
+      </c>
+      <c r="G130" t="s">
+        <v>75</v>
+      </c>
+      <c r="H130" t="s">
+        <v>82</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>1</v>
+      </c>
+      <c r="O130" t="s">
+        <v>86</v>
+      </c>
+      <c r="P130" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q130">
+        <v>3.4</v>
+      </c>
+      <c r="R130">
+        <v>2.1</v>
+      </c>
+      <c r="S130">
+        <v>2.88</v>
+      </c>
+      <c r="T130">
+        <v>1.4</v>
+      </c>
+      <c r="U130">
+        <v>2.75</v>
+      </c>
+      <c r="V130">
+        <v>2.75</v>
+      </c>
+      <c r="W130">
+        <v>1.4</v>
+      </c>
+      <c r="X130">
+        <v>7</v>
+      </c>
+      <c r="Y130">
+        <v>1.08</v>
+      </c>
+      <c r="Z130">
+        <v>2.88</v>
+      </c>
+      <c r="AA130">
+        <v>3.3</v>
+      </c>
+      <c r="AB130">
+        <v>2.25</v>
+      </c>
+      <c r="AC130">
+        <v>1.01</v>
+      </c>
+      <c r="AD130">
+        <v>10.4</v>
+      </c>
+      <c r="AE130">
+        <v>1.25</v>
+      </c>
+      <c r="AF130">
+        <v>3.68</v>
+      </c>
+      <c r="AG130">
+        <v>1.85</v>
+      </c>
+      <c r="AH130">
+        <v>1.95</v>
+      </c>
+      <c r="AI130">
+        <v>1.73</v>
+      </c>
+      <c r="AJ130">
+        <v>2</v>
+      </c>
+      <c r="AK130">
+        <v>1.55</v>
+      </c>
+      <c r="AL130">
+        <v>1.28</v>
+      </c>
+      <c r="AM130">
+        <v>1.41</v>
+      </c>
+      <c r="AN130">
+        <v>0.86</v>
+      </c>
+      <c r="AO130">
+        <v>1.88</v>
+      </c>
+      <c r="AP130">
+        <v>0.75</v>
+      </c>
+      <c r="AQ130">
+        <v>2</v>
+      </c>
+      <c r="AR130">
+        <v>1.29</v>
+      </c>
+      <c r="AS130">
+        <v>1.49</v>
+      </c>
+      <c r="AT130">
+        <v>2.78</v>
+      </c>
+      <c r="AU130">
+        <v>2</v>
+      </c>
+      <c r="AV130">
+        <v>5</v>
+      </c>
+      <c r="AW130">
+        <v>2</v>
+      </c>
+      <c r="AX130">
+        <v>4</v>
+      </c>
+      <c r="AY130">
+        <v>4</v>
+      </c>
+      <c r="AZ130">
+        <v>10</v>
+      </c>
+      <c r="BA130">
+        <v>6</v>
+      </c>
+      <c r="BB130">
+        <v>4</v>
+      </c>
+      <c r="BC130">
+        <v>10</v>
+      </c>
+      <c r="BD130">
+        <v>2.05</v>
+      </c>
+      <c r="BE130">
+        <v>6.35</v>
+      </c>
+      <c r="BF130">
+        <v>2.17</v>
+      </c>
+      <c r="BG130">
+        <v>1.22</v>
+      </c>
+      <c r="BH130">
+        <v>3.5</v>
+      </c>
+      <c r="BI130">
+        <v>1.43</v>
+      </c>
+      <c r="BJ130">
+        <v>2.54</v>
+      </c>
+      <c r="BK130">
+        <v>1.78</v>
+      </c>
+      <c r="BL130">
+        <v>1.93</v>
+      </c>
+      <c r="BM130">
+        <v>2.25</v>
+      </c>
+      <c r="BN130">
+        <v>1.54</v>
+      </c>
+      <c r="BO130">
+        <v>2.97</v>
+      </c>
+      <c r="BP130">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:68">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>7484666</v>
+      </c>
+      <c r="C131" t="s">
+        <v>68</v>
+      </c>
+      <c r="D131" t="s">
+        <v>69</v>
+      </c>
+      <c r="E131" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F131">
+        <v>17</v>
+      </c>
+      <c r="G131" t="s">
+        <v>72</v>
+      </c>
+      <c r="H131" t="s">
+        <v>78</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>2</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>2</v>
+      </c>
+      <c r="O131" t="s">
+        <v>167</v>
+      </c>
+      <c r="P131" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q131">
+        <v>3.4</v>
+      </c>
+      <c r="R131">
+        <v>2.1</v>
+      </c>
+      <c r="S131">
+        <v>2.88</v>
+      </c>
+      <c r="T131">
+        <v>1.4</v>
+      </c>
+      <c r="U131">
+        <v>2.75</v>
+      </c>
+      <c r="V131">
+        <v>2.75</v>
+      </c>
+      <c r="W131">
+        <v>1.4</v>
+      </c>
+      <c r="X131">
+        <v>7</v>
+      </c>
+      <c r="Y131">
+        <v>1.08</v>
+      </c>
+      <c r="Z131">
+        <v>2.88</v>
+      </c>
+      <c r="AA131">
+        <v>3.25</v>
+      </c>
+      <c r="AB131">
+        <v>2.3</v>
+      </c>
+      <c r="AC131">
+        <v>1</v>
+      </c>
+      <c r="AD131">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE131">
+        <v>1.25</v>
+      </c>
+      <c r="AF131">
+        <v>3.67</v>
+      </c>
+      <c r="AG131">
+        <v>1.85</v>
+      </c>
+      <c r="AH131">
+        <v>1.95</v>
+      </c>
+      <c r="AI131">
+        <v>1.67</v>
+      </c>
+      <c r="AJ131">
+        <v>2.1</v>
+      </c>
+      <c r="AK131">
+        <v>1.57</v>
+      </c>
+      <c r="AL131">
+        <v>1.28</v>
+      </c>
+      <c r="AM131">
+        <v>1.39</v>
+      </c>
+      <c r="AN131">
+        <v>0.63</v>
+      </c>
+      <c r="AO131">
+        <v>1.57</v>
+      </c>
+      <c r="AP131">
+        <v>0.89</v>
+      </c>
+      <c r="AQ131">
+        <v>1.38</v>
+      </c>
+      <c r="AR131">
+        <v>1.14</v>
+      </c>
+      <c r="AS131">
+        <v>1.39</v>
+      </c>
+      <c r="AT131">
+        <v>2.53</v>
+      </c>
+      <c r="AU131">
+        <v>5</v>
+      </c>
+      <c r="AV131">
+        <v>4</v>
+      </c>
+      <c r="AW131">
+        <v>5</v>
+      </c>
+      <c r="AX131">
+        <v>9</v>
+      </c>
+      <c r="AY131">
+        <v>14</v>
+      </c>
+      <c r="AZ131">
+        <v>16</v>
+      </c>
+      <c r="BA131">
+        <v>3</v>
+      </c>
+      <c r="BB131">
+        <v>6</v>
+      </c>
+      <c r="BC131">
+        <v>9</v>
+      </c>
+      <c r="BD131">
+        <v>0</v>
+      </c>
+      <c r="BE131">
+        <v>0</v>
+      </c>
+      <c r="BF131">
+        <v>0</v>
+      </c>
+      <c r="BG131">
+        <v>0</v>
+      </c>
+      <c r="BH131">
+        <v>0</v>
+      </c>
+      <c r="BI131">
+        <v>0</v>
+      </c>
+      <c r="BJ131">
+        <v>0</v>
+      </c>
+      <c r="BK131">
+        <v>0</v>
+      </c>
+      <c r="BL131">
+        <v>0</v>
+      </c>
+      <c r="BM131">
+        <v>0</v>
+      </c>
+      <c r="BN131">
+        <v>0</v>
+      </c>
+      <c r="BO131">
+        <v>0</v>
+      </c>
+      <c r="BP131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7484668</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45709.58333333334</v>
+      </c>
+      <c r="F132">
+        <v>17</v>
+      </c>
+      <c r="G132" t="s">
+        <v>77</v>
+      </c>
+      <c r="H132" t="s">
+        <v>80</v>
+      </c>
+      <c r="I132">
+        <v>1</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+      <c r="O132" t="s">
+        <v>153</v>
+      </c>
+      <c r="P132" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q132">
+        <v>2.88</v>
+      </c>
+      <c r="R132">
+        <v>2.1</v>
+      </c>
+      <c r="S132">
+        <v>3.4</v>
+      </c>
+      <c r="T132">
+        <v>1.4</v>
+      </c>
+      <c r="U132">
+        <v>2.75</v>
+      </c>
+      <c r="V132">
+        <v>2.75</v>
+      </c>
+      <c r="W132">
+        <v>1.4</v>
+      </c>
+      <c r="X132">
+        <v>7</v>
+      </c>
+      <c r="Y132">
+        <v>1.08</v>
+      </c>
+      <c r="Z132">
+        <v>2.3</v>
+      </c>
+      <c r="AA132">
+        <v>3.2</v>
+      </c>
+      <c r="AB132">
+        <v>2.9</v>
+      </c>
+      <c r="AC132">
+        <v>1.03</v>
+      </c>
+      <c r="AD132">
+        <v>9</v>
+      </c>
+      <c r="AE132">
+        <v>1.27</v>
+      </c>
+      <c r="AF132">
+        <v>3.51</v>
+      </c>
+      <c r="AG132">
+        <v>1.95</v>
+      </c>
+      <c r="AH132">
+        <v>1.85</v>
+      </c>
+      <c r="AI132">
+        <v>1.73</v>
+      </c>
+      <c r="AJ132">
+        <v>2</v>
+      </c>
+      <c r="AK132">
+        <v>1.38</v>
+      </c>
+      <c r="AL132">
+        <v>1.3</v>
+      </c>
+      <c r="AM132">
+        <v>1.55</v>
+      </c>
+      <c r="AN132">
+        <v>1.14</v>
+      </c>
+      <c r="AO132">
+        <v>1.63</v>
+      </c>
+      <c r="AP132">
+        <v>1.13</v>
+      </c>
+      <c r="AQ132">
+        <v>1.56</v>
+      </c>
+      <c r="AR132">
+        <v>1.23</v>
+      </c>
+      <c r="AS132">
+        <v>1.17</v>
+      </c>
+      <c r="AT132">
+        <v>2.4</v>
+      </c>
+      <c r="AU132">
+        <v>7</v>
+      </c>
+      <c r="AV132">
+        <v>3</v>
+      </c>
+      <c r="AW132">
+        <v>10</v>
+      </c>
+      <c r="AX132">
+        <v>5</v>
+      </c>
+      <c r="AY132">
+        <v>19</v>
+      </c>
+      <c r="AZ132">
+        <v>9</v>
+      </c>
+      <c r="BA132">
+        <v>9</v>
+      </c>
+      <c r="BB132">
+        <v>6</v>
+      </c>
+      <c r="BC132">
+        <v>15</v>
+      </c>
+      <c r="BD132">
+        <v>1.61</v>
+      </c>
+      <c r="BE132">
+        <v>6.7</v>
+      </c>
+      <c r="BF132">
+        <v>2.98</v>
+      </c>
+      <c r="BG132">
+        <v>1.21</v>
+      </c>
+      <c r="BH132">
+        <v>3.58</v>
+      </c>
+      <c r="BI132">
+        <v>1.42</v>
+      </c>
+      <c r="BJ132">
+        <v>2.57</v>
+      </c>
+      <c r="BK132">
+        <v>1.76</v>
+      </c>
+      <c r="BL132">
+        <v>1.95</v>
+      </c>
+      <c r="BM132">
+        <v>2.21</v>
+      </c>
+      <c r="BN132">
+        <v>1.56</v>
+      </c>
+      <c r="BO132">
+        <v>2.92</v>
+      </c>
+      <c r="BP132">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7484670</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45709.6875</v>
+      </c>
+      <c r="F133">
+        <v>17</v>
+      </c>
+      <c r="G133" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" t="s">
+        <v>85</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>2</v>
+      </c>
+      <c r="L133">
+        <v>3</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>4</v>
+      </c>
+      <c r="O133" t="s">
+        <v>168</v>
+      </c>
+      <c r="P133" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q133">
+        <v>2.5</v>
+      </c>
+      <c r="R133">
+        <v>2.1</v>
+      </c>
+      <c r="S133">
+        <v>4</v>
+      </c>
+      <c r="T133">
+        <v>1.4</v>
+      </c>
+      <c r="U133">
+        <v>2.75</v>
+      </c>
+      <c r="V133">
+        <v>3</v>
+      </c>
+      <c r="W133">
+        <v>1.36</v>
+      </c>
+      <c r="X133">
+        <v>7</v>
+      </c>
+      <c r="Y133">
+        <v>1.08</v>
+      </c>
+      <c r="Z133">
+        <v>1.9</v>
+      </c>
+      <c r="AA133">
+        <v>3.6</v>
+      </c>
+      <c r="AB133">
+        <v>3.5</v>
+      </c>
+      <c r="AC133">
+        <v>1.03</v>
+      </c>
+      <c r="AD133">
+        <v>9</v>
+      </c>
+      <c r="AE133">
+        <v>1.29</v>
+      </c>
+      <c r="AF133">
+        <v>3.25</v>
+      </c>
+      <c r="AG133">
+        <v>1.95</v>
+      </c>
+      <c r="AH133">
+        <v>1.85</v>
+      </c>
+      <c r="AI133">
+        <v>1.83</v>
+      </c>
+      <c r="AJ133">
+        <v>1.83</v>
+      </c>
+      <c r="AK133">
+        <v>1.25</v>
+      </c>
+      <c r="AL133">
+        <v>1.27</v>
+      </c>
+      <c r="AM133">
+        <v>1.83</v>
+      </c>
+      <c r="AN133">
+        <v>2.38</v>
+      </c>
+      <c r="AO133">
+        <v>2.29</v>
+      </c>
+      <c r="AP133">
+        <v>2.44</v>
+      </c>
+      <c r="AQ133">
+        <v>2</v>
+      </c>
+      <c r="AR133">
+        <v>1.4</v>
+      </c>
+      <c r="AS133">
+        <v>1.57</v>
+      </c>
+      <c r="AT133">
+        <v>2.97</v>
+      </c>
+      <c r="AU133">
+        <v>4</v>
+      </c>
+      <c r="AV133">
+        <v>5</v>
+      </c>
+      <c r="AW133">
+        <v>6</v>
+      </c>
+      <c r="AX133">
+        <v>6</v>
+      </c>
+      <c r="AY133">
+        <v>13</v>
+      </c>
+      <c r="AZ133">
+        <v>13</v>
+      </c>
+      <c r="BA133">
+        <v>1</v>
+      </c>
+      <c r="BB133">
+        <v>3</v>
+      </c>
+      <c r="BC133">
+        <v>4</v>
+      </c>
+      <c r="BD133">
+        <v>0</v>
+      </c>
+      <c r="BE133">
+        <v>0</v>
+      </c>
+      <c r="BF133">
+        <v>0</v>
+      </c>
+      <c r="BG133">
+        <v>0</v>
+      </c>
+      <c r="BH133">
+        <v>0</v>
+      </c>
+      <c r="BI133">
+        <v>0</v>
+      </c>
+      <c r="BJ133">
+        <v>0</v>
+      </c>
+      <c r="BK133">
+        <v>0</v>
+      </c>
+      <c r="BL133">
+        <v>0</v>
+      </c>
+      <c r="BM133">
+        <v>0</v>
+      </c>
+      <c r="BN133">
+        <v>0</v>
+      </c>
+      <c r="BO133">
+        <v>0</v>
+      </c>
+      <c r="BP133">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>['36', '61', '74']</t>
+  </si>
+  <si>
+    <t>['30', '74', '79', '89']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1113,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP133"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1369,7 +1372,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1447,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ2">
         <v>2</v>
@@ -1575,7 +1578,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1781,7 +1784,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1987,7 +1990,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2068,7 +2071,7 @@
         <v>0.38</v>
       </c>
       <c r="AQ5">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2193,7 +2196,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2480,7 +2483,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2683,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
         <v>1.43</v>
@@ -3223,7 +3226,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3429,7 +3432,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4047,7 +4050,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4253,7 +4256,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4459,7 +4462,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4665,7 +4668,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4743,7 +4746,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ18">
         <v>1.43</v>
@@ -4871,7 +4874,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5077,7 +5080,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5283,7 +5286,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5489,7 +5492,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5570,7 +5573,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ22">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR22">
         <v>1.76</v>
@@ -5776,7 +5779,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR23">
         <v>2.04</v>
@@ -5901,7 +5904,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -5979,7 +5982,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ24">
         <v>1.56</v>
@@ -6107,7 +6110,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6313,7 +6316,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6519,7 +6522,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6931,7 +6934,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7137,7 +7140,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7343,7 +7346,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7961,7 +7964,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8039,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ34">
         <v>1.33</v>
@@ -8167,7 +8170,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8248,7 +8251,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ35">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR35">
         <v>1.62</v>
@@ -8373,7 +8376,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8579,7 +8582,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8785,7 +8788,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9197,7 +9200,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9403,7 +9406,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9609,7 +9612,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10021,7 +10024,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10102,7 +10105,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR44">
         <v>1.33</v>
@@ -10227,7 +10230,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10433,7 +10436,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10514,7 +10517,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ46">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR46">
         <v>1.15</v>
@@ -10639,7 +10642,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10845,7 +10848,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11463,7 +11466,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11669,7 +11672,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11747,7 +11750,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ52">
         <v>0.75</v>
@@ -11953,7 +11956,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
         <v>0.5</v>
@@ -12081,7 +12084,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12493,7 +12496,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12699,7 +12702,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12905,7 +12908,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -12986,7 +12989,7 @@
         <v>2</v>
       </c>
       <c r="AQ58">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR58">
         <v>1.23</v>
@@ -13395,7 +13398,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ60">
         <v>1.38</v>
@@ -13523,7 +13526,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13604,7 +13607,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR61">
         <v>1.31</v>
@@ -13935,7 +13938,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14347,7 +14350,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14428,7 +14431,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR65">
         <v>1.19</v>
@@ -14553,7 +14556,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14759,7 +14762,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14965,7 +14968,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15583,7 +15586,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15867,7 +15870,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ72">
         <v>1.44</v>
@@ -16407,7 +16410,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16613,7 +16616,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16819,7 +16822,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17025,7 +17028,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17231,7 +17234,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17312,7 +17315,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ79">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR79">
         <v>0.98</v>
@@ -17643,7 +17646,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18339,7 +18342,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ84">
         <v>0.5</v>
@@ -18467,7 +18470,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18548,7 +18551,7 @@
         <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR85">
         <v>1.86</v>
@@ -18673,7 +18676,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18751,7 +18754,7 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ86">
         <v>2.38</v>
@@ -19085,7 +19088,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19291,7 +19294,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19497,7 +19500,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19909,7 +19912,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20115,7 +20118,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20321,7 +20324,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20527,7 +20530,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20939,7 +20942,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21226,7 +21229,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ98">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR98">
         <v>1.62</v>
@@ -21351,7 +21354,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21557,7 +21560,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21763,7 +21766,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22175,7 +22178,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22253,7 +22256,7 @@
         <v>2.17</v>
       </c>
       <c r="AP103">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
         <v>2.38</v>
@@ -22381,7 +22384,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22665,10 +22668,10 @@
         <v>1.17</v>
       </c>
       <c r="AP105">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR105">
         <v>1.61</v>
@@ -22793,7 +22796,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22999,7 +23002,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23205,7 +23208,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23411,7 +23414,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24235,7 +24238,7 @@
         <v>137</v>
       </c>
       <c r="P113" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24853,7 +24856,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -24934,7 +24937,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ116">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR116">
         <v>1.11</v>
@@ -25140,7 +25143,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -25471,7 +25474,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25549,7 +25552,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ119">
         <v>1.38</v>
@@ -25755,7 +25758,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120">
         <v>0.89</v>
@@ -26089,7 +26092,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26501,7 +26504,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26707,7 +26710,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26913,7 +26916,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27119,7 +27122,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27325,7 +27328,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27531,7 +27534,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27737,7 +27740,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28149,7 +28152,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28355,7 +28358,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28512,6 +28515,418 @@
       </c>
       <c r="BP133">
         <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7484664</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45710.4375</v>
+      </c>
+      <c r="F134">
+        <v>17</v>
+      </c>
+      <c r="G134" t="s">
+        <v>70</v>
+      </c>
+      <c r="H134" t="s">
+        <v>79</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>1</v>
+      </c>
+      <c r="L134">
+        <v>4</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>5</v>
+      </c>
+      <c r="O134" t="s">
+        <v>169</v>
+      </c>
+      <c r="P134" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q134">
+        <v>2.03</v>
+      </c>
+      <c r="R134">
+        <v>2.66</v>
+      </c>
+      <c r="S134">
+        <v>4.83</v>
+      </c>
+      <c r="T134">
+        <v>1.22</v>
+      </c>
+      <c r="U134">
+        <v>3.8</v>
+      </c>
+      <c r="V134">
+        <v>2.13</v>
+      </c>
+      <c r="W134">
+        <v>1.68</v>
+      </c>
+      <c r="X134">
+        <v>4.4</v>
+      </c>
+      <c r="Y134">
+        <v>1.18</v>
+      </c>
+      <c r="Z134">
+        <v>1.57</v>
+      </c>
+      <c r="AA134">
+        <v>4.58</v>
+      </c>
+      <c r="AB134">
+        <v>4.19</v>
+      </c>
+      <c r="AC134">
+        <v>1.01</v>
+      </c>
+      <c r="AD134">
+        <v>17</v>
+      </c>
+      <c r="AE134">
+        <v>1.13</v>
+      </c>
+      <c r="AF134">
+        <v>5.4</v>
+      </c>
+      <c r="AG134">
+        <v>1.44</v>
+      </c>
+      <c r="AH134">
+        <v>2.65</v>
+      </c>
+      <c r="AI134">
+        <v>1.52</v>
+      </c>
+      <c r="AJ134">
+        <v>2.35</v>
+      </c>
+      <c r="AK134">
+        <v>1.19</v>
+      </c>
+      <c r="AL134">
+        <v>1.19</v>
+      </c>
+      <c r="AM134">
+        <v>2.25</v>
+      </c>
+      <c r="AN134">
+        <v>0.75</v>
+      </c>
+      <c r="AO134">
+        <v>0.5</v>
+      </c>
+      <c r="AP134">
+        <v>1</v>
+      </c>
+      <c r="AQ134">
+        <v>0.44</v>
+      </c>
+      <c r="AR134">
+        <v>1.56</v>
+      </c>
+      <c r="AS134">
+        <v>1.37</v>
+      </c>
+      <c r="AT134">
+        <v>2.93</v>
+      </c>
+      <c r="AU134">
+        <v>8</v>
+      </c>
+      <c r="AV134">
+        <v>3</v>
+      </c>
+      <c r="AW134">
+        <v>4</v>
+      </c>
+      <c r="AX134">
+        <v>5</v>
+      </c>
+      <c r="AY134">
+        <v>12</v>
+      </c>
+      <c r="AZ134">
+        <v>8</v>
+      </c>
+      <c r="BA134">
+        <v>4</v>
+      </c>
+      <c r="BB134">
+        <v>3</v>
+      </c>
+      <c r="BC134">
+        <v>7</v>
+      </c>
+      <c r="BD134">
+        <v>1.47</v>
+      </c>
+      <c r="BE134">
+        <v>7.3</v>
+      </c>
+      <c r="BF134">
+        <v>3.48</v>
+      </c>
+      <c r="BG134">
+        <v>1.15</v>
+      </c>
+      <c r="BH134">
+        <v>4.5</v>
+      </c>
+      <c r="BI134">
+        <v>1.26</v>
+      </c>
+      <c r="BJ134">
+        <v>3.22</v>
+      </c>
+      <c r="BK134">
+        <v>1.49</v>
+      </c>
+      <c r="BL134">
+        <v>2.38</v>
+      </c>
+      <c r="BM134">
+        <v>1.85</v>
+      </c>
+      <c r="BN134">
+        <v>1.85</v>
+      </c>
+      <c r="BO134">
+        <v>2.32</v>
+      </c>
+      <c r="BP134">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7484671</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45710.66666666666</v>
+      </c>
+      <c r="F135">
+        <v>17</v>
+      </c>
+      <c r="G135" t="s">
+        <v>76</v>
+      </c>
+      <c r="H135" t="s">
+        <v>84</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="L135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135" t="s">
+        <v>99</v>
+      </c>
+      <c r="P135" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q135">
+        <v>2.59</v>
+      </c>
+      <c r="R135">
+        <v>2.61</v>
+      </c>
+      <c r="S135">
+        <v>3.33</v>
+      </c>
+      <c r="T135">
+        <v>1.21</v>
+      </c>
+      <c r="U135">
+        <v>4</v>
+      </c>
+      <c r="V135">
+        <v>2.06</v>
+      </c>
+      <c r="W135">
+        <v>1.74</v>
+      </c>
+      <c r="X135">
+        <v>4.2</v>
+      </c>
+      <c r="Y135">
+        <v>1.19</v>
+      </c>
+      <c r="Z135">
+        <v>1.95</v>
+      </c>
+      <c r="AA135">
+        <v>3.7</v>
+      </c>
+      <c r="AB135">
+        <v>2.8</v>
+      </c>
+      <c r="AC135">
+        <v>1.01</v>
+      </c>
+      <c r="AD135">
+        <v>17</v>
+      </c>
+      <c r="AE135">
+        <v>1.12</v>
+      </c>
+      <c r="AF135">
+        <v>5.8</v>
+      </c>
+      <c r="AG135">
+        <v>1.41</v>
+      </c>
+      <c r="AH135">
+        <v>2.75</v>
+      </c>
+      <c r="AI135">
+        <v>1.4</v>
+      </c>
+      <c r="AJ135">
+        <v>2.7</v>
+      </c>
+      <c r="AK135">
+        <v>1.41</v>
+      </c>
+      <c r="AL135">
+        <v>1.22</v>
+      </c>
+      <c r="AM135">
+        <v>1.68</v>
+      </c>
+      <c r="AN135">
+        <v>1.29</v>
+      </c>
+      <c r="AO135">
+        <v>1.38</v>
+      </c>
+      <c r="AP135">
+        <v>1.5</v>
+      </c>
+      <c r="AQ135">
+        <v>1.22</v>
+      </c>
+      <c r="AR135">
+        <v>1.26</v>
+      </c>
+      <c r="AS135">
+        <v>1.46</v>
+      </c>
+      <c r="AT135">
+        <v>2.72</v>
+      </c>
+      <c r="AU135">
+        <v>5</v>
+      </c>
+      <c r="AV135">
+        <v>10</v>
+      </c>
+      <c r="AW135">
+        <v>5</v>
+      </c>
+      <c r="AX135">
+        <v>11</v>
+      </c>
+      <c r="AY135">
+        <v>13</v>
+      </c>
+      <c r="AZ135">
+        <v>24</v>
+      </c>
+      <c r="BA135">
+        <v>3</v>
+      </c>
+      <c r="BB135">
+        <v>7</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>2</v>
+      </c>
+      <c r="BE135">
+        <v>6.55</v>
+      </c>
+      <c r="BF135">
+        <v>2.21</v>
+      </c>
+      <c r="BG135">
+        <v>0</v>
+      </c>
+      <c r="BH135">
+        <v>0</v>
+      </c>
+      <c r="BI135">
+        <v>1.32</v>
+      </c>
+      <c r="BJ135">
+        <v>2.88</v>
+      </c>
+      <c r="BK135">
+        <v>1.6</v>
+      </c>
+      <c r="BL135">
+        <v>2.14</v>
+      </c>
+      <c r="BM135">
+        <v>2.02</v>
+      </c>
+      <c r="BN135">
+        <v>1.71</v>
+      </c>
+      <c r="BO135">
+        <v>2.6</v>
+      </c>
+      <c r="BP135">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="247">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1116,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1865,7 +1865,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ4">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ5">
         <v>1.22</v>
@@ -5367,7 +5367,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ21">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR21">
         <v>1.86</v>
@@ -6394,7 +6394,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ26">
         <v>1.44</v>
@@ -9281,7 +9281,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ40">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -11547,7 +11547,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ51">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR51">
         <v>1.65</v>
@@ -12574,7 +12574,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -14016,7 +14016,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -16285,7 +16285,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ74">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR74">
         <v>1.42</v>
@@ -16488,7 +16488,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ75">
         <v>1.33</v>
@@ -19166,7 +19166,7 @@
         <v>1.2</v>
       </c>
       <c r="AP88">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ88">
         <v>2</v>
@@ -19787,7 +19787,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ91">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR91">
         <v>1.44</v>
@@ -21844,7 +21844,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ101">
         <v>0.89</v>
@@ -22259,7 +22259,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ103">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -24522,7 +24522,7 @@
         <v>2.5</v>
       </c>
       <c r="AP114">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AQ114">
         <v>2.38</v>
@@ -25349,7 +25349,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ118">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AR118">
         <v>1.23</v>
@@ -28927,6 +28927,212 @@
       </c>
       <c r="BP135">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7484667</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45711.35416666666</v>
+      </c>
+      <c r="F136">
+        <v>17</v>
+      </c>
+      <c r="G136" t="s">
+        <v>73</v>
+      </c>
+      <c r="H136" t="s">
+        <v>81</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>1</v>
+      </c>
+      <c r="O136" t="s">
+        <v>86</v>
+      </c>
+      <c r="P136" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q136">
+        <v>7.8</v>
+      </c>
+      <c r="R136">
+        <v>2.65</v>
+      </c>
+      <c r="S136">
+        <v>1.72</v>
+      </c>
+      <c r="T136">
+        <v>1.28</v>
+      </c>
+      <c r="U136">
+        <v>3.4</v>
+      </c>
+      <c r="V136">
+        <v>2.28</v>
+      </c>
+      <c r="W136">
+        <v>1.57</v>
+      </c>
+      <c r="X136">
+        <v>5.1</v>
+      </c>
+      <c r="Y136">
+        <v>1.14</v>
+      </c>
+      <c r="Z136">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA136">
+        <v>5.05</v>
+      </c>
+      <c r="AB136">
+        <v>1.34</v>
+      </c>
+      <c r="AC136">
+        <v>1.01</v>
+      </c>
+      <c r="AD136">
+        <v>13</v>
+      </c>
+      <c r="AE136">
+        <v>1.2</v>
+      </c>
+      <c r="AF136">
+        <v>4.2</v>
+      </c>
+      <c r="AG136">
+        <v>1.61</v>
+      </c>
+      <c r="AH136">
+        <v>2.22</v>
+      </c>
+      <c r="AI136">
+        <v>1.96</v>
+      </c>
+      <c r="AJ136">
+        <v>1.75</v>
+      </c>
+      <c r="AK136">
+        <v>3.1</v>
+      </c>
+      <c r="AL136">
+        <v>1.13</v>
+      </c>
+      <c r="AM136">
+        <v>1.07</v>
+      </c>
+      <c r="AN136">
+        <v>0.38</v>
+      </c>
+      <c r="AO136">
+        <v>2.38</v>
+      </c>
+      <c r="AP136">
+        <v>0.33</v>
+      </c>
+      <c r="AQ136">
+        <v>2.44</v>
+      </c>
+      <c r="AR136">
+        <v>1.11</v>
+      </c>
+      <c r="AS136">
+        <v>1.53</v>
+      </c>
+      <c r="AT136">
+        <v>2.64</v>
+      </c>
+      <c r="AU136">
+        <v>2</v>
+      </c>
+      <c r="AV136">
+        <v>7</v>
+      </c>
+      <c r="AW136">
+        <v>0</v>
+      </c>
+      <c r="AX136">
+        <v>7</v>
+      </c>
+      <c r="AY136">
+        <v>2</v>
+      </c>
+      <c r="AZ136">
+        <v>17</v>
+      </c>
+      <c r="BA136">
+        <v>0</v>
+      </c>
+      <c r="BB136">
+        <v>5</v>
+      </c>
+      <c r="BC136">
+        <v>5</v>
+      </c>
+      <c r="BD136">
+        <v>5.7</v>
+      </c>
+      <c r="BE136">
+        <v>10.75</v>
+      </c>
+      <c r="BF136">
+        <v>1.2</v>
+      </c>
+      <c r="BG136">
+        <v>1.38</v>
+      </c>
+      <c r="BH136">
+        <v>2.71</v>
+      </c>
+      <c r="BI136">
+        <v>1.71</v>
+      </c>
+      <c r="BJ136">
+        <v>2.02</v>
+      </c>
+      <c r="BK136">
+        <v>2.17</v>
+      </c>
+      <c r="BL136">
+        <v>1.58</v>
+      </c>
+      <c r="BM136">
+        <v>2.88</v>
+      </c>
+      <c r="BN136">
+        <v>1.32</v>
+      </c>
+      <c r="BO136">
+        <v>0</v>
+      </c>
+      <c r="BP136">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="249">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -526,6 +526,9 @@
     <t>['30', '74', '79', '89']</t>
   </si>
   <si>
+    <t>['32', '90+3']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -755,6 +758,9 @@
   </si>
   <si>
     <t>['42']</t>
+  </si>
+  <si>
+    <t>['40']</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP136"/>
+  <dimension ref="A1:BP137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1372,7 +1378,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1578,7 +1584,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1656,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>1.38</v>
@@ -1784,7 +1790,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1990,7 +1996,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2196,7 +2202,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2689,7 +2695,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3226,7 +3232,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3432,7 +3438,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4050,7 +4056,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4256,7 +4262,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4462,7 +4468,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4668,7 +4674,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4749,7 +4755,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
         <v>1.17</v>
@@ -4874,7 +4880,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -4952,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ19">
         <v>0.75</v>
@@ -5080,7 +5086,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5286,7 +5292,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5492,7 +5498,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5904,7 +5910,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6110,7 +6116,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6316,7 +6322,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6522,7 +6528,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6934,7 +6940,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7140,7 +7146,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7346,7 +7352,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7964,7 +7970,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8170,7 +8176,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8376,7 +8382,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8457,7 +8463,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ36">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR36">
         <v>1.65</v>
@@ -8582,7 +8588,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8788,7 +8794,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9200,7 +9206,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9406,7 +9412,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9484,7 +9490,7 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ41">
         <v>1.56</v>
@@ -9612,7 +9618,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10024,7 +10030,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10230,7 +10236,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10311,7 +10317,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ45">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR45">
         <v>0.9399999999999999</v>
@@ -10436,7 +10442,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10642,7 +10648,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10720,7 +10726,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
         <v>2</v>
@@ -10848,7 +10854,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11466,7 +11472,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11672,7 +11678,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12084,7 +12090,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12496,7 +12502,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12702,7 +12708,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12908,7 +12914,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13526,7 +13532,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13938,7 +13944,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14350,7 +14356,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14428,7 +14434,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ65">
         <v>0.44</v>
@@ -14556,7 +14562,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14762,7 +14768,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14968,7 +14974,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15586,7 +15592,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16410,7 +16416,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16616,7 +16622,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16697,7 +16703,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR76">
         <v>1.4</v>
@@ -16822,7 +16828,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17028,7 +17034,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17234,7 +17240,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17646,7 +17652,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18470,7 +18476,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18676,7 +18682,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19088,7 +19094,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19294,7 +19300,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19500,7 +19506,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19912,7 +19918,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20118,7 +20124,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20196,7 +20202,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>1.63</v>
@@ -20324,7 +20330,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20405,7 +20411,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR94">
         <v>1.93</v>
@@ -20530,7 +20536,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20942,7 +20948,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21354,7 +21360,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21560,7 +21566,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21766,7 +21772,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22178,7 +22184,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22384,7 +22390,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22462,7 +22468,7 @@
         <v>2.4</v>
       </c>
       <c r="AP104">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ104">
         <v>2.38</v>
@@ -22796,7 +22802,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23002,7 +23008,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23208,7 +23214,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23414,7 +23420,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23701,7 +23707,7 @@
         <v>2</v>
       </c>
       <c r="AQ110">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AR110">
         <v>1.28</v>
@@ -24238,7 +24244,7 @@
         <v>137</v>
       </c>
       <c r="P113" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24728,7 +24734,7 @@
         <v>1.71</v>
       </c>
       <c r="AP115">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ115">
         <v>1.44</v>
@@ -24856,7 +24862,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25474,7 +25480,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26092,7 +26098,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26504,7 +26510,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26710,7 +26716,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26916,7 +26922,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27122,7 +27128,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27328,7 +27334,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27534,7 +27540,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27740,7 +27746,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28152,7 +28158,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28358,7 +28364,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29133,6 +29139,212 @@
       </c>
       <c r="BP136">
         <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7484665</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45713.58333333334</v>
+      </c>
+      <c r="F137">
+        <v>17</v>
+      </c>
+      <c r="G137" t="s">
+        <v>71</v>
+      </c>
+      <c r="H137" t="s">
+        <v>83</v>
+      </c>
+      <c r="I137">
+        <v>1</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>2</v>
+      </c>
+      <c r="M137">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>3</v>
+      </c>
+      <c r="O137" t="s">
+        <v>170</v>
+      </c>
+      <c r="P137" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q137">
+        <v>2.75</v>
+      </c>
+      <c r="R137">
+        <v>2.2</v>
+      </c>
+      <c r="S137">
+        <v>3.6</v>
+      </c>
+      <c r="T137">
+        <v>1.36</v>
+      </c>
+      <c r="U137">
+        <v>3</v>
+      </c>
+      <c r="V137">
+        <v>2.63</v>
+      </c>
+      <c r="W137">
+        <v>1.44</v>
+      </c>
+      <c r="X137">
+        <v>6.5</v>
+      </c>
+      <c r="Y137">
+        <v>1.1</v>
+      </c>
+      <c r="Z137">
+        <v>2.1</v>
+      </c>
+      <c r="AA137">
+        <v>3.2</v>
+      </c>
+      <c r="AB137">
+        <v>3.3</v>
+      </c>
+      <c r="AC137">
+        <v>1</v>
+      </c>
+      <c r="AD137">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE137">
+        <v>1.25</v>
+      </c>
+      <c r="AF137">
+        <v>3.73</v>
+      </c>
+      <c r="AG137">
+        <v>1.85</v>
+      </c>
+      <c r="AH137">
+        <v>1.95</v>
+      </c>
+      <c r="AI137">
+        <v>1.67</v>
+      </c>
+      <c r="AJ137">
+        <v>2.1</v>
+      </c>
+      <c r="AK137">
+        <v>1.32</v>
+      </c>
+      <c r="AL137">
+        <v>1.29</v>
+      </c>
+      <c r="AM137">
+        <v>1.65</v>
+      </c>
+      <c r="AN137">
+        <v>0.75</v>
+      </c>
+      <c r="AO137">
+        <v>1.43</v>
+      </c>
+      <c r="AP137">
+        <v>1</v>
+      </c>
+      <c r="AQ137">
+        <v>1.25</v>
+      </c>
+      <c r="AR137">
+        <v>1.29</v>
+      </c>
+      <c r="AS137">
+        <v>1.37</v>
+      </c>
+      <c r="AT137">
+        <v>2.66</v>
+      </c>
+      <c r="AU137">
+        <v>6</v>
+      </c>
+      <c r="AV137">
+        <v>3</v>
+      </c>
+      <c r="AW137">
+        <v>7</v>
+      </c>
+      <c r="AX137">
+        <v>4</v>
+      </c>
+      <c r="AY137">
+        <v>15</v>
+      </c>
+      <c r="AZ137">
+        <v>10</v>
+      </c>
+      <c r="BA137">
+        <v>5</v>
+      </c>
+      <c r="BB137">
+        <v>2</v>
+      </c>
+      <c r="BC137">
+        <v>7</v>
+      </c>
+      <c r="BD137">
+        <v>1.66</v>
+      </c>
+      <c r="BE137">
+        <v>6.6</v>
+      </c>
+      <c r="BF137">
+        <v>2.84</v>
+      </c>
+      <c r="BG137">
+        <v>1.21</v>
+      </c>
+      <c r="BH137">
+        <v>3.58</v>
+      </c>
+      <c r="BI137">
+        <v>1.42</v>
+      </c>
+      <c r="BJ137">
+        <v>2.57</v>
+      </c>
+      <c r="BK137">
+        <v>1.76</v>
+      </c>
+      <c r="BL137">
+        <v>1.95</v>
+      </c>
+      <c r="BM137">
+        <v>2.21</v>
+      </c>
+      <c r="BN137">
+        <v>1.56</v>
+      </c>
+      <c r="BO137">
+        <v>2.92</v>
+      </c>
+      <c r="BP137">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="255">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -529,6 +529,21 @@
     <t>['32', '90+3']</t>
   </si>
   <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['28', '50']</t>
+  </si>
+  <si>
+    <t>['49', '55']</t>
+  </si>
+  <si>
+    <t>['8', '38', '45']</t>
+  </si>
+  <si>
+    <t>['1', '40']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -721,9 +736,6 @@
     <t>['19', '45+1', '69', '87']</t>
   </si>
   <si>
-    <t>['43']</t>
-  </si>
-  <si>
     <t>['25', '31', '69']</t>
   </si>
   <si>
@@ -761,6 +773,12 @@
   </si>
   <si>
     <t>['40']</t>
+  </si>
+  <si>
+    <t>['16']</t>
+  </si>
+  <si>
+    <t>['69']</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP137"/>
+  <dimension ref="A1:BP143"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1378,7 +1396,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1584,7 +1602,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1790,7 +1808,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1996,7 +2014,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2074,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ5">
         <v>1.22</v>
@@ -2202,7 +2220,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2901,7 +2919,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ9">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3104,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3232,7 +3250,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3310,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ11">
         <v>1.63</v>
@@ -3438,7 +3456,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3519,7 +3537,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ12">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3722,7 +3740,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ13">
         <v>0.75</v>
@@ -3931,7 +3949,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ14">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4056,7 +4074,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4137,7 +4155,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ15">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4262,7 +4280,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4340,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ16">
         <v>1.33</v>
@@ -4468,7 +4486,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4546,10 +4564,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ17">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4674,7 +4692,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4880,7 +4898,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5086,7 +5104,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5292,7 +5310,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5498,7 +5516,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5910,7 +5928,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6116,7 +6134,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6322,7 +6340,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6400,10 +6418,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ26">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6528,7 +6546,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6609,7 +6627,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ27">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR27">
         <v>1.73</v>
@@ -6815,7 +6833,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ28">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR28">
         <v>1.55</v>
@@ -6940,7 +6958,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7018,7 +7036,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ29">
         <v>1.33</v>
@@ -7146,7 +7164,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7224,10 +7242,10 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR30">
         <v>1.86</v>
@@ -7352,7 +7370,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7430,10 +7448,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ31">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR31">
         <v>0.93</v>
@@ -7636,7 +7654,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ32">
         <v>1.63</v>
@@ -7842,10 +7860,10 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ33">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR33">
         <v>1.76</v>
@@ -7970,7 +7988,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8176,7 +8194,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8382,7 +8400,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8460,7 +8478,7 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ36">
         <v>1.25</v>
@@ -8588,7 +8606,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8669,7 +8687,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ37">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR37">
         <v>1.32</v>
@@ -8794,7 +8812,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -8872,10 +8890,10 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ38">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR38">
         <v>0.95</v>
@@ -9206,7 +9224,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9284,7 +9302,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ40">
         <v>2.44</v>
@@ -9412,7 +9430,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9618,7 +9636,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9699,7 +9717,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR42">
         <v>1.18</v>
@@ -9902,10 +9920,10 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ43">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10030,7 +10048,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10236,7 +10254,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10442,7 +10460,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10520,7 +10538,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ46">
         <v>1.22</v>
@@ -10648,7 +10666,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10729,7 +10747,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR47">
         <v>1.13</v>
@@ -10854,7 +10872,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -10932,7 +10950,7 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ48">
         <v>1.56</v>
@@ -11141,7 +11159,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ49">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR49">
         <v>1.42</v>
@@ -11472,7 +11490,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11550,7 +11568,7 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ51">
         <v>2.44</v>
@@ -11678,7 +11696,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11965,7 +11983,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR53">
         <v>0.98</v>
@@ -12090,7 +12108,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12377,7 +12395,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ55">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12502,7 +12520,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12580,7 +12598,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ56">
         <v>1.38</v>
@@ -12708,7 +12726,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12914,7 +12932,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -12992,7 +13010,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ58">
         <v>1.22</v>
@@ -13201,7 +13219,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR59">
         <v>1.05</v>
@@ -13407,7 +13425,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ60">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR60">
         <v>1.45</v>
@@ -13532,7 +13550,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13819,7 +13837,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ62">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -13944,7 +13962,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14022,7 +14040,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ63">
         <v>2</v>
@@ -14228,7 +14246,7 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ64">
         <v>1.38</v>
@@ -14356,7 +14374,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14562,7 +14580,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14643,7 +14661,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ66">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14768,7 +14786,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14974,7 +14992,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15052,7 +15070,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ68">
         <v>1.33</v>
@@ -15258,7 +15276,7 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ69">
         <v>1.56</v>
@@ -15464,10 +15482,10 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ70">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR70">
         <v>1.74</v>
@@ -15592,7 +15610,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15670,10 +15688,10 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ71">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15879,7 +15897,7 @@
         <v>1</v>
       </c>
       <c r="AQ72">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16416,7 +16434,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16494,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ75">
         <v>1.33</v>
@@ -16622,7 +16640,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16828,7 +16846,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16909,7 +16927,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ77">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR77">
         <v>1.02</v>
@@ -17034,7 +17052,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17112,7 +17130,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ78">
         <v>2</v>
@@ -17240,7 +17258,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17652,7 +17670,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17730,10 +17748,10 @@
         <v>0.8</v>
       </c>
       <c r="AP81">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.61</v>
@@ -17936,7 +17954,7 @@
         <v>2.4</v>
       </c>
       <c r="AP82">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ82">
         <v>1.56</v>
@@ -18142,10 +18160,10 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ83">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR83">
         <v>1.17</v>
@@ -18351,7 +18369,7 @@
         <v>1</v>
       </c>
       <c r="AQ84">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -18476,7 +18494,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18554,7 +18572,7 @@
         <v>0.2</v>
       </c>
       <c r="AP85">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ85">
         <v>0.44</v>
@@ -18682,7 +18700,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18763,7 +18781,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ86">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -18969,7 +18987,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ87">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR87">
         <v>1.6</v>
@@ -19094,7 +19112,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19172,10 +19190,10 @@
         <v>1.2</v>
       </c>
       <c r="AP88">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ88">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR88">
         <v>1.25</v>
@@ -19300,7 +19318,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19506,7 +19524,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19918,7 +19936,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20124,7 +20142,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20330,7 +20348,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20408,7 +20426,7 @@
         <v>1.8</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ94">
         <v>1.25</v>
@@ -20536,7 +20554,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20614,7 +20632,7 @@
         <v>1.2</v>
       </c>
       <c r="AP95">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ95">
         <v>0.75</v>
@@ -20823,7 +20841,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -20948,7 +20966,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21232,7 +21250,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ98">
         <v>0.44</v>
@@ -21360,7 +21378,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21566,7 +21584,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21647,7 +21665,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR100">
         <v>1.75</v>
@@ -21772,7 +21790,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21850,10 +21868,10 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ101">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR101">
         <v>1.23</v>
@@ -22056,10 +22074,10 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR102">
         <v>1.18</v>
@@ -22184,7 +22202,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22390,7 +22408,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22471,7 +22489,7 @@
         <v>1</v>
       </c>
       <c r="AQ104">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22802,7 +22820,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22883,7 +22901,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ106">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23008,7 +23026,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23086,10 +23104,10 @@
         <v>1.71</v>
       </c>
       <c r="AP107">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ107">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -23214,7 +23232,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23292,7 +23310,7 @@
         <v>2.17</v>
       </c>
       <c r="AP108">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ108">
         <v>2</v>
@@ -23420,7 +23438,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23498,7 +23516,7 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ109">
         <v>1.33</v>
@@ -23704,7 +23722,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ110">
         <v>1.25</v>
@@ -24244,7 +24262,7 @@
         <v>137</v>
       </c>
       <c r="P113" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="Q113">
         <v>2.25</v>
@@ -24325,7 +24343,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24528,10 +24546,10 @@
         <v>2.5</v>
       </c>
       <c r="AP114">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ114">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR114">
         <v>1.14</v>
@@ -24737,7 +24755,7 @@
         <v>1</v>
       </c>
       <c r="AQ115">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -24862,7 +24880,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25352,7 +25370,7 @@
         <v>2.29</v>
       </c>
       <c r="AP118">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ118">
         <v>2.44</v>
@@ -25480,7 +25498,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25767,7 +25785,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR120">
         <v>1.33</v>
@@ -26098,7 +26116,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26176,10 +26194,10 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ122">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR122">
         <v>1.65</v>
@@ -26382,10 +26400,10 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR123">
         <v>1.4</v>
@@ -26510,7 +26528,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26591,7 +26609,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ124">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AR124">
         <v>1.35</v>
@@ -26716,7 +26734,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26794,7 +26812,7 @@
         <v>1.86</v>
       </c>
       <c r="AP125">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ125">
         <v>1.63</v>
@@ -26922,7 +26940,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27003,7 +27021,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ126">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AR126">
         <v>1.27</v>
@@ -27128,7 +27146,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27206,10 +27224,10 @@
         <v>1.5</v>
       </c>
       <c r="AP127">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="AQ127">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR127">
         <v>1.44</v>
@@ -27334,7 +27352,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27540,7 +27558,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27618,7 +27636,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ129">
         <v>0.75</v>
@@ -27746,7 +27764,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -27827,7 +27845,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ130">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AR130">
         <v>1.29</v>
@@ -28158,7 +28176,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28364,7 +28382,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29060,7 +29078,7 @@
         <v>2.38</v>
       </c>
       <c r="AP136">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AQ136">
         <v>2.44</v>
@@ -29188,7 +29206,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29345,6 +29363,1242 @@
       </c>
       <c r="BP137">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7484672</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F138">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>78</v>
+      </c>
+      <c r="H138" t="s">
+        <v>82</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138" t="s">
+        <v>86</v>
+      </c>
+      <c r="P138" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q138">
+        <v>3.75</v>
+      </c>
+      <c r="R138">
+        <v>2.18</v>
+      </c>
+      <c r="S138">
+        <v>2.85</v>
+      </c>
+      <c r="T138">
+        <v>1.39</v>
+      </c>
+      <c r="U138">
+        <v>2.8</v>
+      </c>
+      <c r="V138">
+        <v>2.7</v>
+      </c>
+      <c r="W138">
+        <v>1.41</v>
+      </c>
+      <c r="X138">
+        <v>6.15</v>
+      </c>
+      <c r="Y138">
+        <v>1.1</v>
+      </c>
+      <c r="Z138">
+        <v>3</v>
+      </c>
+      <c r="AA138">
+        <v>3.25</v>
+      </c>
+      <c r="AB138">
+        <v>2.17</v>
+      </c>
+      <c r="AC138">
+        <v>1.03</v>
+      </c>
+      <c r="AD138">
+        <v>9</v>
+      </c>
+      <c r="AE138">
+        <v>1.28</v>
+      </c>
+      <c r="AF138">
+        <v>3.3</v>
+      </c>
+      <c r="AG138">
+        <v>1.88</v>
+      </c>
+      <c r="AH138">
+        <v>1.86</v>
+      </c>
+      <c r="AI138">
+        <v>1.71</v>
+      </c>
+      <c r="AJ138">
+        <v>2.03</v>
+      </c>
+      <c r="AK138">
+        <v>1.63</v>
+      </c>
+      <c r="AL138">
+        <v>1.28</v>
+      </c>
+      <c r="AM138">
+        <v>1.35</v>
+      </c>
+      <c r="AN138">
+        <v>1.67</v>
+      </c>
+      <c r="AO138">
+        <v>2</v>
+      </c>
+      <c r="AP138">
+        <v>1.6</v>
+      </c>
+      <c r="AQ138">
+        <v>1.9</v>
+      </c>
+      <c r="AR138">
+        <v>1.61</v>
+      </c>
+      <c r="AS138">
+        <v>1.47</v>
+      </c>
+      <c r="AT138">
+        <v>3.08</v>
+      </c>
+      <c r="AU138">
+        <v>8</v>
+      </c>
+      <c r="AV138">
+        <v>8</v>
+      </c>
+      <c r="AW138">
+        <v>5</v>
+      </c>
+      <c r="AX138">
+        <v>12</v>
+      </c>
+      <c r="AY138">
+        <v>13</v>
+      </c>
+      <c r="AZ138">
+        <v>26</v>
+      </c>
+      <c r="BA138">
+        <v>3</v>
+      </c>
+      <c r="BB138">
+        <v>14</v>
+      </c>
+      <c r="BC138">
+        <v>17</v>
+      </c>
+      <c r="BD138">
+        <v>0</v>
+      </c>
+      <c r="BE138">
+        <v>0</v>
+      </c>
+      <c r="BF138">
+        <v>0</v>
+      </c>
+      <c r="BG138">
+        <v>0</v>
+      </c>
+      <c r="BH138">
+        <v>0</v>
+      </c>
+      <c r="BI138">
+        <v>0</v>
+      </c>
+      <c r="BJ138">
+        <v>0</v>
+      </c>
+      <c r="BK138">
+        <v>2.38</v>
+      </c>
+      <c r="BL138">
+        <v>0</v>
+      </c>
+      <c r="BM138">
+        <v>0</v>
+      </c>
+      <c r="BN138">
+        <v>0</v>
+      </c>
+      <c r="BO138">
+        <v>0</v>
+      </c>
+      <c r="BP138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7484673</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F139">
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>79</v>
+      </c>
+      <c r="H139" t="s">
+        <v>74</v>
+      </c>
+      <c r="I139">
+        <v>1</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>171</v>
+      </c>
+      <c r="P139" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q139">
+        <v>4.8</v>
+      </c>
+      <c r="R139">
+        <v>2.4</v>
+      </c>
+      <c r="S139">
+        <v>2.18</v>
+      </c>
+      <c r="T139">
+        <v>1.31</v>
+      </c>
+      <c r="U139">
+        <v>3.2</v>
+      </c>
+      <c r="V139">
+        <v>2.39</v>
+      </c>
+      <c r="W139">
+        <v>1.52</v>
+      </c>
+      <c r="X139">
+        <v>5.35</v>
+      </c>
+      <c r="Y139">
+        <v>1.12</v>
+      </c>
+      <c r="Z139">
+        <v>4.3</v>
+      </c>
+      <c r="AA139">
+        <v>3.7</v>
+      </c>
+      <c r="AB139">
+        <v>1.68</v>
+      </c>
+      <c r="AC139">
+        <v>1.01</v>
+      </c>
+      <c r="AD139">
+        <v>11</v>
+      </c>
+      <c r="AE139">
+        <v>1.21</v>
+      </c>
+      <c r="AF139">
+        <v>4</v>
+      </c>
+      <c r="AG139">
+        <v>1.66</v>
+      </c>
+      <c r="AH139">
+        <v>2.13</v>
+      </c>
+      <c r="AI139">
+        <v>1.66</v>
+      </c>
+      <c r="AJ139">
+        <v>2.1</v>
+      </c>
+      <c r="AK139">
+        <v>2.08</v>
+      </c>
+      <c r="AL139">
+        <v>1.22</v>
+      </c>
+      <c r="AM139">
+        <v>1.2</v>
+      </c>
+      <c r="AN139">
+        <v>0.63</v>
+      </c>
+      <c r="AO139">
+        <v>2.38</v>
+      </c>
+      <c r="AP139">
+        <v>0.67</v>
+      </c>
+      <c r="AQ139">
+        <v>2.22</v>
+      </c>
+      <c r="AR139">
+        <v>1.38</v>
+      </c>
+      <c r="AS139">
+        <v>1.65</v>
+      </c>
+      <c r="AT139">
+        <v>3.03</v>
+      </c>
+      <c r="AU139">
+        <v>2</v>
+      </c>
+      <c r="AV139">
+        <v>6</v>
+      </c>
+      <c r="AW139">
+        <v>4</v>
+      </c>
+      <c r="AX139">
+        <v>6</v>
+      </c>
+      <c r="AY139">
+        <v>7</v>
+      </c>
+      <c r="AZ139">
+        <v>14</v>
+      </c>
+      <c r="BA139">
+        <v>3</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>6</v>
+      </c>
+      <c r="BD139">
+        <v>0</v>
+      </c>
+      <c r="BE139">
+        <v>0</v>
+      </c>
+      <c r="BF139">
+        <v>0</v>
+      </c>
+      <c r="BG139">
+        <v>0</v>
+      </c>
+      <c r="BH139">
+        <v>0</v>
+      </c>
+      <c r="BI139">
+        <v>0</v>
+      </c>
+      <c r="BJ139">
+        <v>0</v>
+      </c>
+      <c r="BK139">
+        <v>0</v>
+      </c>
+      <c r="BL139">
+        <v>0</v>
+      </c>
+      <c r="BM139">
+        <v>0</v>
+      </c>
+      <c r="BN139">
+        <v>0</v>
+      </c>
+      <c r="BO139">
+        <v>0</v>
+      </c>
+      <c r="BP139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7484675</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F140">
+        <v>18</v>
+      </c>
+      <c r="G140" t="s">
+        <v>84</v>
+      </c>
+      <c r="H140" t="s">
+        <v>75</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>2</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>172</v>
+      </c>
+      <c r="P140" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q140">
+        <v>2.75</v>
+      </c>
+      <c r="R140">
+        <v>2.25</v>
+      </c>
+      <c r="S140">
+        <v>3.65</v>
+      </c>
+      <c r="T140">
+        <v>1.36</v>
+      </c>
+      <c r="U140">
+        <v>2.95</v>
+      </c>
+      <c r="V140">
+        <v>2.55</v>
+      </c>
+      <c r="W140">
+        <v>1.46</v>
+      </c>
+      <c r="X140">
+        <v>5.95</v>
+      </c>
+      <c r="Y140">
+        <v>1.1</v>
+      </c>
+      <c r="Z140">
+        <v>2.14</v>
+      </c>
+      <c r="AA140">
+        <v>3.3</v>
+      </c>
+      <c r="AB140">
+        <v>3</v>
+      </c>
+      <c r="AC140">
+        <v>1.02</v>
+      </c>
+      <c r="AD140">
+        <v>10</v>
+      </c>
+      <c r="AE140">
+        <v>1.24</v>
+      </c>
+      <c r="AF140">
+        <v>3.65</v>
+      </c>
+      <c r="AG140">
+        <v>1.77</v>
+      </c>
+      <c r="AH140">
+        <v>1.98</v>
+      </c>
+      <c r="AI140">
+        <v>1.63</v>
+      </c>
+      <c r="AJ140">
+        <v>2.14</v>
+      </c>
+      <c r="AK140">
+        <v>1.35</v>
+      </c>
+      <c r="AL140">
+        <v>1.27</v>
+      </c>
+      <c r="AM140">
+        <v>1.64</v>
+      </c>
+      <c r="AN140">
+        <v>2</v>
+      </c>
+      <c r="AO140">
+        <v>1.44</v>
+      </c>
+      <c r="AP140">
+        <v>2.11</v>
+      </c>
+      <c r="AQ140">
+        <v>1.3</v>
+      </c>
+      <c r="AR140">
+        <v>1.92</v>
+      </c>
+      <c r="AS140">
+        <v>1.23</v>
+      </c>
+      <c r="AT140">
+        <v>3.15</v>
+      </c>
+      <c r="AU140">
+        <v>5</v>
+      </c>
+      <c r="AV140">
+        <v>5</v>
+      </c>
+      <c r="AW140">
+        <v>9</v>
+      </c>
+      <c r="AX140">
+        <v>6</v>
+      </c>
+      <c r="AY140">
+        <v>17</v>
+      </c>
+      <c r="AZ140">
+        <v>12</v>
+      </c>
+      <c r="BA140">
+        <v>4</v>
+      </c>
+      <c r="BB140">
+        <v>4</v>
+      </c>
+      <c r="BC140">
+        <v>8</v>
+      </c>
+      <c r="BD140">
+        <v>1.9</v>
+      </c>
+      <c r="BE140">
+        <v>6.5</v>
+      </c>
+      <c r="BF140">
+        <v>2.35</v>
+      </c>
+      <c r="BG140">
+        <v>1.18</v>
+      </c>
+      <c r="BH140">
+        <v>3.86</v>
+      </c>
+      <c r="BI140">
+        <v>1.38</v>
+      </c>
+      <c r="BJ140">
+        <v>2.71</v>
+      </c>
+      <c r="BK140">
+        <v>1.69</v>
+      </c>
+      <c r="BL140">
+        <v>2.04</v>
+      </c>
+      <c r="BM140">
+        <v>2.11</v>
+      </c>
+      <c r="BN140">
+        <v>1.62</v>
+      </c>
+      <c r="BO140">
+        <v>2.74</v>
+      </c>
+      <c r="BP140">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7484676</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F141">
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>73</v>
+      </c>
+      <c r="H141" t="s">
+        <v>71</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+      <c r="L141">
+        <v>2</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>3</v>
+      </c>
+      <c r="O141" t="s">
+        <v>173</v>
+      </c>
+      <c r="P141" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q141">
+        <v>3.75</v>
+      </c>
+      <c r="R141">
+        <v>2.25</v>
+      </c>
+      <c r="S141">
+        <v>2.5</v>
+      </c>
+      <c r="T141">
+        <v>1.33</v>
+      </c>
+      <c r="U141">
+        <v>3.25</v>
+      </c>
+      <c r="V141">
+        <v>2.5</v>
+      </c>
+      <c r="W141">
+        <v>1.5</v>
+      </c>
+      <c r="X141">
+        <v>6</v>
+      </c>
+      <c r="Y141">
+        <v>1.11</v>
+      </c>
+      <c r="Z141">
+        <v>3.5</v>
+      </c>
+      <c r="AA141">
+        <v>3.8</v>
+      </c>
+      <c r="AB141">
+        <v>1.91</v>
+      </c>
+      <c r="AC141">
+        <v>1.04</v>
+      </c>
+      <c r="AD141">
+        <v>9</v>
+      </c>
+      <c r="AE141">
+        <v>1.24</v>
+      </c>
+      <c r="AF141">
+        <v>3.7</v>
+      </c>
+      <c r="AG141">
+        <v>1.67</v>
+      </c>
+      <c r="AH141">
+        <v>2.15</v>
+      </c>
+      <c r="AI141">
+        <v>1.62</v>
+      </c>
+      <c r="AJ141">
+        <v>2.2</v>
+      </c>
+      <c r="AK141">
+        <v>1.82</v>
+      </c>
+      <c r="AL141">
+        <v>1.27</v>
+      </c>
+      <c r="AM141">
+        <v>1.27</v>
+      </c>
+      <c r="AN141">
+        <v>0.33</v>
+      </c>
+      <c r="AO141">
+        <v>1.38</v>
+      </c>
+      <c r="AP141">
+        <v>0.6</v>
+      </c>
+      <c r="AQ141">
+        <v>1.22</v>
+      </c>
+      <c r="AR141">
+        <v>1.04</v>
+      </c>
+      <c r="AS141">
+        <v>1.44</v>
+      </c>
+      <c r="AT141">
+        <v>2.48</v>
+      </c>
+      <c r="AU141">
+        <v>4</v>
+      </c>
+      <c r="AV141">
+        <v>3</v>
+      </c>
+      <c r="AW141">
+        <v>1</v>
+      </c>
+      <c r="AX141">
+        <v>10</v>
+      </c>
+      <c r="AY141">
+        <v>5</v>
+      </c>
+      <c r="AZ141">
+        <v>17</v>
+      </c>
+      <c r="BA141">
+        <v>2</v>
+      </c>
+      <c r="BB141">
+        <v>6</v>
+      </c>
+      <c r="BC141">
+        <v>8</v>
+      </c>
+      <c r="BD141">
+        <v>3.52</v>
+      </c>
+      <c r="BE141">
+        <v>8.9</v>
+      </c>
+      <c r="BF141">
+        <v>1.41</v>
+      </c>
+      <c r="BG141">
+        <v>1.27</v>
+      </c>
+      <c r="BH141">
+        <v>3.14</v>
+      </c>
+      <c r="BI141">
+        <v>1.52</v>
+      </c>
+      <c r="BJ141">
+        <v>2.3</v>
+      </c>
+      <c r="BK141">
+        <v>1.92</v>
+      </c>
+      <c r="BL141">
+        <v>1.79</v>
+      </c>
+      <c r="BM141">
+        <v>2.5</v>
+      </c>
+      <c r="BN141">
+        <v>1.44</v>
+      </c>
+      <c r="BO141">
+        <v>3.34</v>
+      </c>
+      <c r="BP141">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:68">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>7484679</v>
+      </c>
+      <c r="C142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E142" s="2">
+        <v>45716.58333333334</v>
+      </c>
+      <c r="F142">
+        <v>18</v>
+      </c>
+      <c r="G142" t="s">
+        <v>85</v>
+      </c>
+      <c r="H142" t="s">
+        <v>72</v>
+      </c>
+      <c r="I142">
+        <v>3</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>3</v>
+      </c>
+      <c r="L142">
+        <v>3</v>
+      </c>
+      <c r="M142">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>4</v>
+      </c>
+      <c r="O142" t="s">
+        <v>174</v>
+      </c>
+      <c r="P142" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q142">
+        <v>2.44</v>
+      </c>
+      <c r="R142">
+        <v>2.19</v>
+      </c>
+      <c r="S142">
+        <v>4.6</v>
+      </c>
+      <c r="T142">
+        <v>1.4</v>
+      </c>
+      <c r="U142">
+        <v>2.75</v>
+      </c>
+      <c r="V142">
+        <v>2.75</v>
+      </c>
+      <c r="W142">
+        <v>1.4</v>
+      </c>
+      <c r="X142">
+        <v>5.95</v>
+      </c>
+      <c r="Y142">
+        <v>1.1</v>
+      </c>
+      <c r="Z142">
+        <v>1.84</v>
+      </c>
+      <c r="AA142">
+        <v>3.4</v>
+      </c>
+      <c r="AB142">
+        <v>3.8</v>
+      </c>
+      <c r="AC142">
+        <v>1.01</v>
+      </c>
+      <c r="AD142">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AE142">
+        <v>1.3</v>
+      </c>
+      <c r="AF142">
+        <v>3.2</v>
+      </c>
+      <c r="AG142">
+        <v>1.92</v>
+      </c>
+      <c r="AH142">
+        <v>1.82</v>
+      </c>
+      <c r="AI142">
+        <v>1.81</v>
+      </c>
+      <c r="AJ142">
+        <v>1.9</v>
+      </c>
+      <c r="AK142">
+        <v>1.24</v>
+      </c>
+      <c r="AL142">
+        <v>1.26</v>
+      </c>
+      <c r="AM142">
+        <v>1.87</v>
+      </c>
+      <c r="AN142">
+        <v>1.67</v>
+      </c>
+      <c r="AO142">
+        <v>0.5</v>
+      </c>
+      <c r="AP142">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142">
+        <v>0.44</v>
+      </c>
+      <c r="AR142">
+        <v>1.21</v>
+      </c>
+      <c r="AS142">
+        <v>1.06</v>
+      </c>
+      <c r="AT142">
+        <v>2.27</v>
+      </c>
+      <c r="AU142">
+        <v>5</v>
+      </c>
+      <c r="AV142">
+        <v>4</v>
+      </c>
+      <c r="AW142">
+        <v>5</v>
+      </c>
+      <c r="AX142">
+        <v>1</v>
+      </c>
+      <c r="AY142">
+        <v>12</v>
+      </c>
+      <c r="AZ142">
+        <v>5</v>
+      </c>
+      <c r="BA142">
+        <v>5</v>
+      </c>
+      <c r="BB142">
+        <v>5</v>
+      </c>
+      <c r="BC142">
+        <v>10</v>
+      </c>
+      <c r="BD142">
+        <v>1.54</v>
+      </c>
+      <c r="BE142">
+        <v>9</v>
+      </c>
+      <c r="BF142">
+        <v>2.9</v>
+      </c>
+      <c r="BG142">
+        <v>1.19</v>
+      </c>
+      <c r="BH142">
+        <v>3.92</v>
+      </c>
+      <c r="BI142">
+        <v>1.33</v>
+      </c>
+      <c r="BJ142">
+        <v>2.83</v>
+      </c>
+      <c r="BK142">
+        <v>1.61</v>
+      </c>
+      <c r="BL142">
+        <v>2.12</v>
+      </c>
+      <c r="BM142">
+        <v>2.03</v>
+      </c>
+      <c r="BN142">
+        <v>1.7</v>
+      </c>
+      <c r="BO142">
+        <v>2.64</v>
+      </c>
+      <c r="BP142">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:68">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>7484678</v>
+      </c>
+      <c r="C143" t="s">
+        <v>68</v>
+      </c>
+      <c r="D143" t="s">
+        <v>69</v>
+      </c>
+      <c r="E143" s="2">
+        <v>45716.6875</v>
+      </c>
+      <c r="F143">
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>81</v>
+      </c>
+      <c r="H143" t="s">
+        <v>77</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143">
+        <v>2</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>2</v>
+      </c>
+      <c r="O143" t="s">
+        <v>175</v>
+      </c>
+      <c r="P143" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q143">
+        <v>1.83</v>
+      </c>
+      <c r="R143">
+        <v>2.48</v>
+      </c>
+      <c r="S143">
+        <v>7.6</v>
+      </c>
+      <c r="T143">
+        <v>1.34</v>
+      </c>
+      <c r="U143">
+        <v>3.05</v>
+      </c>
+      <c r="V143">
+        <v>2.5</v>
+      </c>
+      <c r="W143">
+        <v>1.47</v>
+      </c>
+      <c r="X143">
+        <v>5.95</v>
+      </c>
+      <c r="Y143">
+        <v>1.1</v>
+      </c>
+      <c r="Z143">
+        <v>1.39</v>
+      </c>
+      <c r="AA143">
+        <v>4.2</v>
+      </c>
+      <c r="AB143">
+        <v>7</v>
+      </c>
+      <c r="AC143">
+        <v>1.01</v>
+      </c>
+      <c r="AD143">
+        <v>8.9</v>
+      </c>
+      <c r="AE143">
+        <v>1.26</v>
+      </c>
+      <c r="AF143">
+        <v>3.5</v>
+      </c>
+      <c r="AG143">
+        <v>1.81</v>
+      </c>
+      <c r="AH143">
+        <v>1.93</v>
+      </c>
+      <c r="AI143">
+        <v>2.07</v>
+      </c>
+      <c r="AJ143">
+        <v>1.67</v>
+      </c>
+      <c r="AK143">
+        <v>1.09</v>
+      </c>
+      <c r="AL143">
+        <v>1.17</v>
+      </c>
+      <c r="AM143">
+        <v>2.75</v>
+      </c>
+      <c r="AN143">
+        <v>2</v>
+      </c>
+      <c r="AO143">
+        <v>0.89</v>
+      </c>
+      <c r="AP143">
+        <v>2.11</v>
+      </c>
+      <c r="AQ143">
+        <v>0.8</v>
+      </c>
+      <c r="AR143">
+        <v>1.39</v>
+      </c>
+      <c r="AS143">
+        <v>1.26</v>
+      </c>
+      <c r="AT143">
+        <v>2.65</v>
+      </c>
+      <c r="AU143">
+        <v>6</v>
+      </c>
+      <c r="AV143">
+        <v>0</v>
+      </c>
+      <c r="AW143">
+        <v>7</v>
+      </c>
+      <c r="AX143">
+        <v>5</v>
+      </c>
+      <c r="AY143">
+        <v>13</v>
+      </c>
+      <c r="AZ143">
+        <v>6</v>
+      </c>
+      <c r="BA143">
+        <v>1</v>
+      </c>
+      <c r="BB143">
+        <v>1</v>
+      </c>
+      <c r="BC143">
+        <v>2</v>
+      </c>
+      <c r="BD143">
+        <v>1.26</v>
+      </c>
+      <c r="BE143">
+        <v>9.9</v>
+      </c>
+      <c r="BF143">
+        <v>4.75</v>
+      </c>
+      <c r="BG143">
+        <v>1.31</v>
+      </c>
+      <c r="BH143">
+        <v>2.92</v>
+      </c>
+      <c r="BI143">
+        <v>1.63</v>
+      </c>
+      <c r="BJ143">
+        <v>2.21</v>
+      </c>
+      <c r="BK143">
+        <v>2.05</v>
+      </c>
+      <c r="BL143">
+        <v>1.74</v>
+      </c>
+      <c r="BM143">
+        <v>2.64</v>
+      </c>
+      <c r="BN143">
+        <v>1.4</v>
+      </c>
+      <c r="BO143">
+        <v>3.58</v>
+      </c>
+      <c r="BP143">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="256">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>['1', '40']</t>
+  </si>
+  <si>
+    <t>['89']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1140,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP143"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1396,7 +1399,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1602,7 +1605,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1808,7 +1811,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2014,7 +2017,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2220,7 +2223,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -3250,7 +3253,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3456,7 +3459,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3534,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ12">
         <v>0.8</v>
@@ -4074,7 +4077,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4280,7 +4283,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4361,7 +4364,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4486,7 +4489,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4692,7 +4695,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4898,7 +4901,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5104,7 +5107,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5310,7 +5313,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5516,7 +5519,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5928,7 +5931,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6134,7 +6137,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6340,7 +6343,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6546,7 +6549,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6830,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ28">
         <v>1.9</v>
@@ -6958,7 +6961,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7039,7 +7042,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7164,7 +7167,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7370,7 +7373,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7988,7 +7991,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8069,7 +8072,7 @@
         <v>1</v>
       </c>
       <c r="AQ34">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR34">
         <v>1.46</v>
@@ -8194,7 +8197,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8400,7 +8403,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8606,7 +8609,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8812,7 +8815,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9224,7 +9227,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9430,7 +9433,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9636,7 +9639,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9714,7 +9717,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ42">
         <v>1.3</v>
@@ -10048,7 +10051,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10254,7 +10257,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10460,7 +10463,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10666,7 +10669,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10872,7 +10875,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11365,7 +11368,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ50">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR50">
         <v>1.26</v>
@@ -11490,7 +11493,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11696,7 +11699,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12108,7 +12111,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12520,7 +12523,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12726,7 +12729,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12804,7 +12807,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ57">
         <v>1.63</v>
@@ -12932,7 +12935,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13550,7 +13553,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13962,7 +13965,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14374,7 +14377,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14580,7 +14583,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14786,7 +14789,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14992,7 +14995,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15073,7 +15076,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ68">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR68">
         <v>1.14</v>
@@ -15610,7 +15613,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16434,7 +16437,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16515,7 +16518,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ75">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16640,7 +16643,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16846,7 +16849,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17052,7 +17055,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17258,7 +17261,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17336,7 +17339,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79">
         <v>1.22</v>
@@ -17670,7 +17673,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18494,7 +18497,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18700,7 +18703,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19112,7 +19115,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19318,7 +19321,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19524,7 +19527,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19605,7 +19608,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ90">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR90">
         <v>1.43</v>
@@ -19936,7 +19939,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20142,7 +20145,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20348,7 +20351,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20554,7 +20557,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20966,7 +20969,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21044,7 +21047,7 @@
         <v>2</v>
       </c>
       <c r="AP97">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ97">
         <v>2</v>
@@ -21378,7 +21381,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21584,7 +21587,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21790,7 +21793,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22202,7 +22205,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22408,7 +22411,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22820,7 +22823,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23026,7 +23029,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23232,7 +23235,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23438,7 +23441,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23519,7 +23522,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR109">
         <v>1.43</v>
@@ -23928,7 +23931,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ111">
         <v>0.75</v>
@@ -24880,7 +24883,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25498,7 +25501,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26116,7 +26119,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26528,7 +26531,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26734,7 +26737,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26940,7 +26943,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27018,7 +27021,7 @@
         <v>2.29</v>
       </c>
       <c r="AP126">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ126">
         <v>2.22</v>
@@ -27146,7 +27149,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27352,7 +27355,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27433,7 +27436,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ128">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -27558,7 +27561,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27764,7 +27767,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28176,7 +28179,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28382,7 +28385,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29206,7 +29209,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29618,7 +29621,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30030,7 +30033,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30236,7 +30239,7 @@
         <v>174</v>
       </c>
       <c r="P142" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q142">
         <v>2.44</v>
@@ -30599,6 +30602,212 @@
       </c>
       <c r="BP143">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:68">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>7484677</v>
+      </c>
+      <c r="C144" t="s">
+        <v>68</v>
+      </c>
+      <c r="D144" t="s">
+        <v>69</v>
+      </c>
+      <c r="E144" s="2">
+        <v>45717.4375</v>
+      </c>
+      <c r="F144">
+        <v>18</v>
+      </c>
+      <c r="G144" t="s">
+        <v>80</v>
+      </c>
+      <c r="H144" t="s">
+        <v>76</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+      <c r="M144">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>2</v>
+      </c>
+      <c r="O144" t="s">
+        <v>176</v>
+      </c>
+      <c r="P144" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q144">
+        <v>2.8</v>
+      </c>
+      <c r="R144">
+        <v>2.31</v>
+      </c>
+      <c r="S144">
+        <v>3.4</v>
+      </c>
+      <c r="T144">
+        <v>1.32</v>
+      </c>
+      <c r="U144">
+        <v>3.1</v>
+      </c>
+      <c r="V144">
+        <v>2.4</v>
+      </c>
+      <c r="W144">
+        <v>1.51</v>
+      </c>
+      <c r="X144">
+        <v>5.35</v>
+      </c>
+      <c r="Y144">
+        <v>1.12</v>
+      </c>
+      <c r="Z144">
+        <v>2.21</v>
+      </c>
+      <c r="AA144">
+        <v>3.45</v>
+      </c>
+      <c r="AB144">
+        <v>2.8</v>
+      </c>
+      <c r="AC144">
+        <v>1.01</v>
+      </c>
+      <c r="AD144">
+        <v>11</v>
+      </c>
+      <c r="AE144">
+        <v>1.21</v>
+      </c>
+      <c r="AF144">
+        <v>4</v>
+      </c>
+      <c r="AG144">
+        <v>1.66</v>
+      </c>
+      <c r="AH144">
+        <v>2.14</v>
+      </c>
+      <c r="AI144">
+        <v>1.56</v>
+      </c>
+      <c r="AJ144">
+        <v>2.28</v>
+      </c>
+      <c r="AK144">
+        <v>1.4</v>
+      </c>
+      <c r="AL144">
+        <v>1.26</v>
+      </c>
+      <c r="AM144">
+        <v>1.61</v>
+      </c>
+      <c r="AN144">
+        <v>1.5</v>
+      </c>
+      <c r="AO144">
+        <v>1.33</v>
+      </c>
+      <c r="AP144">
+        <v>1.44</v>
+      </c>
+      <c r="AQ144">
+        <v>1.3</v>
+      </c>
+      <c r="AR144">
+        <v>1.3</v>
+      </c>
+      <c r="AS144">
+        <v>1.61</v>
+      </c>
+      <c r="AT144">
+        <v>2.91</v>
+      </c>
+      <c r="AU144">
+        <v>7</v>
+      </c>
+      <c r="AV144">
+        <v>3</v>
+      </c>
+      <c r="AW144">
+        <v>11</v>
+      </c>
+      <c r="AX144">
+        <v>3</v>
+      </c>
+      <c r="AY144">
+        <v>21</v>
+      </c>
+      <c r="AZ144">
+        <v>7</v>
+      </c>
+      <c r="BA144">
+        <v>10</v>
+      </c>
+      <c r="BB144">
+        <v>2</v>
+      </c>
+      <c r="BC144">
+        <v>12</v>
+      </c>
+      <c r="BD144">
+        <v>0</v>
+      </c>
+      <c r="BE144">
+        <v>0</v>
+      </c>
+      <c r="BF144">
+        <v>0</v>
+      </c>
+      <c r="BG144">
+        <v>0</v>
+      </c>
+      <c r="BH144">
+        <v>0</v>
+      </c>
+      <c r="BI144">
+        <v>0</v>
+      </c>
+      <c r="BJ144">
+        <v>0</v>
+      </c>
+      <c r="BK144">
+        <v>1.64</v>
+      </c>
+      <c r="BL144">
+        <v>2.19</v>
+      </c>
+      <c r="BM144">
+        <v>2.03</v>
+      </c>
+      <c r="BN144">
+        <v>1.75</v>
+      </c>
+      <c r="BO144">
+        <v>0</v>
+      </c>
+      <c r="BP144">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="261">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -547,6 +547,18 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['69']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['45+2', '73', '90+2']</t>
+  </si>
+  <si>
+    <t>['50', '56', '66']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -781,7 +793,10 @@
     <t>['16']</t>
   </si>
   <si>
-    <t>['69']</t>
+    <t>['90+1']</t>
+  </si>
+  <si>
+    <t>['68']</t>
   </si>
 </sst>
 </file>
@@ -1143,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1399,7 +1414,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1605,7 +1620,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1683,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ3">
         <v>1.38</v>
@@ -1811,7 +1826,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1889,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ4">
         <v>2.44</v>
@@ -2017,7 +2032,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2098,7 +2113,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ5">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2223,7 +2238,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2304,7 +2319,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ6">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2507,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3253,7 +3268,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3459,7 +3474,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3746,7 +3761,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ13">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -3949,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ14">
         <v>1.3</v>
@@ -4077,7 +4092,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4283,7 +4298,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4489,7 +4504,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4695,7 +4710,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4901,7 +4916,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -4979,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR19">
         <v>0.97</v>
@@ -5107,7 +5122,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5185,7 +5200,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ20">
         <v>2</v>
@@ -5313,7 +5328,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5519,7 +5534,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5597,10 +5612,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ22">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR22">
         <v>1.76</v>
@@ -5806,7 +5821,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ23">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR23">
         <v>2.04</v>
@@ -5931,7 +5946,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6012,7 +6027,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ24">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR24">
         <v>1.2</v>
@@ -6137,7 +6152,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6215,7 +6230,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ25">
         <v>1.38</v>
@@ -6343,7 +6358,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6549,7 +6564,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6961,7 +6976,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7167,7 +7182,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7373,7 +7388,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7991,7 +8006,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8197,7 +8212,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8278,7 +8293,7 @@
         <v>2.44</v>
       </c>
       <c r="AQ35">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR35">
         <v>1.62</v>
@@ -8403,7 +8418,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8609,7 +8624,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8687,7 +8702,7 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
         <v>0.8</v>
@@ -8815,7 +8830,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9099,10 +9114,10 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ39">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR39">
         <v>0.82</v>
@@ -9227,7 +9242,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9433,7 +9448,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9511,10 +9526,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ41">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR41">
         <v>0.9</v>
@@ -9639,7 +9654,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10051,7 +10066,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10132,7 +10147,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ44">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR44">
         <v>1.33</v>
@@ -10257,7 +10272,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10335,7 +10350,7 @@
         <v>1.67</v>
       </c>
       <c r="AP45">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ45">
         <v>1.25</v>
@@ -10463,7 +10478,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10544,7 +10559,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR46">
         <v>1.15</v>
@@ -10669,7 +10684,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10747,7 +10762,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ47">
         <v>1.9</v>
@@ -10875,7 +10890,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -10956,7 +10971,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ48">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR48">
         <v>1.3</v>
@@ -11365,7 +11380,7 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
         <v>1.3</v>
@@ -11493,7 +11508,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11699,7 +11714,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11780,7 +11795,7 @@
         <v>1</v>
       </c>
       <c r="AQ52">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR52">
         <v>1.53</v>
@@ -12111,7 +12126,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12523,7 +12538,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12729,7 +12744,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12935,7 +12950,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13016,7 +13031,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ58">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR58">
         <v>1.23</v>
@@ -13219,7 +13234,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ59">
         <v>0.44</v>
@@ -13553,7 +13568,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13634,7 +13649,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ61">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR61">
         <v>1.31</v>
@@ -13837,7 +13852,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ62">
         <v>2.22</v>
@@ -13965,7 +13980,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14377,7 +14392,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14455,10 +14470,10 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR65">
         <v>1.19</v>
@@ -14583,7 +14598,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14661,7 +14676,7 @@
         <v>3</v>
       </c>
       <c r="AP66">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ66">
         <v>2.22</v>
@@ -14789,7 +14804,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14870,7 +14885,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ67">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>1.77</v>
@@ -14995,7 +15010,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15282,7 +15297,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ69">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR69">
         <v>1.58</v>
@@ -15613,7 +15628,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16103,7 +16118,7 @@
         <v>2</v>
       </c>
       <c r="AP73">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ73">
         <v>1.63</v>
@@ -16309,7 +16324,7 @@
         <v>3</v>
       </c>
       <c r="AP74">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ74">
         <v>2.44</v>
@@ -16437,7 +16452,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16643,7 +16658,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16849,7 +16864,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16927,7 +16942,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ77">
         <v>1.22</v>
@@ -17055,7 +17070,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17261,7 +17276,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17342,7 +17357,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ79">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR79">
         <v>0.98</v>
@@ -17673,7 +17688,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17960,7 +17975,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ82">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18497,7 +18512,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18578,7 +18593,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ85">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR85">
         <v>1.86</v>
@@ -18703,7 +18718,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19115,7 +19130,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19321,7 +19336,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19527,7 +19542,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19605,7 +19620,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ90">
         <v>1.3</v>
@@ -19939,7 +19954,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20017,7 +20032,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ92">
         <v>1.38</v>
@@ -20145,7 +20160,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20223,7 +20238,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ93">
         <v>1.63</v>
@@ -20351,7 +20366,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20557,7 +20572,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20638,7 +20653,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ95">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -20969,7 +20984,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21256,7 +21271,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ98">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR98">
         <v>1.62</v>
@@ -21381,7 +21396,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21459,10 +21474,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ99">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR99">
         <v>1.1</v>
@@ -21587,7 +21602,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21793,7 +21808,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22205,7 +22220,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22411,7 +22426,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22489,7 +22504,7 @@
         <v>2.4</v>
       </c>
       <c r="AP104">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ104">
         <v>2.22</v>
@@ -22698,7 +22713,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR105">
         <v>1.61</v>
@@ -22823,7 +22838,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23029,7 +23044,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23235,7 +23250,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23441,7 +23456,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23934,7 +23949,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ111">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR111">
         <v>1.21</v>
@@ -24343,7 +24358,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
         <v>0.44</v>
@@ -24755,7 +24770,7 @@
         <v>1.71</v>
       </c>
       <c r="AP115">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ115">
         <v>1.3</v>
@@ -24883,7 +24898,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -24961,10 +24976,10 @@
         <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ116">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR116">
         <v>1.11</v>
@@ -25167,10 +25182,10 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ117">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -25501,7 +25516,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25994,7 +26009,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ121">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR121">
         <v>1.76</v>
@@ -26119,7 +26134,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26531,7 +26546,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26609,7 +26624,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ124">
         <v>0.8</v>
@@ -26737,7 +26752,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26943,7 +26958,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27149,7 +27164,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27355,7 +27370,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27561,7 +27576,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27642,7 +27657,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ129">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR129">
         <v>1.89</v>
@@ -27767,7 +27782,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -27845,7 +27860,7 @@
         <v>1.88</v>
       </c>
       <c r="AP130">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AQ130">
         <v>1.9</v>
@@ -28051,7 +28066,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AQ131">
         <v>1.38</v>
@@ -28179,7 +28194,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28260,7 +28275,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ132">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR132">
         <v>1.23</v>
@@ -28385,7 +28400,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28672,7 +28687,7 @@
         <v>1</v>
       </c>
       <c r="AQ134">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR134">
         <v>1.56</v>
@@ -28878,7 +28893,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ135">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29209,7 +29224,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29287,7 +29302,7 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ137">
         <v>1.25</v>
@@ -29621,7 +29636,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30033,7 +30048,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30239,7 +30254,7 @@
         <v>174</v>
       </c>
       <c r="P142" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="Q142">
         <v>2.44</v>
@@ -30651,7 +30666,7 @@
         <v>176</v>
       </c>
       <c r="P144" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="Q144">
         <v>2.8</v>
@@ -30807,6 +30822,830 @@
         <v>0</v>
       </c>
       <c r="BP144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:68">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>7484684</v>
+      </c>
+      <c r="C145" t="s">
+        <v>68</v>
+      </c>
+      <c r="D145" t="s">
+        <v>69</v>
+      </c>
+      <c r="E145" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F145">
+        <v>19</v>
+      </c>
+      <c r="G145" t="s">
+        <v>75</v>
+      </c>
+      <c r="H145" t="s">
+        <v>73</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>1</v>
+      </c>
+      <c r="O145" t="s">
+        <v>177</v>
+      </c>
+      <c r="P145" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q145">
+        <v>2.19</v>
+      </c>
+      <c r="R145">
+        <v>2.15</v>
+      </c>
+      <c r="S145">
+        <v>5.3</v>
+      </c>
+      <c r="T145">
+        <v>1.35</v>
+      </c>
+      <c r="U145">
+        <v>2.9</v>
+      </c>
+      <c r="V145">
+        <v>2.7</v>
+      </c>
+      <c r="W145">
+        <v>1.4</v>
+      </c>
+      <c r="X145">
+        <v>6.5</v>
+      </c>
+      <c r="Y145">
+        <v>1.09</v>
+      </c>
+      <c r="Z145">
+        <v>1.55</v>
+      </c>
+      <c r="AA145">
+        <v>3.5</v>
+      </c>
+      <c r="AB145">
+        <v>5</v>
+      </c>
+      <c r="AC145">
+        <v>1.05</v>
+      </c>
+      <c r="AD145">
+        <v>7.8</v>
+      </c>
+      <c r="AE145">
+        <v>1.26</v>
+      </c>
+      <c r="AF145">
+        <v>3.5</v>
+      </c>
+      <c r="AG145">
+        <v>1.93</v>
+      </c>
+      <c r="AH145">
+        <v>1.85</v>
+      </c>
+      <c r="AI145">
+        <v>1.83</v>
+      </c>
+      <c r="AJ145">
+        <v>1.85</v>
+      </c>
+      <c r="AK145">
+        <v>1.13</v>
+      </c>
+      <c r="AL145">
+        <v>1.24</v>
+      </c>
+      <c r="AM145">
+        <v>2.25</v>
+      </c>
+      <c r="AN145">
+        <v>0.75</v>
+      </c>
+      <c r="AO145">
+        <v>0.75</v>
+      </c>
+      <c r="AP145">
+        <v>1</v>
+      </c>
+      <c r="AQ145">
+        <v>0.67</v>
+      </c>
+      <c r="AR145">
+        <v>1.22</v>
+      </c>
+      <c r="AS145">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT145">
+        <v>2.16</v>
+      </c>
+      <c r="AU145">
+        <v>5</v>
+      </c>
+      <c r="AV145">
+        <v>0</v>
+      </c>
+      <c r="AW145">
+        <v>6</v>
+      </c>
+      <c r="AX145">
+        <v>7</v>
+      </c>
+      <c r="AY145">
+        <v>12</v>
+      </c>
+      <c r="AZ145">
+        <v>9</v>
+      </c>
+      <c r="BA145">
+        <v>3</v>
+      </c>
+      <c r="BB145">
+        <v>5</v>
+      </c>
+      <c r="BC145">
+        <v>8</v>
+      </c>
+      <c r="BD145">
+        <v>0</v>
+      </c>
+      <c r="BE145">
+        <v>0</v>
+      </c>
+      <c r="BF145">
+        <v>0</v>
+      </c>
+      <c r="BG145">
+        <v>0</v>
+      </c>
+      <c r="BH145">
+        <v>0</v>
+      </c>
+      <c r="BI145">
+        <v>0</v>
+      </c>
+      <c r="BJ145">
+        <v>0</v>
+      </c>
+      <c r="BK145">
+        <v>0</v>
+      </c>
+      <c r="BL145">
+        <v>0</v>
+      </c>
+      <c r="BM145">
+        <v>0</v>
+      </c>
+      <c r="BN145">
+        <v>0</v>
+      </c>
+      <c r="BO145">
+        <v>0</v>
+      </c>
+      <c r="BP145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:68">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>7484682</v>
+      </c>
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" t="s">
+        <v>69</v>
+      </c>
+      <c r="E146" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F146">
+        <v>19</v>
+      </c>
+      <c r="G146" t="s">
+        <v>72</v>
+      </c>
+      <c r="H146" t="s">
+        <v>79</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="M146">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>2</v>
+      </c>
+      <c r="O146" t="s">
+        <v>178</v>
+      </c>
+      <c r="P146" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q146">
+        <v>2.5</v>
+      </c>
+      <c r="R146">
+        <v>2.15</v>
+      </c>
+      <c r="S146">
+        <v>4</v>
+      </c>
+      <c r="T146">
+        <v>1.36</v>
+      </c>
+      <c r="U146">
+        <v>3.1</v>
+      </c>
+      <c r="V146">
+        <v>2.71</v>
+      </c>
+      <c r="W146">
+        <v>1.42</v>
+      </c>
+      <c r="X146">
+        <v>7</v>
+      </c>
+      <c r="Y146">
+        <v>1.09</v>
+      </c>
+      <c r="Z146">
+        <v>1.93</v>
+      </c>
+      <c r="AA146">
+        <v>3.25</v>
+      </c>
+      <c r="AB146">
+        <v>3.5</v>
+      </c>
+      <c r="AC146">
+        <v>1.05</v>
+      </c>
+      <c r="AD146">
+        <v>8.5</v>
+      </c>
+      <c r="AE146">
+        <v>1.22</v>
+      </c>
+      <c r="AF146">
+        <v>3.7</v>
+      </c>
+      <c r="AG146">
+        <v>1.85</v>
+      </c>
+      <c r="AH146">
+        <v>1.93</v>
+      </c>
+      <c r="AI146">
+        <v>1.67</v>
+      </c>
+      <c r="AJ146">
+        <v>2</v>
+      </c>
+      <c r="AK146">
+        <v>1.3</v>
+      </c>
+      <c r="AL146">
+        <v>1.27</v>
+      </c>
+      <c r="AM146">
+        <v>1.88</v>
+      </c>
+      <c r="AN146">
+        <v>0.89</v>
+      </c>
+      <c r="AO146">
+        <v>0.44</v>
+      </c>
+      <c r="AP146">
+        <v>0.9</v>
+      </c>
+      <c r="AQ146">
+        <v>0.5</v>
+      </c>
+      <c r="AR146">
+        <v>1.16</v>
+      </c>
+      <c r="AS146">
+        <v>1.32</v>
+      </c>
+      <c r="AT146">
+        <v>2.48</v>
+      </c>
+      <c r="AU146">
+        <v>3</v>
+      </c>
+      <c r="AV146">
+        <v>4</v>
+      </c>
+      <c r="AW146">
+        <v>8</v>
+      </c>
+      <c r="AX146">
+        <v>6</v>
+      </c>
+      <c r="AY146">
+        <v>15</v>
+      </c>
+      <c r="AZ146">
+        <v>11</v>
+      </c>
+      <c r="BA146">
+        <v>5</v>
+      </c>
+      <c r="BB146">
+        <v>4</v>
+      </c>
+      <c r="BC146">
+        <v>9</v>
+      </c>
+      <c r="BD146">
+        <v>0</v>
+      </c>
+      <c r="BE146">
+        <v>0</v>
+      </c>
+      <c r="BF146">
+        <v>0</v>
+      </c>
+      <c r="BG146">
+        <v>0</v>
+      </c>
+      <c r="BH146">
+        <v>0</v>
+      </c>
+      <c r="BI146">
+        <v>0</v>
+      </c>
+      <c r="BJ146">
+        <v>0</v>
+      </c>
+      <c r="BK146">
+        <v>2.1</v>
+      </c>
+      <c r="BL146">
+        <v>0</v>
+      </c>
+      <c r="BM146">
+        <v>0</v>
+      </c>
+      <c r="BN146">
+        <v>0</v>
+      </c>
+      <c r="BO146">
+        <v>0</v>
+      </c>
+      <c r="BP146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:68">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>7484685</v>
+      </c>
+      <c r="C147" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F147">
+        <v>19</v>
+      </c>
+      <c r="G147" t="s">
+        <v>82</v>
+      </c>
+      <c r="H147" t="s">
+        <v>80</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+      <c r="L147">
+        <v>3</v>
+      </c>
+      <c r="M147">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>4</v>
+      </c>
+      <c r="O147" t="s">
+        <v>179</v>
+      </c>
+      <c r="P147" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q147">
+        <v>2.36</v>
+      </c>
+      <c r="R147">
+        <v>2.2</v>
+      </c>
+      <c r="S147">
+        <v>4.33</v>
+      </c>
+      <c r="T147">
+        <v>1.33</v>
+      </c>
+      <c r="U147">
+        <v>3</v>
+      </c>
+      <c r="V147">
+        <v>2.65</v>
+      </c>
+      <c r="W147">
+        <v>1.42</v>
+      </c>
+      <c r="X147">
+        <v>5.8</v>
+      </c>
+      <c r="Y147">
+        <v>1.1</v>
+      </c>
+      <c r="Z147">
+        <v>1.8</v>
+      </c>
+      <c r="AA147">
+        <v>3.4</v>
+      </c>
+      <c r="AB147">
+        <v>4</v>
+      </c>
+      <c r="AC147">
+        <v>1.05</v>
+      </c>
+      <c r="AD147">
+        <v>8.5</v>
+      </c>
+      <c r="AE147">
+        <v>1.28</v>
+      </c>
+      <c r="AF147">
+        <v>3.45</v>
+      </c>
+      <c r="AG147">
+        <v>1.9</v>
+      </c>
+      <c r="AH147">
+        <v>1.9</v>
+      </c>
+      <c r="AI147">
+        <v>1.73</v>
+      </c>
+      <c r="AJ147">
+        <v>1.93</v>
+      </c>
+      <c r="AK147">
+        <v>1.26</v>
+      </c>
+      <c r="AL147">
+        <v>1.26</v>
+      </c>
+      <c r="AM147">
+        <v>2</v>
+      </c>
+      <c r="AN147">
+        <v>1.25</v>
+      </c>
+      <c r="AO147">
+        <v>1.56</v>
+      </c>
+      <c r="AP147">
+        <v>1.44</v>
+      </c>
+      <c r="AQ147">
+        <v>1.4</v>
+      </c>
+      <c r="AR147">
+        <v>1.42</v>
+      </c>
+      <c r="AS147">
+        <v>1.16</v>
+      </c>
+      <c r="AT147">
+        <v>2.58</v>
+      </c>
+      <c r="AU147">
+        <v>8</v>
+      </c>
+      <c r="AV147">
+        <v>3</v>
+      </c>
+      <c r="AW147">
+        <v>8</v>
+      </c>
+      <c r="AX147">
+        <v>3</v>
+      </c>
+      <c r="AY147">
+        <v>20</v>
+      </c>
+      <c r="AZ147">
+        <v>6</v>
+      </c>
+      <c r="BA147">
+        <v>10</v>
+      </c>
+      <c r="BB147">
+        <v>5</v>
+      </c>
+      <c r="BC147">
+        <v>15</v>
+      </c>
+      <c r="BD147">
+        <v>0</v>
+      </c>
+      <c r="BE147">
+        <v>0</v>
+      </c>
+      <c r="BF147">
+        <v>0</v>
+      </c>
+      <c r="BG147">
+        <v>0</v>
+      </c>
+      <c r="BH147">
+        <v>0</v>
+      </c>
+      <c r="BI147">
+        <v>0</v>
+      </c>
+      <c r="BJ147">
+        <v>0</v>
+      </c>
+      <c r="BK147">
+        <v>2.2</v>
+      </c>
+      <c r="BL147">
+        <v>0</v>
+      </c>
+      <c r="BM147">
+        <v>0</v>
+      </c>
+      <c r="BN147">
+        <v>0</v>
+      </c>
+      <c r="BO147">
+        <v>0</v>
+      </c>
+      <c r="BP147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:68">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>7484681</v>
+      </c>
+      <c r="C148" t="s">
+        <v>68</v>
+      </c>
+      <c r="D148" t="s">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>45723.58333333334</v>
+      </c>
+      <c r="F148">
+        <v>19</v>
+      </c>
+      <c r="G148" t="s">
+        <v>71</v>
+      </c>
+      <c r="H148" t="s">
+        <v>84</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>3</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>3</v>
+      </c>
+      <c r="O148" t="s">
+        <v>180</v>
+      </c>
+      <c r="P148" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q148">
+        <v>2.7</v>
+      </c>
+      <c r="R148">
+        <v>2.2</v>
+      </c>
+      <c r="S148">
+        <v>3.3</v>
+      </c>
+      <c r="T148">
+        <v>1.32</v>
+      </c>
+      <c r="U148">
+        <v>3.24</v>
+      </c>
+      <c r="V148">
+        <v>2.5</v>
+      </c>
+      <c r="W148">
+        <v>1.45</v>
+      </c>
+      <c r="X148">
+        <v>5.3</v>
+      </c>
+      <c r="Y148">
+        <v>1.12</v>
+      </c>
+      <c r="Z148">
+        <v>2.3</v>
+      </c>
+      <c r="AA148">
+        <v>3.3</v>
+      </c>
+      <c r="AB148">
+        <v>2.74</v>
+      </c>
+      <c r="AC148">
+        <v>1.01</v>
+      </c>
+      <c r="AD148">
+        <v>8</v>
+      </c>
+      <c r="AE148">
+        <v>1.2</v>
+      </c>
+      <c r="AF148">
+        <v>3.8</v>
+      </c>
+      <c r="AG148">
+        <v>1.77</v>
+      </c>
+      <c r="AH148">
+        <v>2</v>
+      </c>
+      <c r="AI148">
+        <v>1.55</v>
+      </c>
+      <c r="AJ148">
+        <v>2.25</v>
+      </c>
+      <c r="AK148">
+        <v>1.3</v>
+      </c>
+      <c r="AL148">
+        <v>1.28</v>
+      </c>
+      <c r="AM148">
+        <v>1.57</v>
+      </c>
+      <c r="AN148">
+        <v>1</v>
+      </c>
+      <c r="AO148">
+        <v>1.22</v>
+      </c>
+      <c r="AP148">
+        <v>1.2</v>
+      </c>
+      <c r="AQ148">
+        <v>1.1</v>
+      </c>
+      <c r="AR148">
+        <v>1.35</v>
+      </c>
+      <c r="AS148">
+        <v>1.58</v>
+      </c>
+      <c r="AT148">
+        <v>2.93</v>
+      </c>
+      <c r="AU148">
+        <v>9</v>
+      </c>
+      <c r="AV148">
+        <v>2</v>
+      </c>
+      <c r="AW148">
+        <v>12</v>
+      </c>
+      <c r="AX148">
+        <v>6</v>
+      </c>
+      <c r="AY148">
+        <v>27</v>
+      </c>
+      <c r="AZ148">
+        <v>10</v>
+      </c>
+      <c r="BA148">
+        <v>9</v>
+      </c>
+      <c r="BB148">
+        <v>2</v>
+      </c>
+      <c r="BC148">
+        <v>11</v>
+      </c>
+      <c r="BD148">
+        <v>0</v>
+      </c>
+      <c r="BE148">
+        <v>0</v>
+      </c>
+      <c r="BF148">
+        <v>0</v>
+      </c>
+      <c r="BG148">
+        <v>0</v>
+      </c>
+      <c r="BH148">
+        <v>0</v>
+      </c>
+      <c r="BI148">
+        <v>0</v>
+      </c>
+      <c r="BJ148">
+        <v>0</v>
+      </c>
+      <c r="BK148">
+        <v>2.38</v>
+      </c>
+      <c r="BL148">
+        <v>0</v>
+      </c>
+      <c r="BM148">
+        <v>0</v>
+      </c>
+      <c r="BN148">
+        <v>0</v>
+      </c>
+      <c r="BO148">
+        <v>0</v>
+      </c>
+      <c r="BP148">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="264">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -559,6 +559,12 @@
     <t>['50', '56', '66']</t>
   </si>
   <si>
+    <t>['41', '73', '86']</t>
+  </si>
+  <si>
+    <t>['29', '59']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -797,6 +803,9 @@
   </si>
   <si>
     <t>['68']</t>
+  </si>
+  <si>
+    <t>['83', '89']</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1414,7 +1423,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1620,7 +1629,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1701,7 +1710,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ3">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1826,7 +1835,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2032,7 +2041,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2238,7 +2247,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2316,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
         <v>1.4</v>
@@ -2728,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3268,7 +3277,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3474,7 +3483,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4092,7 +4101,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4298,7 +4307,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4504,7 +4513,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4710,7 +4719,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4791,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="AQ18">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR18">
         <v>1.17</v>
@@ -4916,7 +4925,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5122,7 +5131,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5328,7 +5337,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5534,7 +5543,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5818,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ23">
         <v>0.5</v>
@@ -5946,7 +5955,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6024,7 +6033,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ24">
         <v>1.4</v>
@@ -6152,7 +6161,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6233,7 +6242,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ25">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR25">
         <v>0.84</v>
@@ -6358,7 +6367,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6564,7 +6573,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6976,7 +6985,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7182,7 +7191,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7388,7 +7397,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8006,7 +8015,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8212,7 +8221,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8290,7 +8299,7 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ35">
         <v>1.1</v>
@@ -8418,7 +8427,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8499,7 +8508,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ36">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR36">
         <v>1.65</v>
@@ -8624,7 +8633,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8830,7 +8839,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9242,7 +9251,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9448,7 +9457,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9654,7 +9663,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10066,7 +10075,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10272,7 +10281,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10353,7 +10362,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ45">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR45">
         <v>0.9399999999999999</v>
@@ -10478,7 +10487,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10684,7 +10693,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10890,7 +10899,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11174,7 +11183,7 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ49">
         <v>0.8</v>
@@ -11508,7 +11517,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11714,7 +11723,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11998,7 +12007,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ53">
         <v>0.44</v>
@@ -12126,7 +12135,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12410,7 +12419,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ55">
         <v>1.3</v>
@@ -12538,7 +12547,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12619,7 +12628,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ56">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR56">
         <v>1.26</v>
@@ -12744,7 +12753,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12950,7 +12959,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13440,7 +13449,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ60">
         <v>1.22</v>
@@ -13568,7 +13577,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13980,7 +13989,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14267,7 +14276,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ64">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR64">
         <v>1.93</v>
@@ -14392,7 +14401,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14598,7 +14607,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14804,7 +14813,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15010,7 +15019,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15628,7 +15637,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16452,7 +16461,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16658,7 +16667,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16739,7 +16748,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR76">
         <v>1.4</v>
@@ -16864,7 +16873,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17070,7 +17079,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17276,7 +17285,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17560,10 +17569,10 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ80">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR80">
         <v>1.44</v>
@@ -17688,7 +17697,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18512,7 +18521,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18718,7 +18727,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18796,7 +18805,7 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ86">
         <v>2.22</v>
@@ -19130,7 +19139,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19336,7 +19345,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19542,7 +19551,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19826,7 +19835,7 @@
         <v>2.6</v>
       </c>
       <c r="AP91">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ91">
         <v>2.44</v>
@@ -19954,7 +19963,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20035,7 +20044,7 @@
         <v>1</v>
       </c>
       <c r="AQ92">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR92">
         <v>1.32</v>
@@ -20160,7 +20169,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20366,7 +20375,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20447,7 +20456,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ94">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR94">
         <v>1.93</v>
@@ -20572,7 +20581,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20984,7 +20993,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21396,7 +21405,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21602,7 +21611,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21808,7 +21817,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22220,7 +22229,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22298,7 +22307,7 @@
         <v>2.17</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ103">
         <v>2.44</v>
@@ -22426,7 +22435,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22838,7 +22847,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23044,7 +23053,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23250,7 +23259,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23456,7 +23465,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23743,7 +23752,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ110">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR110">
         <v>1.28</v>
@@ -24152,7 +24161,7 @@
         <v>2.17</v>
       </c>
       <c r="AP112">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ112">
         <v>1.63</v>
@@ -24898,7 +24907,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25516,7 +25525,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25597,7 +25606,7 @@
         <v>1</v>
       </c>
       <c r="AQ119">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR119">
         <v>1.62</v>
@@ -25800,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>0.8</v>
@@ -26134,7 +26143,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26546,7 +26555,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26752,7 +26761,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26958,7 +26967,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27164,7 +27173,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27370,7 +27379,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27576,7 +27585,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27782,7 +27791,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28069,7 +28078,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ131">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28194,7 +28203,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28400,7 +28409,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28478,7 +28487,7 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AQ133">
         <v>2</v>
@@ -28890,7 +28899,7 @@
         <v>1.38</v>
       </c>
       <c r="AP135">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ135">
         <v>1.1</v>
@@ -29224,7 +29233,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29305,7 +29314,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ137">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AR137">
         <v>1.29</v>
@@ -29636,7 +29645,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30048,7 +30057,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -31078,7 +31087,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31284,7 +31293,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31646,6 +31655,418 @@
         <v>0</v>
       </c>
       <c r="BP148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:68">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>7484686</v>
+      </c>
+      <c r="C149" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="2">
+        <v>45723.6875</v>
+      </c>
+      <c r="F149">
+        <v>19</v>
+      </c>
+      <c r="G149" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" t="s">
+        <v>83</v>
+      </c>
+      <c r="I149">
+        <v>1</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+      <c r="L149">
+        <v>3</v>
+      </c>
+      <c r="M149">
+        <v>2</v>
+      </c>
+      <c r="N149">
+        <v>5</v>
+      </c>
+      <c r="O149" t="s">
+        <v>181</v>
+      </c>
+      <c r="P149" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q149">
+        <v>2.1</v>
+      </c>
+      <c r="R149">
+        <v>2.15</v>
+      </c>
+      <c r="S149">
+        <v>5.3</v>
+      </c>
+      <c r="T149">
+        <v>1.33</v>
+      </c>
+      <c r="U149">
+        <v>3</v>
+      </c>
+      <c r="V149">
+        <v>2.6</v>
+      </c>
+      <c r="W149">
+        <v>1.42</v>
+      </c>
+      <c r="X149">
+        <v>6</v>
+      </c>
+      <c r="Y149">
+        <v>1.05</v>
+      </c>
+      <c r="Z149">
+        <v>1.6</v>
+      </c>
+      <c r="AA149">
+        <v>3.83</v>
+      </c>
+      <c r="AB149">
+        <v>4.8</v>
+      </c>
+      <c r="AC149">
+        <v>1.04</v>
+      </c>
+      <c r="AD149">
+        <v>8.5</v>
+      </c>
+      <c r="AE149">
+        <v>1.22</v>
+      </c>
+      <c r="AF149">
+        <v>3.7</v>
+      </c>
+      <c r="AG149">
+        <v>1.8</v>
+      </c>
+      <c r="AH149">
+        <v>2</v>
+      </c>
+      <c r="AI149">
+        <v>1.8</v>
+      </c>
+      <c r="AJ149">
+        <v>1.85</v>
+      </c>
+      <c r="AK149">
+        <v>1.12</v>
+      </c>
+      <c r="AL149">
+        <v>1.23</v>
+      </c>
+      <c r="AM149">
+        <v>2.2</v>
+      </c>
+      <c r="AN149">
+        <v>2.44</v>
+      </c>
+      <c r="AO149">
+        <v>1.25</v>
+      </c>
+      <c r="AP149">
+        <v>2.5</v>
+      </c>
+      <c r="AQ149">
+        <v>1.11</v>
+      </c>
+      <c r="AR149">
+        <v>1.38</v>
+      </c>
+      <c r="AS149">
+        <v>1.3</v>
+      </c>
+      <c r="AT149">
+        <v>2.68</v>
+      </c>
+      <c r="AU149">
+        <v>6</v>
+      </c>
+      <c r="AV149">
+        <v>4</v>
+      </c>
+      <c r="AW149">
+        <v>12</v>
+      </c>
+      <c r="AX149">
+        <v>3</v>
+      </c>
+      <c r="AY149">
+        <v>23</v>
+      </c>
+      <c r="AZ149">
+        <v>8</v>
+      </c>
+      <c r="BA149">
+        <v>3</v>
+      </c>
+      <c r="BB149">
+        <v>3</v>
+      </c>
+      <c r="BC149">
+        <v>6</v>
+      </c>
+      <c r="BD149">
+        <v>0</v>
+      </c>
+      <c r="BE149">
+        <v>0</v>
+      </c>
+      <c r="BF149">
+        <v>0</v>
+      </c>
+      <c r="BG149">
+        <v>0</v>
+      </c>
+      <c r="BH149">
+        <v>0</v>
+      </c>
+      <c r="BI149">
+        <v>0</v>
+      </c>
+      <c r="BJ149">
+        <v>0</v>
+      </c>
+      <c r="BK149">
+        <v>0</v>
+      </c>
+      <c r="BL149">
+        <v>0</v>
+      </c>
+      <c r="BM149">
+        <v>0</v>
+      </c>
+      <c r="BN149">
+        <v>0</v>
+      </c>
+      <c r="BO149">
+        <v>0</v>
+      </c>
+      <c r="BP149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:68">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>7484687</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="2">
+        <v>45724.66666666666</v>
+      </c>
+      <c r="F150">
+        <v>19</v>
+      </c>
+      <c r="G150" t="s">
+        <v>76</v>
+      </c>
+      <c r="H150" t="s">
+        <v>78</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>2</v>
+      </c>
+      <c r="M150">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>3</v>
+      </c>
+      <c r="O150" t="s">
+        <v>182</v>
+      </c>
+      <c r="P150" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q150">
+        <v>2.63</v>
+      </c>
+      <c r="R150">
+        <v>2.3</v>
+      </c>
+      <c r="S150">
+        <v>3.4</v>
+      </c>
+      <c r="T150">
+        <v>1.3</v>
+      </c>
+      <c r="U150">
+        <v>3.4</v>
+      </c>
+      <c r="V150">
+        <v>2.5</v>
+      </c>
+      <c r="W150">
+        <v>1.5</v>
+      </c>
+      <c r="X150">
+        <v>5.5</v>
+      </c>
+      <c r="Y150">
+        <v>1.13</v>
+      </c>
+      <c r="Z150">
+        <v>2.18</v>
+      </c>
+      <c r="AA150">
+        <v>3.6</v>
+      </c>
+      <c r="AB150">
+        <v>3.03</v>
+      </c>
+      <c r="AC150">
+        <v>1.01</v>
+      </c>
+      <c r="AD150">
+        <v>13</v>
+      </c>
+      <c r="AE150">
+        <v>1.15</v>
+      </c>
+      <c r="AF150">
+        <v>4.2</v>
+      </c>
+      <c r="AG150">
+        <v>1.62</v>
+      </c>
+      <c r="AH150">
+        <v>2.25</v>
+      </c>
+      <c r="AI150">
+        <v>1.57</v>
+      </c>
+      <c r="AJ150">
+        <v>2.25</v>
+      </c>
+      <c r="AK150">
+        <v>1.36</v>
+      </c>
+      <c r="AL150">
+        <v>1.26</v>
+      </c>
+      <c r="AM150">
+        <v>1.67</v>
+      </c>
+      <c r="AN150">
+        <v>1.5</v>
+      </c>
+      <c r="AO150">
+        <v>1.38</v>
+      </c>
+      <c r="AP150">
+        <v>1.67</v>
+      </c>
+      <c r="AQ150">
+        <v>1.22</v>
+      </c>
+      <c r="AR150">
+        <v>1.28</v>
+      </c>
+      <c r="AS150">
+        <v>1.4</v>
+      </c>
+      <c r="AT150">
+        <v>2.68</v>
+      </c>
+      <c r="AU150">
+        <v>3</v>
+      </c>
+      <c r="AV150">
+        <v>6</v>
+      </c>
+      <c r="AW150">
+        <v>7</v>
+      </c>
+      <c r="AX150">
+        <v>5</v>
+      </c>
+      <c r="AY150">
+        <v>11</v>
+      </c>
+      <c r="AZ150">
+        <v>13</v>
+      </c>
+      <c r="BA150">
+        <v>4</v>
+      </c>
+      <c r="BB150">
+        <v>6</v>
+      </c>
+      <c r="BC150">
+        <v>10</v>
+      </c>
+      <c r="BD150">
+        <v>0</v>
+      </c>
+      <c r="BE150">
+        <v>0</v>
+      </c>
+      <c r="BF150">
+        <v>0</v>
+      </c>
+      <c r="BG150">
+        <v>0</v>
+      </c>
+      <c r="BH150">
+        <v>0</v>
+      </c>
+      <c r="BI150">
+        <v>0</v>
+      </c>
+      <c r="BJ150">
+        <v>0</v>
+      </c>
+      <c r="BK150">
+        <v>2.38</v>
+      </c>
+      <c r="BL150">
+        <v>0</v>
+      </c>
+      <c r="BM150">
+        <v>0</v>
+      </c>
+      <c r="BN150">
+        <v>0</v>
+      </c>
+      <c r="BO150">
+        <v>0</v>
+      </c>
+      <c r="BP150">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="266">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -565,6 +565,9 @@
     <t>['29', '59']</t>
   </si>
   <si>
+    <t>['14', '90+4']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -806,6 +809,9 @@
   </si>
   <si>
     <t>['83', '89']</t>
+  </si>
+  <si>
+    <t>['29']</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP150"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1423,7 +1429,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1504,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="AQ2">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1629,7 +1635,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1835,7 +1841,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2041,7 +2047,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2247,7 +2253,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2943,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
         <v>1.9</v>
@@ -3277,7 +3283,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3483,7 +3489,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4101,7 +4107,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4307,7 +4313,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4513,7 +4519,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4719,7 +4725,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4925,7 +4931,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5131,7 +5137,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5212,7 +5218,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ20">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR20">
         <v>0.71</v>
@@ -5337,7 +5343,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5415,7 +5421,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ21">
         <v>2.44</v>
@@ -5543,7 +5549,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5955,7 +5961,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6161,7 +6167,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6367,7 +6373,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6573,7 +6579,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6985,7 +6991,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7191,7 +7197,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7397,7 +7403,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8015,7 +8021,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8221,7 +8227,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8427,7 +8433,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8633,7 +8639,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8839,7 +8845,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9251,7 +9257,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9457,7 +9463,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9663,7 +9669,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10075,7 +10081,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10281,7 +10287,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10487,7 +10493,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10693,7 +10699,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10899,7 +10905,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11517,7 +11523,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11723,7 +11729,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12135,7 +12141,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12216,7 +12222,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ54">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12547,7 +12553,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12753,7 +12759,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12959,7 +12965,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13577,7 +13583,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13655,7 +13661,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ61">
         <v>0.5</v>
@@ -13989,7 +13995,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14070,7 +14076,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ63">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14401,7 +14407,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14607,7 +14613,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14813,7 +14819,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15019,7 +15025,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15637,7 +15643,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16461,7 +16467,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16667,7 +16673,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16745,7 +16751,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ76">
         <v>1.11</v>
@@ -16873,7 +16879,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17079,7 +17085,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17160,7 +17166,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ78">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR78">
         <v>1.34</v>
@@ -17285,7 +17291,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17697,7 +17703,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18521,7 +18527,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18727,7 +18733,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19139,7 +19145,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19345,7 +19351,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19423,7 +19429,7 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ89">
         <v>1.63</v>
@@ -19551,7 +19557,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19963,7 +19969,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20169,7 +20175,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20375,7 +20381,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20581,7 +20587,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20865,7 +20871,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ96">
         <v>0.44</v>
@@ -20993,7 +20999,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21074,7 +21080,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ97">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR97">
         <v>1.11</v>
@@ -21405,7 +21411,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21611,7 +21617,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21817,7 +21823,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22229,7 +22235,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22435,7 +22441,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22847,7 +22853,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22925,7 +22931,7 @@
         <v>0.83</v>
       </c>
       <c r="AP106">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ106">
         <v>1.22</v>
@@ -23053,7 +23059,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23259,7 +23265,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23340,7 +23346,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ108">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR108">
         <v>1.76</v>
@@ -23465,7 +23471,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24907,7 +24913,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25525,7 +25531,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26143,7 +26149,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26555,7 +26561,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26761,7 +26767,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26967,7 +26973,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27173,7 +27179,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27379,7 +27385,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27585,7 +27591,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27791,7 +27797,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28203,7 +28209,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28281,7 +28287,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AQ132">
         <v>1.4</v>
@@ -28409,7 +28415,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28490,7 +28496,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ133">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AR133">
         <v>1.4</v>
@@ -29233,7 +29239,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29645,7 +29651,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30057,7 +30063,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -31087,7 +31093,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31293,7 +31299,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31705,7 +31711,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31911,7 +31917,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32067,6 +32073,212 @@
         <v>0</v>
       </c>
       <c r="BP150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:68">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>7484683</v>
+      </c>
+      <c r="C151" t="s">
+        <v>68</v>
+      </c>
+      <c r="D151" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="2">
+        <v>45725.27083333334</v>
+      </c>
+      <c r="F151">
+        <v>19</v>
+      </c>
+      <c r="G151" t="s">
+        <v>77</v>
+      </c>
+      <c r="H151" t="s">
+        <v>85</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+      <c r="K151">
+        <v>2</v>
+      </c>
+      <c r="L151">
+        <v>2</v>
+      </c>
+      <c r="M151">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>3</v>
+      </c>
+      <c r="O151" t="s">
+        <v>183</v>
+      </c>
+      <c r="P151" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q151">
+        <v>3.5</v>
+      </c>
+      <c r="R151">
+        <v>2</v>
+      </c>
+      <c r="S151">
+        <v>3</v>
+      </c>
+      <c r="T151">
+        <v>1.44</v>
+      </c>
+      <c r="U151">
+        <v>2.63</v>
+      </c>
+      <c r="V151">
+        <v>3.25</v>
+      </c>
+      <c r="W151">
+        <v>1.33</v>
+      </c>
+      <c r="X151">
+        <v>7.5</v>
+      </c>
+      <c r="Y151">
+        <v>1.07</v>
+      </c>
+      <c r="Z151">
+        <v>3</v>
+      </c>
+      <c r="AA151">
+        <v>3.25</v>
+      </c>
+      <c r="AB151">
+        <v>2.3</v>
+      </c>
+      <c r="AC151">
+        <v>1.01</v>
+      </c>
+      <c r="AD151">
+        <v>8.4</v>
+      </c>
+      <c r="AE151">
+        <v>1.31</v>
+      </c>
+      <c r="AF151">
+        <v>2.93</v>
+      </c>
+      <c r="AG151">
+        <v>2.1</v>
+      </c>
+      <c r="AH151">
+        <v>1.7</v>
+      </c>
+      <c r="AI151">
+        <v>1.83</v>
+      </c>
+      <c r="AJ151">
+        <v>1.83</v>
+      </c>
+      <c r="AK151">
+        <v>1.58</v>
+      </c>
+      <c r="AL151">
+        <v>1.31</v>
+      </c>
+      <c r="AM151">
+        <v>1.36</v>
+      </c>
+      <c r="AN151">
+        <v>1.13</v>
+      </c>
+      <c r="AO151">
+        <v>2</v>
+      </c>
+      <c r="AP151">
+        <v>1.33</v>
+      </c>
+      <c r="AQ151">
+        <v>1.78</v>
+      </c>
+      <c r="AR151">
+        <v>1.34</v>
+      </c>
+      <c r="AS151">
+        <v>1.55</v>
+      </c>
+      <c r="AT151">
+        <v>2.89</v>
+      </c>
+      <c r="AU151">
+        <v>7</v>
+      </c>
+      <c r="AV151">
+        <v>3</v>
+      </c>
+      <c r="AW151">
+        <v>4</v>
+      </c>
+      <c r="AX151">
+        <v>1</v>
+      </c>
+      <c r="AY151">
+        <v>11</v>
+      </c>
+      <c r="AZ151">
+        <v>4</v>
+      </c>
+      <c r="BA151">
+        <v>6</v>
+      </c>
+      <c r="BB151">
+        <v>1</v>
+      </c>
+      <c r="BC151">
+        <v>7</v>
+      </c>
+      <c r="BD151">
+        <v>0</v>
+      </c>
+      <c r="BE151">
+        <v>0</v>
+      </c>
+      <c r="BF151">
+        <v>0</v>
+      </c>
+      <c r="BG151">
+        <v>0</v>
+      </c>
+      <c r="BH151">
+        <v>0</v>
+      </c>
+      <c r="BI151">
+        <v>0</v>
+      </c>
+      <c r="BJ151">
+        <v>0</v>
+      </c>
+      <c r="BK151">
+        <v>0</v>
+      </c>
+      <c r="BL151">
+        <v>0</v>
+      </c>
+      <c r="BM151">
+        <v>0</v>
+      </c>
+      <c r="BN151">
+        <v>0</v>
+      </c>
+      <c r="BO151">
+        <v>0</v>
+      </c>
+      <c r="BP151">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="267">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -566,6 +566,9 @@
   </si>
   <si>
     <t>['14', '90+4']</t>
+  </si>
+  <si>
+    <t>['9', '32', '89']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1173,7 +1176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1429,7 +1432,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1507,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ2">
         <v>1.78</v>
@@ -1635,7 +1638,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1841,7 +1844,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1922,7 +1925,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ4">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2047,7 +2050,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2253,7 +2256,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -3283,7 +3286,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3489,7 +3492,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4107,7 +4110,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4313,7 +4316,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4519,7 +4522,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4725,7 +4728,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4803,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ18">
         <v>1.11</v>
@@ -4931,7 +4934,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5137,7 +5140,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5343,7 +5346,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5424,7 +5427,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ21">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR21">
         <v>1.86</v>
@@ -5549,7 +5552,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5961,7 +5964,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6167,7 +6170,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6373,7 +6376,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6579,7 +6582,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6991,7 +6994,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7197,7 +7200,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7403,7 +7406,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -8021,7 +8024,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8099,7 +8102,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ34">
         <v>1.3</v>
@@ -8227,7 +8230,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8433,7 +8436,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8639,7 +8642,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8845,7 +8848,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9257,7 +9260,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9338,7 +9341,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ40">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9463,7 +9466,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9669,7 +9672,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10081,7 +10084,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10287,7 +10290,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10493,7 +10496,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10699,7 +10702,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10905,7 +10908,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11523,7 +11526,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11604,7 +11607,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ51">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR51">
         <v>1.65</v>
@@ -11729,7 +11732,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11807,7 +11810,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -12141,7 +12144,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12553,7 +12556,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12759,7 +12762,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12965,7 +12968,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13583,7 +13586,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13995,7 +13998,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14407,7 +14410,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14613,7 +14616,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14819,7 +14822,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15025,7 +15028,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15643,7 +15646,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15927,7 +15930,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ72">
         <v>1.3</v>
@@ -16342,7 +16345,7 @@
         <v>1</v>
       </c>
       <c r="AQ74">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR74">
         <v>1.42</v>
@@ -16467,7 +16470,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16673,7 +16676,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16879,7 +16882,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17085,7 +17088,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17291,7 +17294,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17703,7 +17706,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18399,7 +18402,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ84">
         <v>0.44</v>
@@ -18527,7 +18530,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18733,7 +18736,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19145,7 +19148,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19351,7 +19354,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19557,7 +19560,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19844,7 +19847,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ91">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR91">
         <v>1.44</v>
@@ -19969,7 +19972,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20175,7 +20178,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20381,7 +20384,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20587,7 +20590,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20999,7 +21002,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21411,7 +21414,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21617,7 +21620,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21823,7 +21826,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22235,7 +22238,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22316,7 +22319,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ103">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22441,7 +22444,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22725,7 +22728,7 @@
         <v>1.17</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ105">
         <v>1.1</v>
@@ -22853,7 +22856,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23059,7 +23062,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23265,7 +23268,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23471,7 +23474,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24913,7 +24916,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25406,7 +25409,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ118">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR118">
         <v>1.23</v>
@@ -25531,7 +25534,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25609,7 +25612,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ119">
         <v>1.22</v>
@@ -26149,7 +26152,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26561,7 +26564,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26767,7 +26770,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26973,7 +26976,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27179,7 +27182,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27385,7 +27388,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27591,7 +27594,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27797,7 +27800,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28209,7 +28212,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28415,7 +28418,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28699,7 +28702,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ134">
         <v>0.5</v>
@@ -29114,7 +29117,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ136">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AR136">
         <v>1.11</v>
@@ -29239,7 +29242,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29651,7 +29654,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30063,7 +30066,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -31093,7 +31096,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31299,7 +31302,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31711,7 +31714,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31917,7 +31920,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32123,7 +32126,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32228,7 +32231,7 @@
         <v>1</v>
       </c>
       <c r="AY151">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ151">
         <v>4</v>
@@ -32279,6 +32282,212 @@
         <v>0</v>
       </c>
       <c r="BP151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:68">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>7484680</v>
+      </c>
+      <c r="C152" t="s">
+        <v>68</v>
+      </c>
+      <c r="D152" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="2">
+        <v>45725.35416666666</v>
+      </c>
+      <c r="F152">
+        <v>19</v>
+      </c>
+      <c r="G152" t="s">
+        <v>70</v>
+      </c>
+      <c r="H152" t="s">
+        <v>81</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>3</v>
+      </c>
+      <c r="L152">
+        <v>3</v>
+      </c>
+      <c r="M152">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>4</v>
+      </c>
+      <c r="O152" t="s">
+        <v>184</v>
+      </c>
+      <c r="P152" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q152">
+        <v>5</v>
+      </c>
+      <c r="R152">
+        <v>2.3</v>
+      </c>
+      <c r="S152">
+        <v>2.1</v>
+      </c>
+      <c r="T152">
+        <v>1.33</v>
+      </c>
+      <c r="U152">
+        <v>3.25</v>
+      </c>
+      <c r="V152">
+        <v>2.63</v>
+      </c>
+      <c r="W152">
+        <v>1.44</v>
+      </c>
+      <c r="X152">
+        <v>6</v>
+      </c>
+      <c r="Y152">
+        <v>1.11</v>
+      </c>
+      <c r="Z152">
+        <v>4.2</v>
+      </c>
+      <c r="AA152">
+        <v>4.75</v>
+      </c>
+      <c r="AB152">
+        <v>1.6</v>
+      </c>
+      <c r="AC152">
+        <v>1.01</v>
+      </c>
+      <c r="AD152">
+        <v>11</v>
+      </c>
+      <c r="AE152">
+        <v>1.17</v>
+      </c>
+      <c r="AF152">
+        <v>4.05</v>
+      </c>
+      <c r="AG152">
+        <v>1.7</v>
+      </c>
+      <c r="AH152">
+        <v>2.1</v>
+      </c>
+      <c r="AI152">
+        <v>1.8</v>
+      </c>
+      <c r="AJ152">
+        <v>1.91</v>
+      </c>
+      <c r="AK152">
+        <v>2.26</v>
+      </c>
+      <c r="AL152">
+        <v>1.22</v>
+      </c>
+      <c r="AM152">
+        <v>1.15</v>
+      </c>
+      <c r="AN152">
+        <v>1</v>
+      </c>
+      <c r="AO152">
+        <v>2.44</v>
+      </c>
+      <c r="AP152">
+        <v>1.2</v>
+      </c>
+      <c r="AQ152">
+        <v>2.2</v>
+      </c>
+      <c r="AR152">
+        <v>1.56</v>
+      </c>
+      <c r="AS152">
+        <v>1.59</v>
+      </c>
+      <c r="AT152">
+        <v>3.15</v>
+      </c>
+      <c r="AU152">
+        <v>6</v>
+      </c>
+      <c r="AV152">
+        <v>7</v>
+      </c>
+      <c r="AW152">
+        <v>9</v>
+      </c>
+      <c r="AX152">
+        <v>6</v>
+      </c>
+      <c r="AY152">
+        <v>19</v>
+      </c>
+      <c r="AZ152">
+        <v>16</v>
+      </c>
+      <c r="BA152">
+        <v>4</v>
+      </c>
+      <c r="BB152">
+        <v>3</v>
+      </c>
+      <c r="BC152">
+        <v>7</v>
+      </c>
+      <c r="BD152">
+        <v>0</v>
+      </c>
+      <c r="BE152">
+        <v>0</v>
+      </c>
+      <c r="BF152">
+        <v>0</v>
+      </c>
+      <c r="BG152">
+        <v>0</v>
+      </c>
+      <c r="BH152">
+        <v>0</v>
+      </c>
+      <c r="BI152">
+        <v>0</v>
+      </c>
+      <c r="BJ152">
+        <v>0</v>
+      </c>
+      <c r="BK152">
+        <v>0</v>
+      </c>
+      <c r="BL152">
+        <v>0</v>
+      </c>
+      <c r="BM152">
+        <v>0</v>
+      </c>
+      <c r="BN152">
+        <v>0</v>
+      </c>
+      <c r="BO152">
+        <v>0</v>
+      </c>
+      <c r="BP152">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="273">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -571,6 +571,18 @@
     <t>['9', '32', '89']</t>
   </si>
   <si>
+    <t>['70', '90+5']</t>
+  </si>
+  <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['5']</t>
+  </si>
+  <si>
+    <t>['70', '89', '90+1']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -581,9 +593,6 @@
   </si>
   <si>
     <t>['4', '10', '44']</t>
-  </si>
-  <si>
-    <t>['15']</t>
   </si>
   <si>
     <t>['8', '17', '33', '43', '77']</t>
@@ -815,6 +824,15 @@
   </si>
   <si>
     <t>['29']</t>
+  </si>
+  <si>
+    <t>['29', '85', '89']</t>
+  </si>
+  <si>
+    <t>['11']</t>
+  </si>
+  <si>
+    <t>['48', '68', '76']</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP152"/>
+  <dimension ref="A1:BP158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1432,7 +1450,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1513,7 +1531,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ2">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1638,7 +1656,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1719,7 +1737,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ3">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1844,7 +1862,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2050,7 +2068,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2128,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ5">
         <v>1.1</v>
@@ -2256,7 +2274,7 @@
         <v>86</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q6">
         <v>2.05</v>
@@ -2746,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ8">
         <v>1.11</v>
@@ -2952,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ9">
         <v>1.9</v>
@@ -3161,7 +3179,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ10">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3286,7 +3304,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3367,7 +3385,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ11">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3492,7 +3510,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3982,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4110,7 +4128,7 @@
         <v>94</v>
       </c>
       <c r="P15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q15">
         <v>3.1</v>
@@ -4188,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ15">
         <v>1.22</v>
@@ -4316,7 +4334,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4394,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ16">
         <v>1.3</v>
@@ -4522,7 +4540,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4603,7 +4621,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ17">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -4728,7 +4746,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4934,7 +4952,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5140,7 +5158,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5221,7 +5239,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ20">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR20">
         <v>0.71</v>
@@ -5346,7 +5364,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5424,7 +5442,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ21">
         <v>2.2</v>
@@ -5552,7 +5570,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5964,7 +5982,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6042,7 +6060,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ24">
         <v>1.4</v>
@@ -6170,7 +6188,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6248,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR25">
         <v>0.84</v>
@@ -6376,7 +6394,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6454,10 +6472,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6582,7 +6600,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6660,10 +6678,10 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ27">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR27">
         <v>1.73</v>
@@ -6994,7 +7012,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7200,7 +7218,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7281,7 +7299,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ30">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR30">
         <v>1.86</v>
@@ -7406,7 +7424,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7693,7 +7711,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ32">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -7896,7 +7914,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ33">
         <v>1.22</v>
@@ -8024,7 +8042,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8230,7 +8248,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8436,7 +8454,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8642,7 +8660,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8848,7 +8866,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9260,7 +9278,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9466,7 +9484,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9672,7 +9690,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9753,7 +9771,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ42">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR42">
         <v>1.18</v>
@@ -10084,7 +10102,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10162,7 +10180,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44">
         <v>0.5</v>
@@ -10290,7 +10308,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10496,7 +10514,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10702,7 +10720,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10908,7 +10926,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11526,7 +11544,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11732,7 +11750,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12016,10 +12034,10 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ53">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR53">
         <v>0.98</v>
@@ -12144,7 +12162,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12222,10 +12240,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ54">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12431,7 +12449,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ55">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12556,7 +12574,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12634,10 +12652,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ56">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR56">
         <v>1.26</v>
@@ -12762,7 +12780,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12843,7 +12861,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ57">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR57">
         <v>1.02</v>
@@ -12968,7 +12986,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13252,10 +13270,10 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ59">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR59">
         <v>1.05</v>
@@ -13458,7 +13476,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ60">
         <v>1.22</v>
@@ -13586,7 +13604,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13664,7 +13682,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ61">
         <v>0.5</v>
@@ -13870,10 +13888,10 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ62">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -13998,7 +14016,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14076,10 +14094,10 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14282,10 +14300,10 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ64">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR64">
         <v>1.93</v>
@@ -14410,7 +14428,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14616,7 +14634,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14697,7 +14715,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ66">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -14822,7 +14840,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14900,7 +14918,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ67">
         <v>0.67</v>
@@ -15028,7 +15046,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15518,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ70">
         <v>0.8</v>
@@ -15646,7 +15664,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15933,7 +15951,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ72">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16136,10 +16154,10 @@
         <v>2</v>
       </c>
       <c r="AP73">
+        <v>1.4</v>
+      </c>
+      <c r="AQ73">
         <v>1.44</v>
-      </c>
-      <c r="AQ73">
-        <v>1.63</v>
       </c>
       <c r="AR73">
         <v>1.39</v>
@@ -16470,7 +16488,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16548,7 +16566,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ75">
         <v>1.3</v>
@@ -16676,7 +16694,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16754,7 +16772,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ76">
         <v>1.11</v>
@@ -16882,7 +16900,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17088,7 +17106,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17169,7 +17187,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ78">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR78">
         <v>1.34</v>
@@ -17294,7 +17312,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17581,7 +17599,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ80">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR80">
         <v>1.44</v>
@@ -17706,7 +17724,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18405,7 +18423,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ84">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -18530,7 +18548,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18608,7 +18626,7 @@
         <v>0.2</v>
       </c>
       <c r="AP85">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ85">
         <v>0.5</v>
@@ -18736,7 +18754,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -18814,10 +18832,10 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ86">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19020,10 +19038,10 @@
         <v>2.2</v>
       </c>
       <c r="AP87">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ87">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.6</v>
@@ -19148,7 +19166,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19226,7 +19244,7 @@
         <v>1.2</v>
       </c>
       <c r="AP88">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ88">
         <v>1.9</v>
@@ -19354,7 +19372,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19432,10 +19450,10 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ89">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -19560,7 +19578,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19638,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ90">
         <v>1.3</v>
@@ -19972,7 +19990,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20053,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="AQ92">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR92">
         <v>1.32</v>
@@ -20178,7 +20196,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20259,7 +20277,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ93">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20384,7 +20402,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20462,7 +20480,7 @@
         <v>1.8</v>
       </c>
       <c r="AP94">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ94">
         <v>1.11</v>
@@ -20590,7 +20608,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20874,10 +20892,10 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ96">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21002,7 +21020,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21083,7 +21101,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ97">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR97">
         <v>1.11</v>
@@ -21414,7 +21432,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21620,7 +21638,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21698,7 +21716,7 @@
         <v>1.5</v>
       </c>
       <c r="AP100">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ100">
         <v>1.9</v>
@@ -21826,7 +21844,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21904,7 +21922,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ101">
         <v>0.8</v>
@@ -22113,7 +22131,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ102">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR102">
         <v>1.18</v>
@@ -22238,7 +22256,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22316,7 +22334,7 @@
         <v>2.17</v>
       </c>
       <c r="AP103">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ103">
         <v>2.2</v>
@@ -22444,7 +22462,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22525,7 +22543,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ104">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -22856,7 +22874,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22934,7 +22952,7 @@
         <v>0.83</v>
       </c>
       <c r="AP106">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ106">
         <v>1.22</v>
@@ -23062,7 +23080,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23140,7 +23158,7 @@
         <v>1.71</v>
       </c>
       <c r="AP107">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ107">
         <v>1.9</v>
@@ -23268,7 +23286,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23349,7 +23367,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ108">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR108">
         <v>1.76</v>
@@ -23474,7 +23492,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24173,7 +24191,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ112">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR112">
         <v>1.39</v>
@@ -24379,7 +24397,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24582,10 +24600,10 @@
         <v>2.5</v>
       </c>
       <c r="AP114">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ114">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR114">
         <v>1.14</v>
@@ -24791,7 +24809,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ115">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -24916,7 +24934,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25200,7 +25218,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ117">
         <v>0.5</v>
@@ -25534,7 +25552,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25615,7 +25633,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ119">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR119">
         <v>1.62</v>
@@ -25818,7 +25836,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ120">
         <v>0.8</v>
@@ -26024,7 +26042,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ121">
         <v>1.4</v>
@@ -26152,7 +26170,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26439,7 +26457,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ123">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR123">
         <v>1.4</v>
@@ -26564,7 +26582,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26642,7 +26660,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ124">
         <v>0.8</v>
@@ -26770,7 +26788,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26851,7 +26869,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ125">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -26976,7 +26994,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27057,7 +27075,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ126">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR126">
         <v>1.27</v>
@@ -27182,7 +27200,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27263,7 +27281,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ127">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR127">
         <v>1.44</v>
@@ -27388,7 +27406,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27466,7 +27484,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128">
         <v>1.3</v>
@@ -27594,7 +27612,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27672,7 +27690,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ129">
         <v>0.67</v>
@@ -27800,7 +27818,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28087,7 +28105,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ131">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28212,7 +28230,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28290,7 +28308,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ132">
         <v>1.4</v>
@@ -28418,7 +28436,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28499,7 +28517,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ133">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR133">
         <v>1.4</v>
@@ -28908,7 +28926,7 @@
         <v>1.38</v>
       </c>
       <c r="AP135">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ135">
         <v>1.1</v>
@@ -29114,7 +29132,7 @@
         <v>2.38</v>
       </c>
       <c r="AP136">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ136">
         <v>2.2</v>
@@ -29242,7 +29260,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29654,7 +29672,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -29735,7 +29753,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ139">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AR139">
         <v>1.38</v>
@@ -29938,10 +29956,10 @@
         <v>1.44</v>
       </c>
       <c r="AP140">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ140">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR140">
         <v>1.92</v>
@@ -30066,7 +30084,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30144,7 +30162,7 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AQ141">
         <v>1.22</v>
@@ -30353,7 +30371,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ142">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AR142">
         <v>1.21</v>
@@ -31096,7 +31114,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31302,7 +31320,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31380,7 +31398,7 @@
         <v>1.56</v>
       </c>
       <c r="AP147">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ147">
         <v>1.4</v>
@@ -31714,7 +31732,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31920,7 +31938,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -31998,10 +32016,10 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AQ150">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR150">
         <v>1.28</v>
@@ -32126,7 +32144,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32204,10 +32222,10 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AQ151">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AR151">
         <v>1.34</v>
@@ -32489,6 +32507,1242 @@
       </c>
       <c r="BP152">
         <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:68">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>7484688</v>
+      </c>
+      <c r="C153" t="s">
+        <v>68</v>
+      </c>
+      <c r="D153" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F153">
+        <v>20</v>
+      </c>
+      <c r="G153" t="s">
+        <v>83</v>
+      </c>
+      <c r="H153" t="s">
+        <v>78</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>2</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <v>3</v>
+      </c>
+      <c r="O153" t="s">
+        <v>185</v>
+      </c>
+      <c r="P153" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q153">
+        <v>2.88</v>
+      </c>
+      <c r="R153">
+        <v>2.25</v>
+      </c>
+      <c r="S153">
+        <v>3.2</v>
+      </c>
+      <c r="T153">
+        <v>1.33</v>
+      </c>
+      <c r="U153">
+        <v>3.25</v>
+      </c>
+      <c r="V153">
+        <v>2.63</v>
+      </c>
+      <c r="W153">
+        <v>1.44</v>
+      </c>
+      <c r="X153">
+        <v>6</v>
+      </c>
+      <c r="Y153">
+        <v>1.11</v>
+      </c>
+      <c r="Z153">
+        <v>2.46</v>
+      </c>
+      <c r="AA153">
+        <v>3.53</v>
+      </c>
+      <c r="AB153">
+        <v>2.66</v>
+      </c>
+      <c r="AC153">
+        <v>1.04</v>
+      </c>
+      <c r="AD153">
+        <v>9</v>
+      </c>
+      <c r="AE153">
+        <v>1.22</v>
+      </c>
+      <c r="AF153">
+        <v>4</v>
+      </c>
+      <c r="AG153">
+        <v>1.7</v>
+      </c>
+      <c r="AH153">
+        <v>2.1</v>
+      </c>
+      <c r="AI153">
+        <v>1.62</v>
+      </c>
+      <c r="AJ153">
+        <v>2.2</v>
+      </c>
+      <c r="AK153">
+        <v>1.45</v>
+      </c>
+      <c r="AL153">
+        <v>1.22</v>
+      </c>
+      <c r="AM153">
+        <v>1.55</v>
+      </c>
+      <c r="AN153">
+        <v>2.11</v>
+      </c>
+      <c r="AO153">
+        <v>1.22</v>
+      </c>
+      <c r="AP153">
+        <v>2.2</v>
+      </c>
+      <c r="AQ153">
+        <v>1.1</v>
+      </c>
+      <c r="AR153">
+        <v>1.72</v>
+      </c>
+      <c r="AS153">
+        <v>1.44</v>
+      </c>
+      <c r="AT153">
+        <v>3.16</v>
+      </c>
+      <c r="AU153">
+        <v>5</v>
+      </c>
+      <c r="AV153">
+        <v>6</v>
+      </c>
+      <c r="AW153">
+        <v>4</v>
+      </c>
+      <c r="AX153">
+        <v>10</v>
+      </c>
+      <c r="AY153">
+        <v>9</v>
+      </c>
+      <c r="AZ153">
+        <v>18</v>
+      </c>
+      <c r="BA153">
+        <v>7</v>
+      </c>
+      <c r="BB153">
+        <v>12</v>
+      </c>
+      <c r="BC153">
+        <v>19</v>
+      </c>
+      <c r="BD153">
+        <v>1.9</v>
+      </c>
+      <c r="BE153">
+        <v>6.8</v>
+      </c>
+      <c r="BF153">
+        <v>2.28</v>
+      </c>
+      <c r="BG153">
+        <v>1.24</v>
+      </c>
+      <c r="BH153">
+        <v>3.52</v>
+      </c>
+      <c r="BI153">
+        <v>1.47</v>
+      </c>
+      <c r="BJ153">
+        <v>2.59</v>
+      </c>
+      <c r="BK153">
+        <v>1.79</v>
+      </c>
+      <c r="BL153">
+        <v>2</v>
+      </c>
+      <c r="BM153">
+        <v>2.24</v>
+      </c>
+      <c r="BN153">
+        <v>1.62</v>
+      </c>
+      <c r="BO153">
+        <v>2.83</v>
+      </c>
+      <c r="BP153">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="154" spans="1:68">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>7484689</v>
+      </c>
+      <c r="C154" t="s">
+        <v>68</v>
+      </c>
+      <c r="D154" t="s">
+        <v>69</v>
+      </c>
+      <c r="E154" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F154">
+        <v>20</v>
+      </c>
+      <c r="G154" t="s">
+        <v>84</v>
+      </c>
+      <c r="H154" t="s">
+        <v>74</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <v>1</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>3</v>
+      </c>
+      <c r="N154">
+        <v>3</v>
+      </c>
+      <c r="O154" t="s">
+        <v>86</v>
+      </c>
+      <c r="P154" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q154">
+        <v>3.75</v>
+      </c>
+      <c r="R154">
+        <v>2.1</v>
+      </c>
+      <c r="S154">
+        <v>2.63</v>
+      </c>
+      <c r="T154">
+        <v>1.4</v>
+      </c>
+      <c r="U154">
+        <v>2.75</v>
+      </c>
+      <c r="V154">
+        <v>2.75</v>
+      </c>
+      <c r="W154">
+        <v>1.4</v>
+      </c>
+      <c r="X154">
+        <v>7</v>
+      </c>
+      <c r="Y154">
+        <v>1.08</v>
+      </c>
+      <c r="Z154">
+        <v>3.2</v>
+      </c>
+      <c r="AA154">
+        <v>3.4</v>
+      </c>
+      <c r="AB154">
+        <v>2.05</v>
+      </c>
+      <c r="AC154">
+        <v>1.05</v>
+      </c>
+      <c r="AD154">
+        <v>8.5</v>
+      </c>
+      <c r="AE154">
+        <v>1.28</v>
+      </c>
+      <c r="AF154">
+        <v>3.55</v>
+      </c>
+      <c r="AG154">
+        <v>1.85</v>
+      </c>
+      <c r="AH154">
+        <v>1.95</v>
+      </c>
+      <c r="AI154">
+        <v>1.73</v>
+      </c>
+      <c r="AJ154">
+        <v>2</v>
+      </c>
+      <c r="AK154">
+        <v>1.77</v>
+      </c>
+      <c r="AL154">
+        <v>1.25</v>
+      </c>
+      <c r="AM154">
+        <v>1.28</v>
+      </c>
+      <c r="AN154">
+        <v>2.11</v>
+      </c>
+      <c r="AO154">
+        <v>2.22</v>
+      </c>
+      <c r="AP154">
+        <v>1.9</v>
+      </c>
+      <c r="AQ154">
+        <v>2.3</v>
+      </c>
+      <c r="AR154">
+        <v>1.88</v>
+      </c>
+      <c r="AS154">
+        <v>1.65</v>
+      </c>
+      <c r="AT154">
+        <v>3.53</v>
+      </c>
+      <c r="AU154">
+        <v>3</v>
+      </c>
+      <c r="AV154">
+        <v>6</v>
+      </c>
+      <c r="AW154">
+        <v>3</v>
+      </c>
+      <c r="AX154">
+        <v>10</v>
+      </c>
+      <c r="AY154">
+        <v>7</v>
+      </c>
+      <c r="AZ154">
+        <v>21</v>
+      </c>
+      <c r="BA154">
+        <v>4</v>
+      </c>
+      <c r="BB154">
+        <v>3</v>
+      </c>
+      <c r="BC154">
+        <v>7</v>
+      </c>
+      <c r="BD154">
+        <v>2.88</v>
+      </c>
+      <c r="BE154">
+        <v>7</v>
+      </c>
+      <c r="BF154">
+        <v>1.64</v>
+      </c>
+      <c r="BG154">
+        <v>1.42</v>
+      </c>
+      <c r="BH154">
+        <v>2.65</v>
+      </c>
+      <c r="BI154">
+        <v>1.77</v>
+      </c>
+      <c r="BJ154">
+        <v>2.01</v>
+      </c>
+      <c r="BK154">
+        <v>2.19</v>
+      </c>
+      <c r="BL154">
+        <v>1.64</v>
+      </c>
+      <c r="BM154">
+        <v>2.83</v>
+      </c>
+      <c r="BN154">
+        <v>1.37</v>
+      </c>
+      <c r="BO154">
+        <v>3.88</v>
+      </c>
+      <c r="BP154">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:68">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>7484690</v>
+      </c>
+      <c r="C155" t="s">
+        <v>68</v>
+      </c>
+      <c r="D155" t="s">
+        <v>69</v>
+      </c>
+      <c r="E155" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F155">
+        <v>20</v>
+      </c>
+      <c r="G155" t="s">
+        <v>73</v>
+      </c>
+      <c r="H155" t="s">
+        <v>72</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="J155">
+        <v>1</v>
+      </c>
+      <c r="K155">
+        <v>2</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="M155">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>2</v>
+      </c>
+      <c r="O155" t="s">
+        <v>186</v>
+      </c>
+      <c r="P155" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q155">
+        <v>3.6</v>
+      </c>
+      <c r="R155">
+        <v>2.05</v>
+      </c>
+      <c r="S155">
+        <v>2.88</v>
+      </c>
+      <c r="T155">
+        <v>1.44</v>
+      </c>
+      <c r="U155">
+        <v>2.63</v>
+      </c>
+      <c r="V155">
+        <v>3.25</v>
+      </c>
+      <c r="W155">
+        <v>1.33</v>
+      </c>
+      <c r="X155">
+        <v>7.5</v>
+      </c>
+      <c r="Y155">
+        <v>1.07</v>
+      </c>
+      <c r="Z155">
+        <v>2.8</v>
+      </c>
+      <c r="AA155">
+        <v>3.5</v>
+      </c>
+      <c r="AB155">
+        <v>2.2</v>
+      </c>
+      <c r="AC155">
+        <v>1.05</v>
+      </c>
+      <c r="AD155">
+        <v>8.5</v>
+      </c>
+      <c r="AE155">
+        <v>1.33</v>
+      </c>
+      <c r="AF155">
+        <v>3.1</v>
+      </c>
+      <c r="AG155">
+        <v>2.08</v>
+      </c>
+      <c r="AH155">
+        <v>1.73</v>
+      </c>
+      <c r="AI155">
+        <v>1.83</v>
+      </c>
+      <c r="AJ155">
+        <v>1.83</v>
+      </c>
+      <c r="AK155">
+        <v>1.6</v>
+      </c>
+      <c r="AL155">
+        <v>1.25</v>
+      </c>
+      <c r="AM155">
+        <v>1.38</v>
+      </c>
+      <c r="AN155">
+        <v>0.6</v>
+      </c>
+      <c r="AO155">
+        <v>0.44</v>
+      </c>
+      <c r="AP155">
+        <v>0.64</v>
+      </c>
+      <c r="AQ155">
+        <v>0.5</v>
+      </c>
+      <c r="AR155">
+        <v>1.03</v>
+      </c>
+      <c r="AS155">
+        <v>1.06</v>
+      </c>
+      <c r="AT155">
+        <v>2.09</v>
+      </c>
+      <c r="AU155">
+        <v>5</v>
+      </c>
+      <c r="AV155">
+        <v>3</v>
+      </c>
+      <c r="AW155">
+        <v>4</v>
+      </c>
+      <c r="AX155">
+        <v>8</v>
+      </c>
+      <c r="AY155">
+        <v>9</v>
+      </c>
+      <c r="AZ155">
+        <v>12</v>
+      </c>
+      <c r="BA155">
+        <v>8</v>
+      </c>
+      <c r="BB155">
+        <v>5</v>
+      </c>
+      <c r="BC155">
+        <v>13</v>
+      </c>
+      <c r="BD155">
+        <v>2.47</v>
+      </c>
+      <c r="BE155">
+        <v>6.35</v>
+      </c>
+      <c r="BF155">
+        <v>1.84</v>
+      </c>
+      <c r="BG155">
+        <v>1.29</v>
+      </c>
+      <c r="BH155">
+        <v>3.04</v>
+      </c>
+      <c r="BI155">
+        <v>1.56</v>
+      </c>
+      <c r="BJ155">
+        <v>2.21</v>
+      </c>
+      <c r="BK155">
+        <v>1.99</v>
+      </c>
+      <c r="BL155">
+        <v>1.73</v>
+      </c>
+      <c r="BM155">
+        <v>2.6</v>
+      </c>
+      <c r="BN155">
+        <v>1.41</v>
+      </c>
+      <c r="BO155">
+        <v>3.5</v>
+      </c>
+      <c r="BP155">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="156" spans="1:68">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>7484691</v>
+      </c>
+      <c r="C156" t="s">
+        <v>68</v>
+      </c>
+      <c r="D156" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F156">
+        <v>20</v>
+      </c>
+      <c r="G156" t="s">
+        <v>77</v>
+      </c>
+      <c r="H156" t="s">
+        <v>75</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156" t="s">
+        <v>86</v>
+      </c>
+      <c r="P156" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q156">
+        <v>3.4</v>
+      </c>
+      <c r="R156">
+        <v>1.91</v>
+      </c>
+      <c r="S156">
+        <v>3.4</v>
+      </c>
+      <c r="T156">
+        <v>1.53</v>
+      </c>
+      <c r="U156">
+        <v>2.38</v>
+      </c>
+      <c r="V156">
+        <v>3.5</v>
+      </c>
+      <c r="W156">
+        <v>1.29</v>
+      </c>
+      <c r="X156">
+        <v>8.5</v>
+      </c>
+      <c r="Y156">
+        <v>1.05</v>
+      </c>
+      <c r="Z156">
+        <v>2.55</v>
+      </c>
+      <c r="AA156">
+        <v>3</v>
+      </c>
+      <c r="AB156">
+        <v>2.7</v>
+      </c>
+      <c r="AC156">
+        <v>1.09</v>
+      </c>
+      <c r="AD156">
+        <v>6.5</v>
+      </c>
+      <c r="AE156">
+        <v>1.45</v>
+      </c>
+      <c r="AF156">
+        <v>2.62</v>
+      </c>
+      <c r="AG156">
+        <v>2.35</v>
+      </c>
+      <c r="AH156">
+        <v>1.57</v>
+      </c>
+      <c r="AI156">
+        <v>2</v>
+      </c>
+      <c r="AJ156">
+        <v>1.73</v>
+      </c>
+      <c r="AK156">
+        <v>1.44</v>
+      </c>
+      <c r="AL156">
+        <v>1.3</v>
+      </c>
+      <c r="AM156">
+        <v>1.44</v>
+      </c>
+      <c r="AN156">
+        <v>1.33</v>
+      </c>
+      <c r="AO156">
+        <v>1.3</v>
+      </c>
+      <c r="AP156">
+        <v>1.3</v>
+      </c>
+      <c r="AQ156">
+        <v>1.27</v>
+      </c>
+      <c r="AR156">
+        <v>1.35</v>
+      </c>
+      <c r="AS156">
+        <v>1.26</v>
+      </c>
+      <c r="AT156">
+        <v>2.61</v>
+      </c>
+      <c r="AU156">
+        <v>2</v>
+      </c>
+      <c r="AV156">
+        <v>2</v>
+      </c>
+      <c r="AW156">
+        <v>2</v>
+      </c>
+      <c r="AX156">
+        <v>3</v>
+      </c>
+      <c r="AY156">
+        <v>5</v>
+      </c>
+      <c r="AZ156">
+        <v>5</v>
+      </c>
+      <c r="BA156">
+        <v>2</v>
+      </c>
+      <c r="BB156">
+        <v>5</v>
+      </c>
+      <c r="BC156">
+        <v>7</v>
+      </c>
+      <c r="BD156">
+        <v>1.98</v>
+      </c>
+      <c r="BE156">
+        <v>6.35</v>
+      </c>
+      <c r="BF156">
+        <v>2.26</v>
+      </c>
+      <c r="BG156">
+        <v>1.24</v>
+      </c>
+      <c r="BH156">
+        <v>3.34</v>
+      </c>
+      <c r="BI156">
+        <v>1.48</v>
+      </c>
+      <c r="BJ156">
+        <v>2.4</v>
+      </c>
+      <c r="BK156">
+        <v>1.85</v>
+      </c>
+      <c r="BL156">
+        <v>1.85</v>
+      </c>
+      <c r="BM156">
+        <v>2.38</v>
+      </c>
+      <c r="BN156">
+        <v>1.49</v>
+      </c>
+      <c r="BO156">
+        <v>3.14</v>
+      </c>
+      <c r="BP156">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="157" spans="1:68">
+      <c r="A157" s="1">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>7484695</v>
+      </c>
+      <c r="C157" t="s">
+        <v>68</v>
+      </c>
+      <c r="D157" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="2">
+        <v>45730.58333333334</v>
+      </c>
+      <c r="F157">
+        <v>20</v>
+      </c>
+      <c r="G157" t="s">
+        <v>76</v>
+      </c>
+      <c r="H157" t="s">
+        <v>70</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+      <c r="L157">
+        <v>1</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>1</v>
+      </c>
+      <c r="O157" t="s">
+        <v>187</v>
+      </c>
+      <c r="P157" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q157">
+        <v>2.88</v>
+      </c>
+      <c r="R157">
+        <v>2.4</v>
+      </c>
+      <c r="S157">
+        <v>2.88</v>
+      </c>
+      <c r="T157">
+        <v>1.25</v>
+      </c>
+      <c r="U157">
+        <v>3.75</v>
+      </c>
+      <c r="V157">
+        <v>2.2</v>
+      </c>
+      <c r="W157">
+        <v>1.62</v>
+      </c>
+      <c r="X157">
+        <v>4.5</v>
+      </c>
+      <c r="Y157">
+        <v>1.17</v>
+      </c>
+      <c r="Z157">
+        <v>2.45</v>
+      </c>
+      <c r="AA157">
+        <v>3.4</v>
+      </c>
+      <c r="AB157">
+        <v>2.55</v>
+      </c>
+      <c r="AC157">
+        <v>1.01</v>
+      </c>
+      <c r="AD157">
+        <v>13</v>
+      </c>
+      <c r="AE157">
+        <v>1.14</v>
+      </c>
+      <c r="AF157">
+        <v>5.25</v>
+      </c>
+      <c r="AG157">
+        <v>1.5</v>
+      </c>
+      <c r="AH157">
+        <v>2.5</v>
+      </c>
+      <c r="AI157">
+        <v>1.4</v>
+      </c>
+      <c r="AJ157">
+        <v>2.75</v>
+      </c>
+      <c r="AK157">
+        <v>1.48</v>
+      </c>
+      <c r="AL157">
+        <v>1.22</v>
+      </c>
+      <c r="AM157">
+        <v>1.53</v>
+      </c>
+      <c r="AN157">
+        <v>1.67</v>
+      </c>
+      <c r="AO157">
+        <v>1.63</v>
+      </c>
+      <c r="AP157">
+        <v>1.8</v>
+      </c>
+      <c r="AQ157">
+        <v>1.44</v>
+      </c>
+      <c r="AR157">
+        <v>1.27</v>
+      </c>
+      <c r="AS157">
+        <v>1.43</v>
+      </c>
+      <c r="AT157">
+        <v>2.7</v>
+      </c>
+      <c r="AU157">
+        <v>5</v>
+      </c>
+      <c r="AV157">
+        <v>5</v>
+      </c>
+      <c r="AW157">
+        <v>6</v>
+      </c>
+      <c r="AX157">
+        <v>5</v>
+      </c>
+      <c r="AY157">
+        <v>13</v>
+      </c>
+      <c r="AZ157">
+        <v>10</v>
+      </c>
+      <c r="BA157">
+        <v>3</v>
+      </c>
+      <c r="BB157">
+        <v>5</v>
+      </c>
+      <c r="BC157">
+        <v>8</v>
+      </c>
+      <c r="BD157">
+        <v>2.73</v>
+      </c>
+      <c r="BE157">
+        <v>6.75</v>
+      </c>
+      <c r="BF157">
+        <v>1.69</v>
+      </c>
+      <c r="BG157">
+        <v>1.2</v>
+      </c>
+      <c r="BH157">
+        <v>3.88</v>
+      </c>
+      <c r="BI157">
+        <v>1.33</v>
+      </c>
+      <c r="BJ157">
+        <v>2.83</v>
+      </c>
+      <c r="BK157">
+        <v>1.6</v>
+      </c>
+      <c r="BL157">
+        <v>2.14</v>
+      </c>
+      <c r="BM157">
+        <v>2.02</v>
+      </c>
+      <c r="BN157">
+        <v>1.71</v>
+      </c>
+      <c r="BO157">
+        <v>2.6</v>
+      </c>
+      <c r="BP157">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="158" spans="1:68">
+      <c r="A158" s="1">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>7484694</v>
+      </c>
+      <c r="C158" t="s">
+        <v>68</v>
+      </c>
+      <c r="D158" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="2">
+        <v>45730.6875</v>
+      </c>
+      <c r="F158">
+        <v>20</v>
+      </c>
+      <c r="G158" t="s">
+        <v>82</v>
+      </c>
+      <c r="H158" t="s">
+        <v>85</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>3</v>
+      </c>
+      <c r="M158">
+        <v>3</v>
+      </c>
+      <c r="N158">
+        <v>6</v>
+      </c>
+      <c r="O158" t="s">
+        <v>188</v>
+      </c>
+      <c r="P158" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q158">
+        <v>2.4</v>
+      </c>
+      <c r="R158">
+        <v>2.2</v>
+      </c>
+      <c r="S158">
+        <v>4.33</v>
+      </c>
+      <c r="T158">
+        <v>1.36</v>
+      </c>
+      <c r="U158">
+        <v>3</v>
+      </c>
+      <c r="V158">
+        <v>2.63</v>
+      </c>
+      <c r="W158">
+        <v>1.44</v>
+      </c>
+      <c r="X158">
+        <v>6.5</v>
+      </c>
+      <c r="Y158">
+        <v>1.1</v>
+      </c>
+      <c r="Z158">
+        <v>1.8</v>
+      </c>
+      <c r="AA158">
+        <v>3.7</v>
+      </c>
+      <c r="AB158">
+        <v>3.7</v>
+      </c>
+      <c r="AC158">
+        <v>1.04</v>
+      </c>
+      <c r="AD158">
+        <v>9</v>
+      </c>
+      <c r="AE158">
+        <v>1.25</v>
+      </c>
+      <c r="AF158">
+        <v>3.65</v>
+      </c>
+      <c r="AG158">
+        <v>1.8</v>
+      </c>
+      <c r="AH158">
+        <v>2</v>
+      </c>
+      <c r="AI158">
+        <v>1.73</v>
+      </c>
+      <c r="AJ158">
+        <v>2</v>
+      </c>
+      <c r="AK158">
+        <v>1.25</v>
+      </c>
+      <c r="AL158">
+        <v>1.22</v>
+      </c>
+      <c r="AM158">
+        <v>1.9</v>
+      </c>
+      <c r="AN158">
+        <v>1.44</v>
+      </c>
+      <c r="AO158">
+        <v>1.78</v>
+      </c>
+      <c r="AP158">
+        <v>1.4</v>
+      </c>
+      <c r="AQ158">
+        <v>1.7</v>
+      </c>
+      <c r="AR158">
+        <v>1.5</v>
+      </c>
+      <c r="AS158">
+        <v>1.46</v>
+      </c>
+      <c r="AT158">
+        <v>2.96</v>
+      </c>
+      <c r="AU158">
+        <v>8</v>
+      </c>
+      <c r="AV158">
+        <v>7</v>
+      </c>
+      <c r="AW158">
+        <v>8</v>
+      </c>
+      <c r="AX158">
+        <v>5</v>
+      </c>
+      <c r="AY158">
+        <v>19</v>
+      </c>
+      <c r="AZ158">
+        <v>12</v>
+      </c>
+      <c r="BA158">
+        <v>5</v>
+      </c>
+      <c r="BB158">
+        <v>0</v>
+      </c>
+      <c r="BC158">
+        <v>5</v>
+      </c>
+      <c r="BD158">
+        <v>1.45</v>
+      </c>
+      <c r="BE158">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF158">
+        <v>3.24</v>
+      </c>
+      <c r="BG158">
+        <v>1.19</v>
+      </c>
+      <c r="BH158">
+        <v>3.95</v>
+      </c>
+      <c r="BI158">
+        <v>1.33</v>
+      </c>
+      <c r="BJ158">
+        <v>2.83</v>
+      </c>
+      <c r="BK158">
+        <v>1.6</v>
+      </c>
+      <c r="BL158">
+        <v>2.14</v>
+      </c>
+      <c r="BM158">
+        <v>2.02</v>
+      </c>
+      <c r="BN158">
+        <v>1.71</v>
+      </c>
+      <c r="BO158">
+        <v>2.6</v>
+      </c>
+      <c r="BP158">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="274">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -581,6 +581,9 @@
   </si>
   <si>
     <t>['70', '89', '90+1']</t>
+  </si>
+  <si>
+    <t>['20', '25', '46', '79']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1194,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP158"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1450,7 +1453,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1656,7 +1659,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1862,7 +1865,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2068,7 +2071,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2561,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3304,7 +3307,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3510,7 +3513,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3794,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13">
         <v>0.67</v>
@@ -4334,7 +4337,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4540,7 +4543,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4746,7 +4749,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4952,7 +4955,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5158,7 +5161,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5364,7 +5367,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5570,7 +5573,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5857,7 +5860,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ23">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR23">
         <v>2.04</v>
@@ -5982,7 +5985,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6188,7 +6191,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6394,7 +6397,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6600,7 +6603,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -7012,7 +7015,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7218,7 +7221,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7424,7 +7427,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7708,7 +7711,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ32">
         <v>1.44</v>
@@ -8042,7 +8045,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8248,7 +8251,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8454,7 +8457,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8660,7 +8663,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8866,7 +8869,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9278,7 +9281,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9484,7 +9487,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9690,7 +9693,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9974,7 +9977,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ43">
         <v>1.22</v>
@@ -10102,7 +10105,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10183,7 +10186,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ44">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR44">
         <v>1.33</v>
@@ -10308,7 +10311,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10514,7 +10517,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10720,7 +10723,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10926,7 +10929,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11544,7 +11547,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11750,7 +11753,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12162,7 +12165,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12574,7 +12577,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12780,7 +12783,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12986,7 +12989,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13064,7 +13067,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ58">
         <v>1.1</v>
@@ -13604,7 +13607,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13685,7 +13688,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ61">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR61">
         <v>1.31</v>
@@ -14016,7 +14019,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14428,7 +14431,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14509,7 +14512,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ65">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR65">
         <v>1.19</v>
@@ -14634,7 +14637,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14840,7 +14843,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15046,7 +15049,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15664,7 +15667,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15742,7 +15745,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ71">
         <v>1.9</v>
@@ -16488,7 +16491,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16694,7 +16697,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16900,7 +16903,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17106,7 +17109,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17312,7 +17315,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17724,7 +17727,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18008,7 +18011,7 @@
         <v>2.4</v>
       </c>
       <c r="AP82">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ82">
         <v>1.4</v>
@@ -18548,7 +18551,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18629,7 +18632,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ85">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR85">
         <v>1.86</v>
@@ -18754,7 +18757,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19166,7 +19169,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19372,7 +19375,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19578,7 +19581,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19990,7 +19993,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20196,7 +20199,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20402,7 +20405,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20608,7 +20611,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -21020,7 +21023,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21307,7 +21310,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ98">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR98">
         <v>1.62</v>
@@ -21432,7 +21435,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21638,7 +21641,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21844,7 +21847,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22256,7 +22259,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22462,7 +22465,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22874,7 +22877,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23080,7 +23083,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23286,7 +23289,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23492,7 +23495,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23776,7 +23779,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ110">
         <v>1.11</v>
@@ -24934,7 +24937,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25221,7 +25224,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -25552,7 +25555,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26170,7 +26173,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26454,7 +26457,7 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ123">
         <v>0.5</v>
@@ -26582,7 +26585,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26788,7 +26791,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26994,7 +26997,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27200,7 +27203,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27406,7 +27409,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27612,7 +27615,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27818,7 +27821,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28230,7 +28233,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28436,7 +28439,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28723,7 +28726,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ134">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR134">
         <v>1.56</v>
@@ -29260,7 +29263,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29672,7 +29675,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30084,7 +30087,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30574,7 +30577,7 @@
         <v>0.89</v>
       </c>
       <c r="AP143">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AQ143">
         <v>0.8</v>
@@ -31114,7 +31117,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31195,7 +31198,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ146">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -31320,7 +31323,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31732,7 +31735,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31938,7 +31941,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32144,7 +32147,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32556,7 +32559,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32762,7 +32765,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -32968,7 +32971,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33586,7 +33589,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -33743,6 +33746,212 @@
       </c>
       <c r="BP158">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="159" spans="1:68">
+      <c r="A159" s="1">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>7484693</v>
+      </c>
+      <c r="C159" t="s">
+        <v>68</v>
+      </c>
+      <c r="D159" t="s">
+        <v>69</v>
+      </c>
+      <c r="E159" s="2">
+        <v>45731.4375</v>
+      </c>
+      <c r="F159">
+        <v>20</v>
+      </c>
+      <c r="G159" t="s">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s">
+        <v>79</v>
+      </c>
+      <c r="I159">
+        <v>2</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>2</v>
+      </c>
+      <c r="L159">
+        <v>4</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>4</v>
+      </c>
+      <c r="O159" t="s">
+        <v>189</v>
+      </c>
+      <c r="P159" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q159">
+        <v>1.62</v>
+      </c>
+      <c r="R159">
+        <v>2.75</v>
+      </c>
+      <c r="S159">
+        <v>8</v>
+      </c>
+      <c r="T159">
+        <v>1.22</v>
+      </c>
+      <c r="U159">
+        <v>4</v>
+      </c>
+      <c r="V159">
+        <v>2.1</v>
+      </c>
+      <c r="W159">
+        <v>1.67</v>
+      </c>
+      <c r="X159">
+        <v>4.33</v>
+      </c>
+      <c r="Y159">
+        <v>1.2</v>
+      </c>
+      <c r="Z159">
+        <v>1.22</v>
+      </c>
+      <c r="AA159">
+        <v>5.75</v>
+      </c>
+      <c r="AB159">
+        <v>9.5</v>
+      </c>
+      <c r="AC159">
+        <v>0</v>
+      </c>
+      <c r="AD159">
+        <v>0</v>
+      </c>
+      <c r="AE159">
+        <v>1.11</v>
+      </c>
+      <c r="AF159">
+        <v>5.5</v>
+      </c>
+      <c r="AG159">
+        <v>1.44</v>
+      </c>
+      <c r="AH159">
+        <v>2.63</v>
+      </c>
+      <c r="AI159">
+        <v>1.83</v>
+      </c>
+      <c r="AJ159">
+        <v>1.83</v>
+      </c>
+      <c r="AK159">
+        <v>1.06</v>
+      </c>
+      <c r="AL159">
+        <v>1.11</v>
+      </c>
+      <c r="AM159">
+        <v>4</v>
+      </c>
+      <c r="AN159">
+        <v>2.11</v>
+      </c>
+      <c r="AO159">
+        <v>0.5</v>
+      </c>
+      <c r="AP159">
+        <v>2.2</v>
+      </c>
+      <c r="AQ159">
+        <v>0.45</v>
+      </c>
+      <c r="AR159">
+        <v>1.42</v>
+      </c>
+      <c r="AS159">
+        <v>1.32</v>
+      </c>
+      <c r="AT159">
+        <v>2.74</v>
+      </c>
+      <c r="AU159">
+        <v>7</v>
+      </c>
+      <c r="AV159">
+        <v>4</v>
+      </c>
+      <c r="AW159">
+        <v>7</v>
+      </c>
+      <c r="AX159">
+        <v>4</v>
+      </c>
+      <c r="AY159">
+        <v>15</v>
+      </c>
+      <c r="AZ159">
+        <v>10</v>
+      </c>
+      <c r="BA159">
+        <v>4</v>
+      </c>
+      <c r="BB159">
+        <v>5</v>
+      </c>
+      <c r="BC159">
+        <v>9</v>
+      </c>
+      <c r="BD159">
+        <v>1.23</v>
+      </c>
+      <c r="BE159">
+        <v>10.2</v>
+      </c>
+      <c r="BF159">
+        <v>5.4</v>
+      </c>
+      <c r="BG159">
+        <v>1.31</v>
+      </c>
+      <c r="BH159">
+        <v>2.92</v>
+      </c>
+      <c r="BI159">
+        <v>1.63</v>
+      </c>
+      <c r="BJ159">
+        <v>2.2</v>
+      </c>
+      <c r="BK159">
+        <v>2.05</v>
+      </c>
+      <c r="BL159">
+        <v>1.74</v>
+      </c>
+      <c r="BM159">
+        <v>2.64</v>
+      </c>
+      <c r="BN159">
+        <v>1.4</v>
+      </c>
+      <c r="BO159">
+        <v>3.58</v>
+      </c>
+      <c r="BP159">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="275">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>['20', '25', '46', '79']</t>
+  </si>
+  <si>
+    <t>['27', '90', '90+4']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1197,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1453,7 +1456,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1659,7 +1662,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1865,7 +1868,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2071,7 +2074,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -3307,7 +3310,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3513,7 +3516,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3591,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ12">
         <v>0.8</v>
@@ -4212,7 +4215,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ15">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4337,7 +4340,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4543,7 +4546,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4749,7 +4752,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4955,7 +4958,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5161,7 +5164,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5367,7 +5370,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5573,7 +5576,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5985,7 +5988,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6191,7 +6194,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6397,7 +6400,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6603,7 +6606,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6887,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ28">
         <v>1.9</v>
@@ -7015,7 +7018,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7221,7 +7224,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7427,7 +7430,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7920,7 +7923,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ33">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR33">
         <v>1.76</v>
@@ -8045,7 +8048,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8251,7 +8254,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8457,7 +8460,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8663,7 +8666,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8869,7 +8872,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9281,7 +9284,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9487,7 +9490,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9693,7 +9696,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9771,7 +9774,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ42">
         <v>1.27</v>
@@ -9980,7 +9983,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ43">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10105,7 +10108,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10311,7 +10314,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10517,7 +10520,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10723,7 +10726,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10929,7 +10932,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11547,7 +11550,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11753,7 +11756,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12165,7 +12168,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12577,7 +12580,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12783,7 +12786,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12861,7 +12864,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ57">
         <v>1.44</v>
@@ -12989,7 +12992,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13482,7 +13485,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ60">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR60">
         <v>1.45</v>
@@ -13607,7 +13610,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -14019,7 +14022,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14431,7 +14434,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14637,7 +14640,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14843,7 +14846,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15049,7 +15052,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15667,7 +15670,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16491,7 +16494,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16697,7 +16700,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16903,7 +16906,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16984,7 +16987,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ77">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR77">
         <v>1.02</v>
@@ -17109,7 +17112,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17315,7 +17318,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17393,7 +17396,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ79">
         <v>1.1</v>
@@ -17727,7 +17730,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18220,7 +18223,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ83">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR83">
         <v>1.17</v>
@@ -18551,7 +18554,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18757,7 +18760,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19169,7 +19172,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19375,7 +19378,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19581,7 +19584,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19993,7 +19996,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20199,7 +20202,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20405,7 +20408,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20611,7 +20614,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -21023,7 +21026,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21101,7 +21104,7 @@
         <v>2</v>
       </c>
       <c r="AP97">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ97">
         <v>1.7</v>
@@ -21435,7 +21438,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21641,7 +21644,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21847,7 +21850,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22259,7 +22262,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22465,7 +22468,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22877,7 +22880,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -22958,7 +22961,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ106">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23083,7 +23086,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23289,7 +23292,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23495,7 +23498,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23985,7 +23988,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ111">
         <v>0.67</v>
@@ -24937,7 +24940,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25555,7 +25558,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26173,7 +26176,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26254,7 +26257,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ122">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR122">
         <v>1.65</v>
@@ -26585,7 +26588,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26791,7 +26794,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26997,7 +27000,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27075,7 +27078,7 @@
         <v>2.29</v>
       </c>
       <c r="AP126">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ126">
         <v>2.3</v>
@@ -27203,7 +27206,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27409,7 +27412,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27615,7 +27618,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27821,7 +27824,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28233,7 +28236,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28439,7 +28442,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29263,7 +29266,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29675,7 +29678,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30087,7 +30090,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30168,7 +30171,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ141">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AR141">
         <v>1.04</v>
@@ -30783,7 +30786,7 @@
         <v>1.33</v>
       </c>
       <c r="AP144">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ144">
         <v>1.3</v>
@@ -31117,7 +31120,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31323,7 +31326,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31735,7 +31738,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31941,7 +31944,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32147,7 +32150,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32559,7 +32562,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32765,7 +32768,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -32971,7 +32974,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33589,7 +33592,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -33952,6 +33955,212 @@
       </c>
       <c r="BP159">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="160" spans="1:68">
+      <c r="A160" s="1">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>7484692</v>
+      </c>
+      <c r="C160" t="s">
+        <v>68</v>
+      </c>
+      <c r="D160" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="2">
+        <v>45732.27083333334</v>
+      </c>
+      <c r="F160">
+        <v>20</v>
+      </c>
+      <c r="G160" t="s">
+        <v>80</v>
+      </c>
+      <c r="H160" t="s">
+        <v>71</v>
+      </c>
+      <c r="I160">
+        <v>1</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>1</v>
+      </c>
+      <c r="L160">
+        <v>3</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>3</v>
+      </c>
+      <c r="O160" t="s">
+        <v>190</v>
+      </c>
+      <c r="P160" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q160">
+        <v>4</v>
+      </c>
+      <c r="R160">
+        <v>2.1</v>
+      </c>
+      <c r="S160">
+        <v>2.5</v>
+      </c>
+      <c r="T160">
+        <v>1.4</v>
+      </c>
+      <c r="U160">
+        <v>2.75</v>
+      </c>
+      <c r="V160">
+        <v>2.75</v>
+      </c>
+      <c r="W160">
+        <v>1.4</v>
+      </c>
+      <c r="X160">
+        <v>7</v>
+      </c>
+      <c r="Y160">
+        <v>1.08</v>
+      </c>
+      <c r="Z160">
+        <v>3.74</v>
+      </c>
+      <c r="AA160">
+        <v>3.66</v>
+      </c>
+      <c r="AB160">
+        <v>1.89</v>
+      </c>
+      <c r="AC160">
+        <v>1.03</v>
+      </c>
+      <c r="AD160">
+        <v>9</v>
+      </c>
+      <c r="AE160">
+        <v>1.29</v>
+      </c>
+      <c r="AF160">
+        <v>3.3</v>
+      </c>
+      <c r="AG160">
+        <v>1.88</v>
+      </c>
+      <c r="AH160">
+        <v>1.9</v>
+      </c>
+      <c r="AI160">
+        <v>1.8</v>
+      </c>
+      <c r="AJ160">
+        <v>1.91</v>
+      </c>
+      <c r="AK160">
+        <v>1.77</v>
+      </c>
+      <c r="AL160">
+        <v>1.28</v>
+      </c>
+      <c r="AM160">
+        <v>1.28</v>
+      </c>
+      <c r="AN160">
+        <v>1.44</v>
+      </c>
+      <c r="AO160">
+        <v>1.22</v>
+      </c>
+      <c r="AP160">
+        <v>1.6</v>
+      </c>
+      <c r="AQ160">
+        <v>1.1</v>
+      </c>
+      <c r="AR160">
+        <v>1.4</v>
+      </c>
+      <c r="AS160">
+        <v>1.44</v>
+      </c>
+      <c r="AT160">
+        <v>2.84</v>
+      </c>
+      <c r="AU160">
+        <v>5</v>
+      </c>
+      <c r="AV160">
+        <v>8</v>
+      </c>
+      <c r="AW160">
+        <v>4</v>
+      </c>
+      <c r="AX160">
+        <v>13</v>
+      </c>
+      <c r="AY160">
+        <v>9</v>
+      </c>
+      <c r="AZ160">
+        <v>27</v>
+      </c>
+      <c r="BA160">
+        <v>2</v>
+      </c>
+      <c r="BB160">
+        <v>6</v>
+      </c>
+      <c r="BC160">
+        <v>8</v>
+      </c>
+      <c r="BD160">
+        <v>3.36</v>
+      </c>
+      <c r="BE160">
+        <v>6.95</v>
+      </c>
+      <c r="BF160">
+        <v>1.53</v>
+      </c>
+      <c r="BG160">
+        <v>1.19</v>
+      </c>
+      <c r="BH160">
+        <v>3.76</v>
+      </c>
+      <c r="BI160">
+        <v>1.48</v>
+      </c>
+      <c r="BJ160">
+        <v>2.51</v>
+      </c>
+      <c r="BK160">
+        <v>1.76</v>
+      </c>
+      <c r="BL160">
+        <v>2.02</v>
+      </c>
+      <c r="BM160">
+        <v>2.2</v>
+      </c>
+      <c r="BN160">
+        <v>1.64</v>
+      </c>
+      <c r="BO160">
+        <v>2.83</v>
+      </c>
+      <c r="BP160">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="284">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -589,6 +589,24 @@
     <t>['27', '90', '90+4']</t>
   </si>
   <si>
+    <t>['48']</t>
+  </si>
+  <si>
+    <t>['39']</t>
+  </si>
+  <si>
+    <t>['37', '62']</t>
+  </si>
+  <si>
+    <t>['2', '30', '69']</t>
+  </si>
+  <si>
+    <t>['51', '67']</t>
+  </si>
+  <si>
+    <t>['3']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -839,6 +857,15 @@
   </si>
   <si>
     <t>['48', '68', '76']</t>
+  </si>
+  <si>
+    <t>['13', '23']</t>
+  </si>
+  <si>
+    <t>['26', '48', '53', '60']</t>
+  </si>
+  <si>
+    <t>['48', '63']</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1456,7 +1483,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1534,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ2">
         <v>1.7</v>
@@ -1662,7 +1689,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1740,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ3">
         <v>1.1</v>
@@ -1868,7 +1895,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -1946,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ4">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2074,7 +2101,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2155,7 +2182,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2358,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ6">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2564,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ7">
         <v>0.45</v>
@@ -2773,7 +2800,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ8">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -2979,7 +3006,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ9">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3182,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10">
         <v>0.5</v>
@@ -3310,7 +3337,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3388,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ11">
         <v>1.44</v>
@@ -3516,7 +3543,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3597,7 +3624,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ12">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4340,7 +4367,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4421,7 +4448,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ16">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4546,7 +4573,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4752,7 +4779,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4830,10 +4857,10 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ18">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR18">
         <v>1.17</v>
@@ -4958,7 +4985,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5036,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ19">
         <v>0.67</v>
@@ -5164,7 +5191,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5242,7 +5269,7 @@
         <v>3</v>
       </c>
       <c r="AP20">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ20">
         <v>1.7</v>
@@ -5370,7 +5397,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5451,7 +5478,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ21">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR21">
         <v>1.86</v>
@@ -5576,7 +5603,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5654,10 +5681,10 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ22">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR22">
         <v>1.76</v>
@@ -5860,7 +5887,7 @@
         <v>1</v>
       </c>
       <c r="AP23">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ23">
         <v>0.45</v>
@@ -5988,7 +6015,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6069,7 +6096,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ24">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR24">
         <v>1.2</v>
@@ -6194,7 +6221,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6400,7 +6427,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6606,7 +6633,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6893,7 +6920,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ28">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR28">
         <v>1.55</v>
@@ -7018,7 +7045,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7096,10 +7123,10 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ29">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR29">
         <v>1.46</v>
@@ -7224,7 +7251,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7302,7 +7329,7 @@
         <v>0</v>
       </c>
       <c r="AP30">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ30">
         <v>0.5</v>
@@ -7430,7 +7457,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7511,7 +7538,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ31">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR31">
         <v>0.93</v>
@@ -8048,7 +8075,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8126,10 +8153,10 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR34">
         <v>1.46</v>
@@ -8254,7 +8281,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8332,10 +8359,10 @@
         <v>2</v>
       </c>
       <c r="AP35">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ35">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR35">
         <v>1.62</v>
@@ -8460,7 +8487,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8538,10 +8565,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ36">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR36">
         <v>1.65</v>
@@ -8666,7 +8693,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8744,10 +8771,10 @@
         <v>1.5</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ37">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR37">
         <v>1.32</v>
@@ -8872,7 +8899,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -8953,7 +8980,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ38">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR38">
         <v>0.95</v>
@@ -9156,7 +9183,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ39">
         <v>0.67</v>
@@ -9284,7 +9311,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9362,10 +9389,10 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ40">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR40">
         <v>1.6</v>
@@ -9490,7 +9517,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9568,10 +9595,10 @@
         <v>3</v>
       </c>
       <c r="AP41">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ41">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR41">
         <v>0.9</v>
@@ -9696,7 +9723,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10108,7 +10135,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10314,7 +10341,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10392,10 +10419,10 @@
         <v>1.67</v>
       </c>
       <c r="AP45">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ45">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR45">
         <v>0.9399999999999999</v>
@@ -10520,7 +10547,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10601,7 +10628,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ46">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR46">
         <v>1.15</v>
@@ -10726,7 +10753,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10804,10 +10831,10 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ47">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR47">
         <v>1.13</v>
@@ -10932,7 +10959,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11010,10 +11037,10 @@
         <v>3</v>
       </c>
       <c r="AP48">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ48">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR48">
         <v>1.3</v>
@@ -11216,10 +11243,10 @@
         <v>1.33</v>
       </c>
       <c r="AP49">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR49">
         <v>1.42</v>
@@ -11422,10 +11449,10 @@
         <v>0.33</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ50">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR50">
         <v>1.26</v>
@@ -11550,7 +11577,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11628,10 +11655,10 @@
         <v>3</v>
       </c>
       <c r="AP51">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ51">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR51">
         <v>1.65</v>
@@ -11756,7 +11783,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11834,7 +11861,7 @@
         <v>1</v>
       </c>
       <c r="AP52">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ52">
         <v>0.67</v>
@@ -12168,7 +12195,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12452,7 +12479,7 @@
         <v>2.33</v>
       </c>
       <c r="AP55">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ55">
         <v>1.27</v>
@@ -12580,7 +12607,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12786,7 +12813,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12992,7 +13019,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13073,7 +13100,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ58">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR58">
         <v>1.23</v>
@@ -13610,7 +13637,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -14022,7 +14049,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14434,7 +14461,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14512,7 +14539,7 @@
         <v>0.25</v>
       </c>
       <c r="AP65">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ65">
         <v>0.45</v>
@@ -14640,7 +14667,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14718,7 +14745,7 @@
         <v>3</v>
       </c>
       <c r="AP66">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ66">
         <v>2.3</v>
@@ -14846,7 +14873,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15052,7 +15079,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15133,7 +15160,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ68">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR68">
         <v>1.14</v>
@@ -15336,10 +15363,10 @@
         <v>3</v>
       </c>
       <c r="AP69">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ69">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR69">
         <v>1.58</v>
@@ -15545,7 +15572,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ70">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR70">
         <v>1.74</v>
@@ -15670,7 +15697,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15751,7 +15778,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ71">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR71">
         <v>1.24</v>
@@ -15954,7 +15981,7 @@
         <v>2</v>
       </c>
       <c r="AP72">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ72">
         <v>1.27</v>
@@ -16366,10 +16393,10 @@
         <v>3</v>
       </c>
       <c r="AP74">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ74">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR74">
         <v>1.42</v>
@@ -16494,7 +16521,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16575,7 +16602,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ75">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR75">
         <v>1.29</v>
@@ -16700,7 +16727,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16781,7 +16808,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ76">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR76">
         <v>1.4</v>
@@ -16906,7 +16933,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -16984,7 +17011,7 @@
         <v>0.5</v>
       </c>
       <c r="AP77">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ77">
         <v>1.1</v>
@@ -17112,7 +17139,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17190,7 +17217,7 @@
         <v>1.75</v>
       </c>
       <c r="AP78">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ78">
         <v>1.7</v>
@@ -17318,7 +17345,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17399,7 +17426,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ79">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR79">
         <v>0.98</v>
@@ -17602,7 +17629,7 @@
         <v>1.25</v>
       </c>
       <c r="AP80">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ80">
         <v>1.1</v>
@@ -17730,7 +17757,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -17808,10 +17835,10 @@
         <v>0.8</v>
       </c>
       <c r="AP81">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR81">
         <v>1.61</v>
@@ -18017,7 +18044,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ82">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR82">
         <v>1.24</v>
@@ -18426,7 +18453,7 @@
         <v>0.5</v>
       </c>
       <c r="AP84">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ84">
         <v>0.5</v>
@@ -18554,7 +18581,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18760,7 +18787,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19172,7 +19199,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19253,7 +19280,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ88">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR88">
         <v>1.25</v>
@@ -19378,7 +19405,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19584,7 +19611,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19665,7 +19692,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ90">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR90">
         <v>1.43</v>
@@ -19868,10 +19895,10 @@
         <v>2.6</v>
       </c>
       <c r="AP91">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ91">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR91">
         <v>1.44</v>
@@ -19996,7 +20023,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20074,7 +20101,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ92">
         <v>1.1</v>
@@ -20202,7 +20229,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20280,7 +20307,7 @@
         <v>2</v>
       </c>
       <c r="AP93">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ93">
         <v>1.44</v>
@@ -20408,7 +20435,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20489,7 +20516,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ94">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR94">
         <v>1.93</v>
@@ -20614,7 +20641,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20692,7 +20719,7 @@
         <v>1.2</v>
       </c>
       <c r="AP95">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ95">
         <v>0.67</v>
@@ -21026,7 +21053,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21310,7 +21337,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ98">
         <v>0.45</v>
@@ -21438,7 +21465,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21516,10 +21543,10 @@
         <v>2</v>
       </c>
       <c r="AP99">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ99">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR99">
         <v>1.1</v>
@@ -21644,7 +21671,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21725,7 +21752,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ100">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR100">
         <v>1.75</v>
@@ -21850,7 +21877,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -21931,7 +21958,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ101">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR101">
         <v>1.23</v>
@@ -22262,7 +22289,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22343,7 +22370,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ103">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR103">
         <v>1.49</v>
@@ -22468,7 +22495,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22546,7 +22573,7 @@
         <v>2.4</v>
       </c>
       <c r="AP104">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ104">
         <v>2.3</v>
@@ -22752,10 +22779,10 @@
         <v>1.17</v>
       </c>
       <c r="AP105">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ105">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR105">
         <v>1.61</v>
@@ -22880,7 +22907,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23086,7 +23113,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23167,7 +23194,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ107">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR107">
         <v>1.93</v>
@@ -23292,7 +23319,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23370,7 +23397,7 @@
         <v>2.17</v>
       </c>
       <c r="AP108">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ108">
         <v>1.7</v>
@@ -23498,7 +23525,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23576,10 +23603,10 @@
         <v>1.29</v>
       </c>
       <c r="AP109">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ109">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR109">
         <v>1.43</v>
@@ -23785,7 +23812,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ110">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR110">
         <v>1.28</v>
@@ -24194,7 +24221,7 @@
         <v>2.17</v>
       </c>
       <c r="AP112">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ112">
         <v>1.44</v>
@@ -24400,7 +24427,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ113">
         <v>0.5</v>
@@ -24812,7 +24839,7 @@
         <v>1.71</v>
       </c>
       <c r="AP115">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ115">
         <v>1.27</v>
@@ -24940,7 +24967,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25018,10 +25045,10 @@
         <v>1.14</v>
       </c>
       <c r="AP116">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ116">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR116">
         <v>1.11</v>
@@ -25433,7 +25460,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ118">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR118">
         <v>1.23</v>
@@ -25558,7 +25585,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25636,7 +25663,7 @@
         <v>1.33</v>
       </c>
       <c r="AP119">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ119">
         <v>1.1</v>
@@ -25845,7 +25872,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ120">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR120">
         <v>1.33</v>
@@ -26051,7 +26078,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ121">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR121">
         <v>1.76</v>
@@ -26176,7 +26203,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26254,7 +26281,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ122">
         <v>1.1</v>
@@ -26588,7 +26615,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26669,7 +26696,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ124">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR124">
         <v>1.35</v>
@@ -26794,7 +26821,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27000,7 +27027,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27206,7 +27233,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27284,7 +27311,7 @@
         <v>1.5</v>
       </c>
       <c r="AP127">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ127">
         <v>1.27</v>
@@ -27412,7 +27439,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27493,7 +27520,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ128">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR128">
         <v>1.75</v>
@@ -27618,7 +27645,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27824,7 +27851,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -27902,10 +27929,10 @@
         <v>1.88</v>
       </c>
       <c r="AP130">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ130">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR130">
         <v>1.29</v>
@@ -28108,7 +28135,7 @@
         <v>1.57</v>
       </c>
       <c r="AP131">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ131">
         <v>1.1</v>
@@ -28236,7 +28263,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28317,7 +28344,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ132">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR132">
         <v>1.23</v>
@@ -28442,7 +28469,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28520,7 +28547,7 @@
         <v>2.29</v>
       </c>
       <c r="AP133">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ133">
         <v>1.7</v>
@@ -28726,7 +28753,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ134">
         <v>0.45</v>
@@ -28935,7 +28962,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ135">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR135">
         <v>1.26</v>
@@ -29141,7 +29168,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ136">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR136">
         <v>1.11</v>
@@ -29266,7 +29293,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29344,10 +29371,10 @@
         <v>1.43</v>
       </c>
       <c r="AP137">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ137">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR137">
         <v>1.29</v>
@@ -29550,10 +29577,10 @@
         <v>2</v>
       </c>
       <c r="AP138">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AQ138">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AR138">
         <v>1.61</v>
@@ -29678,7 +29705,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -29756,7 +29783,7 @@
         <v>2.38</v>
       </c>
       <c r="AP139">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AQ139">
         <v>2.3</v>
@@ -30090,7 +30117,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30583,7 +30610,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ143">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AR143">
         <v>1.39</v>
@@ -30789,7 +30816,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ144">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR144">
         <v>1.3</v>
@@ -30992,7 +31019,7 @@
         <v>0.75</v>
       </c>
       <c r="AP145">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AQ145">
         <v>0.67</v>
@@ -31120,7 +31147,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31198,7 +31225,7 @@
         <v>0.44</v>
       </c>
       <c r="AP146">
-        <v>0.9</v>
+        <v>1.09</v>
       </c>
       <c r="AQ146">
         <v>0.45</v>
@@ -31326,7 +31353,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31407,7 +31434,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ147">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR147">
         <v>1.42</v>
@@ -31610,10 +31637,10 @@
         <v>1.22</v>
       </c>
       <c r="AP148">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ148">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR148">
         <v>1.35</v>
@@ -31738,7 +31765,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31816,10 +31843,10 @@
         <v>1.25</v>
       </c>
       <c r="AP149">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AQ149">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR149">
         <v>1.38</v>
@@ -31944,7 +31971,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32150,7 +32177,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32434,10 +32461,10 @@
         <v>2.44</v>
       </c>
       <c r="AP152">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AR152">
         <v>1.56</v>
@@ -32562,7 +32589,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32768,7 +32795,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -32974,7 +33001,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33592,7 +33619,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -34161,6 +34188,1448 @@
       </c>
       <c r="BP160">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="161" spans="1:68">
+      <c r="A161" s="1">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>7484701</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" t="s">
+        <v>69</v>
+      </c>
+      <c r="E161" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F161">
+        <v>21</v>
+      </c>
+      <c r="G161" t="s">
+        <v>75</v>
+      </c>
+      <c r="H161" t="s">
+        <v>80</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>2</v>
+      </c>
+      <c r="K161">
+        <v>2</v>
+      </c>
+      <c r="L161">
+        <v>1</v>
+      </c>
+      <c r="M161">
+        <v>2</v>
+      </c>
+      <c r="N161">
+        <v>3</v>
+      </c>
+      <c r="O161" t="s">
+        <v>191</v>
+      </c>
+      <c r="P161" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q161">
+        <v>3</v>
+      </c>
+      <c r="R161">
+        <v>2.05</v>
+      </c>
+      <c r="S161">
+        <v>3.6</v>
+      </c>
+      <c r="T161">
+        <v>1.44</v>
+      </c>
+      <c r="U161">
+        <v>2.63</v>
+      </c>
+      <c r="V161">
+        <v>3.25</v>
+      </c>
+      <c r="W161">
+        <v>1.33</v>
+      </c>
+      <c r="X161">
+        <v>7.5</v>
+      </c>
+      <c r="Y161">
+        <v>1.07</v>
+      </c>
+      <c r="Z161">
+        <v>2.25</v>
+      </c>
+      <c r="AA161">
+        <v>3.2</v>
+      </c>
+      <c r="AB161">
+        <v>3</v>
+      </c>
+      <c r="AC161">
+        <v>0</v>
+      </c>
+      <c r="AD161">
+        <v>0</v>
+      </c>
+      <c r="AE161">
+        <v>0</v>
+      </c>
+      <c r="AF161">
+        <v>0</v>
+      </c>
+      <c r="AG161">
+        <v>2.1</v>
+      </c>
+      <c r="AH161">
+        <v>1.7</v>
+      </c>
+      <c r="AI161">
+        <v>1.83</v>
+      </c>
+      <c r="AJ161">
+        <v>1.83</v>
+      </c>
+      <c r="AK161">
+        <v>0</v>
+      </c>
+      <c r="AL161">
+        <v>0</v>
+      </c>
+      <c r="AM161">
+        <v>0</v>
+      </c>
+      <c r="AN161">
+        <v>1</v>
+      </c>
+      <c r="AO161">
+        <v>1.4</v>
+      </c>
+      <c r="AP161">
+        <v>0.9</v>
+      </c>
+      <c r="AQ161">
+        <v>1.55</v>
+      </c>
+      <c r="AR161">
+        <v>1.26</v>
+      </c>
+      <c r="AS161">
+        <v>1.14</v>
+      </c>
+      <c r="AT161">
+        <v>2.4</v>
+      </c>
+      <c r="AU161">
+        <v>4</v>
+      </c>
+      <c r="AV161">
+        <v>5</v>
+      </c>
+      <c r="AW161">
+        <v>6</v>
+      </c>
+      <c r="AX161">
+        <v>3</v>
+      </c>
+      <c r="AY161">
+        <v>10</v>
+      </c>
+      <c r="AZ161">
+        <v>10</v>
+      </c>
+      <c r="BA161">
+        <v>5</v>
+      </c>
+      <c r="BB161">
+        <v>3</v>
+      </c>
+      <c r="BC161">
+        <v>8</v>
+      </c>
+      <c r="BD161">
+        <v>0</v>
+      </c>
+      <c r="BE161">
+        <v>0</v>
+      </c>
+      <c r="BF161">
+        <v>0</v>
+      </c>
+      <c r="BG161">
+        <v>0</v>
+      </c>
+      <c r="BH161">
+        <v>0</v>
+      </c>
+      <c r="BI161">
+        <v>0</v>
+      </c>
+      <c r="BJ161">
+        <v>0</v>
+      </c>
+      <c r="BK161">
+        <v>2.38</v>
+      </c>
+      <c r="BL161">
+        <v>0</v>
+      </c>
+      <c r="BM161">
+        <v>0</v>
+      </c>
+      <c r="BN161">
+        <v>0</v>
+      </c>
+      <c r="BO161">
+        <v>0</v>
+      </c>
+      <c r="BP161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:68">
+      <c r="A162" s="1">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>7484700</v>
+      </c>
+      <c r="C162" t="s">
+        <v>68</v>
+      </c>
+      <c r="D162" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F162">
+        <v>21</v>
+      </c>
+      <c r="G162" t="s">
+        <v>79</v>
+      </c>
+      <c r="H162" t="s">
+        <v>83</v>
+      </c>
+      <c r="I162">
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>1</v>
+      </c>
+      <c r="K162">
+        <v>2</v>
+      </c>
+      <c r="L162">
+        <v>1</v>
+      </c>
+      <c r="M162">
+        <v>4</v>
+      </c>
+      <c r="N162">
+        <v>5</v>
+      </c>
+      <c r="O162" t="s">
+        <v>192</v>
+      </c>
+      <c r="P162" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q162">
+        <v>3.2</v>
+      </c>
+      <c r="R162">
+        <v>2.38</v>
+      </c>
+      <c r="S162">
+        <v>2.75</v>
+      </c>
+      <c r="T162">
+        <v>1.29</v>
+      </c>
+      <c r="U162">
+        <v>3.5</v>
+      </c>
+      <c r="V162">
+        <v>2.25</v>
+      </c>
+      <c r="W162">
+        <v>1.57</v>
+      </c>
+      <c r="X162">
+        <v>5</v>
+      </c>
+      <c r="Y162">
+        <v>1.14</v>
+      </c>
+      <c r="Z162">
+        <v>2.75</v>
+      </c>
+      <c r="AA162">
+        <v>3.7</v>
+      </c>
+      <c r="AB162">
+        <v>2.2</v>
+      </c>
+      <c r="AC162">
+        <v>0</v>
+      </c>
+      <c r="AD162">
+        <v>0</v>
+      </c>
+      <c r="AE162">
+        <v>0</v>
+      </c>
+      <c r="AF162">
+        <v>0</v>
+      </c>
+      <c r="AG162">
+        <v>1.57</v>
+      </c>
+      <c r="AH162">
+        <v>2.35</v>
+      </c>
+      <c r="AI162">
+        <v>1.5</v>
+      </c>
+      <c r="AJ162">
+        <v>2.5</v>
+      </c>
+      <c r="AK162">
+        <v>0</v>
+      </c>
+      <c r="AL162">
+        <v>0</v>
+      </c>
+      <c r="AM162">
+        <v>0</v>
+      </c>
+      <c r="AN162">
+        <v>0.67</v>
+      </c>
+      <c r="AO162">
+        <v>1.11</v>
+      </c>
+      <c r="AP162">
+        <v>0.6</v>
+      </c>
+      <c r="AQ162">
+        <v>1.3</v>
+      </c>
+      <c r="AR162">
+        <v>1.33</v>
+      </c>
+      <c r="AS162">
+        <v>1.28</v>
+      </c>
+      <c r="AT162">
+        <v>2.61</v>
+      </c>
+      <c r="AU162">
+        <v>6</v>
+      </c>
+      <c r="AV162">
+        <v>6</v>
+      </c>
+      <c r="AW162">
+        <v>12</v>
+      </c>
+      <c r="AX162">
+        <v>1</v>
+      </c>
+      <c r="AY162">
+        <v>20</v>
+      </c>
+      <c r="AZ162">
+        <v>8</v>
+      </c>
+      <c r="BA162">
+        <v>7</v>
+      </c>
+      <c r="BB162">
+        <v>1</v>
+      </c>
+      <c r="BC162">
+        <v>8</v>
+      </c>
+      <c r="BD162">
+        <v>0</v>
+      </c>
+      <c r="BE162">
+        <v>0</v>
+      </c>
+      <c r="BF162">
+        <v>0</v>
+      </c>
+      <c r="BG162">
+        <v>0</v>
+      </c>
+      <c r="BH162">
+        <v>0</v>
+      </c>
+      <c r="BI162">
+        <v>0</v>
+      </c>
+      <c r="BJ162">
+        <v>0</v>
+      </c>
+      <c r="BK162">
+        <v>2.1</v>
+      </c>
+      <c r="BL162">
+        <v>0</v>
+      </c>
+      <c r="BM162">
+        <v>0</v>
+      </c>
+      <c r="BN162">
+        <v>0</v>
+      </c>
+      <c r="BO162">
+        <v>0</v>
+      </c>
+      <c r="BP162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:68">
+      <c r="A163" s="1">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>7484699</v>
+      </c>
+      <c r="C163" t="s">
+        <v>68</v>
+      </c>
+      <c r="D163" t="s">
+        <v>69</v>
+      </c>
+      <c r="E163" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F163">
+        <v>21</v>
+      </c>
+      <c r="G163" t="s">
+        <v>72</v>
+      </c>
+      <c r="H163" t="s">
+        <v>76</v>
+      </c>
+      <c r="I163">
+        <v>1</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+      <c r="K163">
+        <v>2</v>
+      </c>
+      <c r="L163">
+        <v>2</v>
+      </c>
+      <c r="M163">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>3</v>
+      </c>
+      <c r="O163" t="s">
+        <v>193</v>
+      </c>
+      <c r="P163" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q163">
+        <v>2.88</v>
+      </c>
+      <c r="R163">
+        <v>2.2</v>
+      </c>
+      <c r="S163">
+        <v>3.25</v>
+      </c>
+      <c r="T163">
+        <v>1.33</v>
+      </c>
+      <c r="U163">
+        <v>3.25</v>
+      </c>
+      <c r="V163">
+        <v>2.63</v>
+      </c>
+      <c r="W163">
+        <v>1.44</v>
+      </c>
+      <c r="X163">
+        <v>6</v>
+      </c>
+      <c r="Y163">
+        <v>1.11</v>
+      </c>
+      <c r="Z163">
+        <v>2.38</v>
+      </c>
+      <c r="AA163">
+        <v>3.47</v>
+      </c>
+      <c r="AB163">
+        <v>2.8</v>
+      </c>
+      <c r="AC163">
+        <v>0</v>
+      </c>
+      <c r="AD163">
+        <v>0</v>
+      </c>
+      <c r="AE163">
+        <v>0</v>
+      </c>
+      <c r="AF163">
+        <v>0</v>
+      </c>
+      <c r="AG163">
+        <v>1.75</v>
+      </c>
+      <c r="AH163">
+        <v>2.05</v>
+      </c>
+      <c r="AI163">
+        <v>1.62</v>
+      </c>
+      <c r="AJ163">
+        <v>2.2</v>
+      </c>
+      <c r="AK163">
+        <v>0</v>
+      </c>
+      <c r="AL163">
+        <v>0</v>
+      </c>
+      <c r="AM163">
+        <v>0</v>
+      </c>
+      <c r="AN163">
+        <v>0.9</v>
+      </c>
+      <c r="AO163">
+        <v>1.3</v>
+      </c>
+      <c r="AP163">
+        <v>1.09</v>
+      </c>
+      <c r="AQ163">
+        <v>1.18</v>
+      </c>
+      <c r="AR163">
+        <v>1.17</v>
+      </c>
+      <c r="AS163">
+        <v>1.54</v>
+      </c>
+      <c r="AT163">
+        <v>2.71</v>
+      </c>
+      <c r="AU163">
+        <v>4</v>
+      </c>
+      <c r="AV163">
+        <v>3</v>
+      </c>
+      <c r="AW163">
+        <v>5</v>
+      </c>
+      <c r="AX163">
+        <v>7</v>
+      </c>
+      <c r="AY163">
+        <v>9</v>
+      </c>
+      <c r="AZ163">
+        <v>13</v>
+      </c>
+      <c r="BA163">
+        <v>6</v>
+      </c>
+      <c r="BB163">
+        <v>6</v>
+      </c>
+      <c r="BC163">
+        <v>12</v>
+      </c>
+      <c r="BD163">
+        <v>0</v>
+      </c>
+      <c r="BE163">
+        <v>0</v>
+      </c>
+      <c r="BF163">
+        <v>0</v>
+      </c>
+      <c r="BG163">
+        <v>0</v>
+      </c>
+      <c r="BH163">
+        <v>0</v>
+      </c>
+      <c r="BI163">
+        <v>0</v>
+      </c>
+      <c r="BJ163">
+        <v>0</v>
+      </c>
+      <c r="BK163">
+        <v>2.1</v>
+      </c>
+      <c r="BL163">
+        <v>0</v>
+      </c>
+      <c r="BM163">
+        <v>0</v>
+      </c>
+      <c r="BN163">
+        <v>0</v>
+      </c>
+      <c r="BO163">
+        <v>0</v>
+      </c>
+      <c r="BP163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:68">
+      <c r="A164" s="1">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>7484697</v>
+      </c>
+      <c r="C164" t="s">
+        <v>68</v>
+      </c>
+      <c r="D164" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F164">
+        <v>21</v>
+      </c>
+      <c r="G164" t="s">
+        <v>71</v>
+      </c>
+      <c r="H164" t="s">
+        <v>81</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>1</v>
+      </c>
+      <c r="O164" t="s">
+        <v>86</v>
+      </c>
+      <c r="P164" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q164">
+        <v>4.75</v>
+      </c>
+      <c r="R164">
+        <v>2.2</v>
+      </c>
+      <c r="S164">
+        <v>2.25</v>
+      </c>
+      <c r="T164">
+        <v>1.4</v>
+      </c>
+      <c r="U164">
+        <v>2.75</v>
+      </c>
+      <c r="V164">
+        <v>2.75</v>
+      </c>
+      <c r="W164">
+        <v>1.4</v>
+      </c>
+      <c r="X164">
+        <v>6.5</v>
+      </c>
+      <c r="Y164">
+        <v>1.1</v>
+      </c>
+      <c r="Z164">
+        <v>4.33</v>
+      </c>
+      <c r="AA164">
+        <v>3.9</v>
+      </c>
+      <c r="AB164">
+        <v>1.67</v>
+      </c>
+      <c r="AC164">
+        <v>0</v>
+      </c>
+      <c r="AD164">
+        <v>0</v>
+      </c>
+      <c r="AE164">
+        <v>2.81</v>
+      </c>
+      <c r="AF164">
+        <v>1.42</v>
+      </c>
+      <c r="AG164">
+        <v>1.85</v>
+      </c>
+      <c r="AH164">
+        <v>1.95</v>
+      </c>
+      <c r="AI164">
+        <v>1.83</v>
+      </c>
+      <c r="AJ164">
+        <v>1.83</v>
+      </c>
+      <c r="AK164">
+        <v>0</v>
+      </c>
+      <c r="AL164">
+        <v>0</v>
+      </c>
+      <c r="AM164">
+        <v>0</v>
+      </c>
+      <c r="AN164">
+        <v>1.2</v>
+      </c>
+      <c r="AO164">
+        <v>2.2</v>
+      </c>
+      <c r="AP164">
+        <v>1.09</v>
+      </c>
+      <c r="AQ164">
+        <v>2.27</v>
+      </c>
+      <c r="AR164">
+        <v>1.46</v>
+      </c>
+      <c r="AS164">
+        <v>1.61</v>
+      </c>
+      <c r="AT164">
+        <v>3.07</v>
+      </c>
+      <c r="AU164">
+        <v>3</v>
+      </c>
+      <c r="AV164">
+        <v>6</v>
+      </c>
+      <c r="AW164">
+        <v>3</v>
+      </c>
+      <c r="AX164">
+        <v>5</v>
+      </c>
+      <c r="AY164">
+        <v>6</v>
+      </c>
+      <c r="AZ164">
+        <v>12</v>
+      </c>
+      <c r="BA164">
+        <v>1</v>
+      </c>
+      <c r="BB164">
+        <v>4</v>
+      </c>
+      <c r="BC164">
+        <v>5</v>
+      </c>
+      <c r="BD164">
+        <v>0</v>
+      </c>
+      <c r="BE164">
+        <v>0</v>
+      </c>
+      <c r="BF164">
+        <v>0</v>
+      </c>
+      <c r="BG164">
+        <v>0</v>
+      </c>
+      <c r="BH164">
+        <v>0</v>
+      </c>
+      <c r="BI164">
+        <v>0</v>
+      </c>
+      <c r="BJ164">
+        <v>0</v>
+      </c>
+      <c r="BK164">
+        <v>0</v>
+      </c>
+      <c r="BL164">
+        <v>0</v>
+      </c>
+      <c r="BM164">
+        <v>0</v>
+      </c>
+      <c r="BN164">
+        <v>0</v>
+      </c>
+      <c r="BO164">
+        <v>0</v>
+      </c>
+      <c r="BP164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:68">
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>7484696</v>
+      </c>
+      <c r="C165" t="s">
+        <v>68</v>
+      </c>
+      <c r="D165" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F165">
+        <v>21</v>
+      </c>
+      <c r="G165" t="s">
+        <v>70</v>
+      </c>
+      <c r="H165" t="s">
+        <v>77</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>2</v>
+      </c>
+      <c r="L165">
+        <v>3</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>3</v>
+      </c>
+      <c r="O165" t="s">
+        <v>194</v>
+      </c>
+      <c r="P165" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q165">
+        <v>2.88</v>
+      </c>
+      <c r="R165">
+        <v>2</v>
+      </c>
+      <c r="S165">
+        <v>3.75</v>
+      </c>
+      <c r="T165">
+        <v>1.44</v>
+      </c>
+      <c r="U165">
+        <v>2.63</v>
+      </c>
+      <c r="V165">
+        <v>3.25</v>
+      </c>
+      <c r="W165">
+        <v>1.33</v>
+      </c>
+      <c r="X165">
+        <v>8</v>
+      </c>
+      <c r="Y165">
+        <v>1.06</v>
+      </c>
+      <c r="Z165">
+        <v>2.15</v>
+      </c>
+      <c r="AA165">
+        <v>3.25</v>
+      </c>
+      <c r="AB165">
+        <v>3.1</v>
+      </c>
+      <c r="AC165">
+        <v>0</v>
+      </c>
+      <c r="AD165">
+        <v>0</v>
+      </c>
+      <c r="AE165">
+        <v>0</v>
+      </c>
+      <c r="AF165">
+        <v>0</v>
+      </c>
+      <c r="AG165">
+        <v>2.08</v>
+      </c>
+      <c r="AH165">
+        <v>1.73</v>
+      </c>
+      <c r="AI165">
+        <v>1.91</v>
+      </c>
+      <c r="AJ165">
+        <v>1.8</v>
+      </c>
+      <c r="AK165">
+        <v>0</v>
+      </c>
+      <c r="AL165">
+        <v>0</v>
+      </c>
+      <c r="AM165">
+        <v>0</v>
+      </c>
+      <c r="AN165">
+        <v>1.2</v>
+      </c>
+      <c r="AO165">
+        <v>0.8</v>
+      </c>
+      <c r="AP165">
+        <v>1.36</v>
+      </c>
+      <c r="AQ165">
+        <v>0.73</v>
+      </c>
+      <c r="AR165">
+        <v>1.59</v>
+      </c>
+      <c r="AS165">
+        <v>1.19</v>
+      </c>
+      <c r="AT165">
+        <v>2.78</v>
+      </c>
+      <c r="AU165">
+        <v>6</v>
+      </c>
+      <c r="AV165">
+        <v>2</v>
+      </c>
+      <c r="AW165">
+        <v>4</v>
+      </c>
+      <c r="AX165">
+        <v>4</v>
+      </c>
+      <c r="AY165">
+        <v>11</v>
+      </c>
+      <c r="AZ165">
+        <v>7</v>
+      </c>
+      <c r="BA165">
+        <v>4</v>
+      </c>
+      <c r="BB165">
+        <v>3</v>
+      </c>
+      <c r="BC165">
+        <v>7</v>
+      </c>
+      <c r="BD165">
+        <v>0</v>
+      </c>
+      <c r="BE165">
+        <v>0</v>
+      </c>
+      <c r="BF165">
+        <v>0</v>
+      </c>
+      <c r="BG165">
+        <v>0</v>
+      </c>
+      <c r="BH165">
+        <v>0</v>
+      </c>
+      <c r="BI165">
+        <v>0</v>
+      </c>
+      <c r="BJ165">
+        <v>0</v>
+      </c>
+      <c r="BK165">
+        <v>2.2</v>
+      </c>
+      <c r="BL165">
+        <v>0</v>
+      </c>
+      <c r="BM165">
+        <v>0</v>
+      </c>
+      <c r="BN165">
+        <v>0</v>
+      </c>
+      <c r="BO165">
+        <v>0</v>
+      </c>
+      <c r="BP165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:68">
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>7484698</v>
+      </c>
+      <c r="C166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D166" t="s">
+        <v>69</v>
+      </c>
+      <c r="E166" s="2">
+        <v>45744.58333333334</v>
+      </c>
+      <c r="F166">
+        <v>21</v>
+      </c>
+      <c r="G166" t="s">
+        <v>78</v>
+      </c>
+      <c r="H166" t="s">
+        <v>84</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>2</v>
+      </c>
+      <c r="M166">
+        <v>2</v>
+      </c>
+      <c r="N166">
+        <v>4</v>
+      </c>
+      <c r="O166" t="s">
+        <v>195</v>
+      </c>
+      <c r="P166" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q166">
+        <v>2.88</v>
+      </c>
+      <c r="R166">
+        <v>2.25</v>
+      </c>
+      <c r="S166">
+        <v>3.2</v>
+      </c>
+      <c r="T166">
+        <v>1.33</v>
+      </c>
+      <c r="U166">
+        <v>3.25</v>
+      </c>
+      <c r="V166">
+        <v>2.5</v>
+      </c>
+      <c r="W166">
+        <v>1.5</v>
+      </c>
+      <c r="X166">
+        <v>6</v>
+      </c>
+      <c r="Y166">
+        <v>1.11</v>
+      </c>
+      <c r="Z166">
+        <v>2.3</v>
+      </c>
+      <c r="AA166">
+        <v>3.4</v>
+      </c>
+      <c r="AB166">
+        <v>2.75</v>
+      </c>
+      <c r="AC166">
+        <v>0</v>
+      </c>
+      <c r="AD166">
+        <v>0</v>
+      </c>
+      <c r="AE166">
+        <v>0</v>
+      </c>
+      <c r="AF166">
+        <v>0</v>
+      </c>
+      <c r="AG166">
+        <v>1.7</v>
+      </c>
+      <c r="AH166">
+        <v>2.1</v>
+      </c>
+      <c r="AI166">
+        <v>1.57</v>
+      </c>
+      <c r="AJ166">
+        <v>2.25</v>
+      </c>
+      <c r="AK166">
+        <v>0</v>
+      </c>
+      <c r="AL166">
+        <v>0</v>
+      </c>
+      <c r="AM166">
+        <v>0</v>
+      </c>
+      <c r="AN166">
+        <v>1.6</v>
+      </c>
+      <c r="AO166">
+        <v>1.1</v>
+      </c>
+      <c r="AP166">
+        <v>1.55</v>
+      </c>
+      <c r="AQ166">
+        <v>1.09</v>
+      </c>
+      <c r="AR166">
+        <v>1.64</v>
+      </c>
+      <c r="AS166">
+        <v>1.53</v>
+      </c>
+      <c r="AT166">
+        <v>3.17</v>
+      </c>
+      <c r="AU166">
+        <v>10</v>
+      </c>
+      <c r="AV166">
+        <v>4</v>
+      </c>
+      <c r="AW166">
+        <v>8</v>
+      </c>
+      <c r="AX166">
+        <v>7</v>
+      </c>
+      <c r="AY166">
+        <v>20</v>
+      </c>
+      <c r="AZ166">
+        <v>13</v>
+      </c>
+      <c r="BA166">
+        <v>8</v>
+      </c>
+      <c r="BB166">
+        <v>5</v>
+      </c>
+      <c r="BC166">
+        <v>13</v>
+      </c>
+      <c r="BD166">
+        <v>0</v>
+      </c>
+      <c r="BE166">
+        <v>0</v>
+      </c>
+      <c r="BF166">
+        <v>0</v>
+      </c>
+      <c r="BG166">
+        <v>0</v>
+      </c>
+      <c r="BH166">
+        <v>0</v>
+      </c>
+      <c r="BI166">
+        <v>0</v>
+      </c>
+      <c r="BJ166">
+        <v>0</v>
+      </c>
+      <c r="BK166">
+        <v>2.1</v>
+      </c>
+      <c r="BL166">
+        <v>0</v>
+      </c>
+      <c r="BM166">
+        <v>0</v>
+      </c>
+      <c r="BN166">
+        <v>0</v>
+      </c>
+      <c r="BO166">
+        <v>0</v>
+      </c>
+      <c r="BP166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:68">
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>7484702</v>
+      </c>
+      <c r="C167" t="s">
+        <v>68</v>
+      </c>
+      <c r="D167" t="s">
+        <v>69</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45744.6875</v>
+      </c>
+      <c r="F167">
+        <v>21</v>
+      </c>
+      <c r="G167" t="s">
+        <v>74</v>
+      </c>
+      <c r="H167" t="s">
+        <v>82</v>
+      </c>
+      <c r="I167">
+        <v>1</v>
+      </c>
+      <c r="J167">
+        <v>1</v>
+      </c>
+      <c r="K167">
+        <v>2</v>
+      </c>
+      <c r="L167">
+        <v>1</v>
+      </c>
+      <c r="M167">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>2</v>
+      </c>
+      <c r="O167" t="s">
+        <v>196</v>
+      </c>
+      <c r="P167" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q167">
+        <v>2.75</v>
+      </c>
+      <c r="R167">
+        <v>2.1</v>
+      </c>
+      <c r="S167">
+        <v>3.75</v>
+      </c>
+      <c r="T167">
+        <v>1.4</v>
+      </c>
+      <c r="U167">
+        <v>2.75</v>
+      </c>
+      <c r="V167">
+        <v>3</v>
+      </c>
+      <c r="W167">
+        <v>1.36</v>
+      </c>
+      <c r="X167">
+        <v>7</v>
+      </c>
+      <c r="Y167">
+        <v>1.08</v>
+      </c>
+      <c r="Z167">
+        <v>2.15</v>
+      </c>
+      <c r="AA167">
+        <v>3.3</v>
+      </c>
+      <c r="AB167">
+        <v>3.1</v>
+      </c>
+      <c r="AC167">
+        <v>0</v>
+      </c>
+      <c r="AD167">
+        <v>0</v>
+      </c>
+      <c r="AE167">
+        <v>0</v>
+      </c>
+      <c r="AF167">
+        <v>0</v>
+      </c>
+      <c r="AG167">
+        <v>2</v>
+      </c>
+      <c r="AH167">
+        <v>1.8</v>
+      </c>
+      <c r="AI167">
+        <v>1.8</v>
+      </c>
+      <c r="AJ167">
+        <v>1.91</v>
+      </c>
+      <c r="AK167">
+        <v>0</v>
+      </c>
+      <c r="AL167">
+        <v>0</v>
+      </c>
+      <c r="AM167">
+        <v>0</v>
+      </c>
+      <c r="AN167">
+        <v>2.5</v>
+      </c>
+      <c r="AO167">
+        <v>1.9</v>
+      </c>
+      <c r="AP167">
+        <v>2.36</v>
+      </c>
+      <c r="AQ167">
+        <v>1.82</v>
+      </c>
+      <c r="AR167">
+        <v>1.46</v>
+      </c>
+      <c r="AS167">
+        <v>1.56</v>
+      </c>
+      <c r="AT167">
+        <v>3.02</v>
+      </c>
+      <c r="AU167">
+        <v>3</v>
+      </c>
+      <c r="AV167">
+        <v>3</v>
+      </c>
+      <c r="AW167">
+        <v>7</v>
+      </c>
+      <c r="AX167">
+        <v>5</v>
+      </c>
+      <c r="AY167">
+        <v>10</v>
+      </c>
+      <c r="AZ167">
+        <v>9</v>
+      </c>
+      <c r="BA167">
+        <v>2</v>
+      </c>
+      <c r="BB167">
+        <v>3</v>
+      </c>
+      <c r="BC167">
+        <v>5</v>
+      </c>
+      <c r="BD167">
+        <v>0</v>
+      </c>
+      <c r="BE167">
+        <v>0</v>
+      </c>
+      <c r="BF167">
+        <v>0</v>
+      </c>
+      <c r="BG167">
+        <v>0</v>
+      </c>
+      <c r="BH167">
+        <v>0</v>
+      </c>
+      <c r="BI167">
+        <v>0</v>
+      </c>
+      <c r="BJ167">
+        <v>0</v>
+      </c>
+      <c r="BK167">
+        <v>0</v>
+      </c>
+      <c r="BL167">
+        <v>0</v>
+      </c>
+      <c r="BM167">
+        <v>0</v>
+      </c>
+      <c r="BN167">
+        <v>0</v>
+      </c>
+      <c r="BO167">
+        <v>0</v>
+      </c>
+      <c r="BP167">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="285">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>['3']</t>
+  </si>
+  <si>
+    <t>['28']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1227,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP167"/>
+  <dimension ref="A1:BP168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1483,7 +1486,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1689,7 +1692,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1895,7 +1898,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2101,7 +2104,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -3337,7 +3340,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3543,7 +3546,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3830,7 +3833,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ13">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4367,7 +4370,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4573,7 +4576,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ17">
         <v>2.3</v>
@@ -4779,7 +4782,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4985,7 +4988,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5066,7 +5069,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ19">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR19">
         <v>0.97</v>
@@ -5191,7 +5194,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5397,7 +5400,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5603,7 +5606,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6015,7 +6018,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6221,7 +6224,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6427,7 +6430,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6633,7 +6636,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -7045,7 +7048,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7251,7 +7254,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7457,7 +7460,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7535,7 +7538,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ31">
         <v>0.73</v>
@@ -8075,7 +8078,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8281,7 +8284,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8487,7 +8490,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8693,7 +8696,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8899,7 +8902,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -8977,7 +8980,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ38">
         <v>1.82</v>
@@ -9186,7 +9189,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ39">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR39">
         <v>0.82</v>
@@ -9311,7 +9314,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9517,7 +9520,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9723,7 +9726,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10135,7 +10138,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10341,7 +10344,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10547,7 +10550,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10625,7 +10628,7 @@
         <v>1.33</v>
       </c>
       <c r="AP46">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ46">
         <v>1.09</v>
@@ -10753,7 +10756,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10959,7 +10962,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11577,7 +11580,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11783,7 +11786,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -11864,7 +11867,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ52">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR52">
         <v>1.53</v>
@@ -12195,7 +12198,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12607,7 +12610,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12813,7 +12816,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -13019,7 +13022,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13637,7 +13640,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -14049,7 +14052,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14461,7 +14464,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14667,7 +14670,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14873,7 +14876,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14954,7 +14957,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ67">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR67">
         <v>1.77</v>
@@ -15079,7 +15082,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15157,7 +15160,7 @@
         <v>0.5</v>
       </c>
       <c r="AP68">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ68">
         <v>1.18</v>
@@ -15697,7 +15700,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16521,7 +16524,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16727,7 +16730,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16933,7 +16936,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17139,7 +17142,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17345,7 +17348,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17757,7 +17760,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18247,7 +18250,7 @@
         <v>1</v>
       </c>
       <c r="AP83">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ83">
         <v>1.1</v>
@@ -18581,7 +18584,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18787,7 +18790,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19199,7 +19202,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19405,7 +19408,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19611,7 +19614,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20023,7 +20026,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20229,7 +20232,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20435,7 +20438,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20641,7 +20644,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20722,7 +20725,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ95">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR95">
         <v>1.33</v>
@@ -21053,7 +21056,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21465,7 +21468,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21671,7 +21674,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21877,7 +21880,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22161,7 +22164,7 @@
         <v>2</v>
       </c>
       <c r="AP102">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ102">
         <v>1.27</v>
@@ -22289,7 +22292,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22495,7 +22498,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22907,7 +22910,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23113,7 +23116,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23319,7 +23322,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23525,7 +23528,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24018,7 +24021,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ111">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR111">
         <v>1.21</v>
@@ -24967,7 +24970,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25457,7 +25460,7 @@
         <v>2.29</v>
       </c>
       <c r="AP118">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ118">
         <v>2.27</v>
@@ -25585,7 +25588,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26203,7 +26206,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26615,7 +26618,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26821,7 +26824,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -26899,7 +26902,7 @@
         <v>1.86</v>
       </c>
       <c r="AP125">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ125">
         <v>1.44</v>
@@ -27027,7 +27030,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27233,7 +27236,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27439,7 +27442,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27645,7 +27648,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27726,7 +27729,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ129">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR129">
         <v>1.89</v>
@@ -27851,7 +27854,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28263,7 +28266,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28469,7 +28472,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29293,7 +29296,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29705,7 +29708,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30117,7 +30120,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30401,7 +30404,7 @@
         <v>0.5</v>
       </c>
       <c r="AP142">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AQ142">
         <v>0.5</v>
@@ -31022,7 +31025,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ145">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AR145">
         <v>1.22</v>
@@ -31147,7 +31150,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31353,7 +31356,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31765,7 +31768,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31971,7 +31974,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32177,7 +32180,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32589,7 +32592,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32795,7 +32798,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -33001,7 +33004,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33619,7 +33622,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -34237,7 +34240,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34443,7 +34446,7 @@
         <v>192</v>
       </c>
       <c r="P162" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q162">
         <v>3.2</v>
@@ -35267,7 +35270,7 @@
         <v>195</v>
       </c>
       <c r="P166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35473,7 +35476,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35629,6 +35632,212 @@
         <v>0</v>
       </c>
       <c r="BP167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:68">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>7484703</v>
+      </c>
+      <c r="C168" t="s">
+        <v>68</v>
+      </c>
+      <c r="D168" t="s">
+        <v>69</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45746.22916666666</v>
+      </c>
+      <c r="F168">
+        <v>21</v>
+      </c>
+      <c r="G168" t="s">
+        <v>85</v>
+      </c>
+      <c r="H168" t="s">
+        <v>73</v>
+      </c>
+      <c r="I168">
+        <v>1</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168">
+        <v>1</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168" t="s">
+        <v>197</v>
+      </c>
+      <c r="P168" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q168">
+        <v>2</v>
+      </c>
+      <c r="R168">
+        <v>2.3</v>
+      </c>
+      <c r="S168">
+        <v>5.5</v>
+      </c>
+      <c r="T168">
+        <v>1.33</v>
+      </c>
+      <c r="U168">
+        <v>3.25</v>
+      </c>
+      <c r="V168">
+        <v>2.63</v>
+      </c>
+      <c r="W168">
+        <v>1.44</v>
+      </c>
+      <c r="X168">
+        <v>6</v>
+      </c>
+      <c r="Y168">
+        <v>1.11</v>
+      </c>
+      <c r="Z168">
+        <v>1.48</v>
+      </c>
+      <c r="AA168">
+        <v>4.33</v>
+      </c>
+      <c r="AB168">
+        <v>5.5</v>
+      </c>
+      <c r="AC168">
+        <v>0</v>
+      </c>
+      <c r="AD168">
+        <v>0</v>
+      </c>
+      <c r="AE168">
+        <v>2.27</v>
+      </c>
+      <c r="AF168">
+        <v>1.61</v>
+      </c>
+      <c r="AG168">
+        <v>1.73</v>
+      </c>
+      <c r="AH168">
+        <v>2.08</v>
+      </c>
+      <c r="AI168">
+        <v>1.83</v>
+      </c>
+      <c r="AJ168">
+        <v>1.83</v>
+      </c>
+      <c r="AK168">
+        <v>0</v>
+      </c>
+      <c r="AL168">
+        <v>0</v>
+      </c>
+      <c r="AM168">
+        <v>0</v>
+      </c>
+      <c r="AN168">
+        <v>1.8</v>
+      </c>
+      <c r="AO168">
+        <v>0.67</v>
+      </c>
+      <c r="AP168">
+        <v>1.91</v>
+      </c>
+      <c r="AQ168">
+        <v>0.6</v>
+      </c>
+      <c r="AR168">
+        <v>1.22</v>
+      </c>
+      <c r="AS168">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT168">
+        <v>2.16</v>
+      </c>
+      <c r="AU168">
+        <v>4</v>
+      </c>
+      <c r="AV168">
+        <v>2</v>
+      </c>
+      <c r="AW168">
+        <v>10</v>
+      </c>
+      <c r="AX168">
+        <v>8</v>
+      </c>
+      <c r="AY168">
+        <v>14</v>
+      </c>
+      <c r="AZ168">
+        <v>11</v>
+      </c>
+      <c r="BA168">
+        <v>6</v>
+      </c>
+      <c r="BB168">
+        <v>7</v>
+      </c>
+      <c r="BC168">
+        <v>13</v>
+      </c>
+      <c r="BD168">
+        <v>0</v>
+      </c>
+      <c r="BE168">
+        <v>0</v>
+      </c>
+      <c r="BF168">
+        <v>0</v>
+      </c>
+      <c r="BG168">
+        <v>0</v>
+      </c>
+      <c r="BH168">
+        <v>0</v>
+      </c>
+      <c r="BI168">
+        <v>0</v>
+      </c>
+      <c r="BJ168">
+        <v>0</v>
+      </c>
+      <c r="BK168">
+        <v>0</v>
+      </c>
+      <c r="BL168">
+        <v>0</v>
+      </c>
+      <c r="BM168">
+        <v>0</v>
+      </c>
+      <c r="BN168">
+        <v>0</v>
+      </c>
+      <c r="BO168">
+        <v>0</v>
+      </c>
+      <c r="BP168">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="290">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -610,6 +610,18 @@
     <t>['28']</t>
   </si>
   <si>
+    <t>['1']</t>
+  </si>
+  <si>
+    <t>['13']</t>
+  </si>
+  <si>
+    <t>['3', '5', '12', '15', '33', '76']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
     <t>['62']</t>
   </si>
   <si>
@@ -671,9 +683,6 @@
   </si>
   <si>
     <t>['78', '90+3']</t>
-  </si>
-  <si>
-    <t>['25']</t>
   </si>
   <si>
     <t>['3', '82']</t>
@@ -869,6 +878,12 @@
   </si>
   <si>
     <t>['48', '63']</t>
+  </si>
+  <si>
+    <t>['50', '54', '90+5']</t>
+  </si>
+  <si>
+    <t>['24', '68', '84', '88']</t>
   </si>
 </sst>
 </file>
@@ -1230,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP168"/>
+  <dimension ref="A1:BP172"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1486,7 +1501,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1567,7 +1582,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ2">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1692,7 +1707,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1773,7 +1788,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ3">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1898,7 +1913,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2104,7 +2119,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -2597,7 +2612,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ7">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3215,7 +3230,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ10">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3340,7 +3355,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3546,7 +3561,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -3624,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ12">
         <v>0.73</v>
@@ -3830,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ13">
         <v>0.6</v>
@@ -4242,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ15">
         <v>1.1</v>
@@ -4370,7 +4385,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4448,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
         <v>1.18</v>
@@ -4576,7 +4591,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4782,7 +4797,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -4988,7 +5003,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5194,7 +5209,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5275,7 +5290,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ20">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR20">
         <v>0.71</v>
@@ -5400,7 +5415,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5606,7 +5621,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -5893,7 +5908,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ23">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR23">
         <v>2.04</v>
@@ -6018,7 +6033,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6224,7 +6239,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6305,7 +6320,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ25">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR25">
         <v>0.84</v>
@@ -6430,7 +6445,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6636,7 +6651,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -6714,7 +6729,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
         <v>2.3</v>
@@ -6920,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ28">
         <v>1.82</v>
@@ -7048,7 +7063,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7254,7 +7269,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7335,7 +7350,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ30">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR30">
         <v>1.86</v>
@@ -7460,7 +7475,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7744,7 +7759,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ32">
         <v>1.44</v>
@@ -7950,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="AP33">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1.1</v>
@@ -8078,7 +8093,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8284,7 +8299,7 @@
         <v>110</v>
       </c>
       <c r="P35" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q35">
         <v>2.4</v>
@@ -8490,7 +8505,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8696,7 +8711,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8902,7 +8917,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9314,7 +9329,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9520,7 +9535,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9726,7 +9741,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -9804,7 +9819,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ42">
         <v>1.27</v>
@@ -10010,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ43">
         <v>1.1</v>
@@ -10138,7 +10153,7 @@
         <v>115</v>
       </c>
       <c r="P44" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q44">
         <v>2.5</v>
@@ -10216,10 +10231,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR44">
         <v>1.33</v>
@@ -10344,7 +10359,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10550,7 +10565,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10756,7 +10771,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10962,7 +10977,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11580,7 +11595,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11786,7 +11801,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12073,7 +12088,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ53">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR53">
         <v>0.98</v>
@@ -12198,7 +12213,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12276,10 +12291,10 @@
         <v>2</v>
       </c>
       <c r="AP54">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ54">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR54">
         <v>1.74</v>
@@ -12610,7 +12625,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12691,7 +12706,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ56">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR56">
         <v>1.26</v>
@@ -12816,7 +12831,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -12894,7 +12909,7 @@
         <v>1.5</v>
       </c>
       <c r="AP57">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ57">
         <v>1.44</v>
@@ -13022,7 +13037,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13100,7 +13115,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13309,7 +13324,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ59">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR59">
         <v>1.05</v>
@@ -13640,7 +13655,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13721,7 +13736,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ61">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR61">
         <v>1.31</v>
@@ -14052,7 +14067,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14133,7 +14148,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ63">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR63">
         <v>1.26</v>
@@ -14336,10 +14351,10 @@
         <v>1.67</v>
       </c>
       <c r="AP64">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR64">
         <v>1.93</v>
@@ -14464,7 +14479,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14545,7 +14560,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ65">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR65">
         <v>1.19</v>
@@ -14670,7 +14685,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14876,7 +14891,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -14954,7 +14969,7 @@
         <v>1.5</v>
       </c>
       <c r="AP67">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.6</v>
@@ -15082,7 +15097,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15572,7 +15587,7 @@
         <v>1</v>
       </c>
       <c r="AP70">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>0.73</v>
@@ -15700,7 +15715,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -15778,7 +15793,7 @@
         <v>0.75</v>
       </c>
       <c r="AP71">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ71">
         <v>1.82</v>
@@ -16524,7 +16539,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16730,7 +16745,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16936,7 +16951,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17142,7 +17157,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17223,7 +17238,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ78">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR78">
         <v>1.34</v>
@@ -17348,7 +17363,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17426,7 +17441,7 @@
         <v>1.4</v>
       </c>
       <c r="AP79">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ79">
         <v>1.09</v>
@@ -17635,7 +17650,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ80">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR80">
         <v>1.44</v>
@@ -17760,7 +17775,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18044,7 +18059,7 @@
         <v>2.4</v>
       </c>
       <c r="AP82">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ82">
         <v>1.55</v>
@@ -18459,7 +18474,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ84">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR84">
         <v>1.58</v>
@@ -18584,7 +18599,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18662,10 +18677,10 @@
         <v>0.2</v>
       </c>
       <c r="AP85">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ85">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR85">
         <v>1.86</v>
@@ -18790,7 +18805,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19074,7 +19089,7 @@
         <v>2.2</v>
       </c>
       <c r="AP87">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ87">
         <v>1.27</v>
@@ -19202,7 +19217,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19408,7 +19423,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19614,7 +19629,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -20026,7 +20041,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20107,7 +20122,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ92">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR92">
         <v>1.32</v>
@@ -20232,7 +20247,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20438,7 +20453,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20516,7 +20531,7 @@
         <v>1.8</v>
       </c>
       <c r="AP94">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.3</v>
@@ -20644,7 +20659,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -20931,7 +20946,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ96">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -21056,7 +21071,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21134,10 +21149,10 @@
         <v>2</v>
       </c>
       <c r="AP97">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR97">
         <v>1.11</v>
@@ -21343,7 +21358,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ98">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR98">
         <v>1.62</v>
@@ -21468,7 +21483,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21674,7 +21689,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21752,7 +21767,7 @@
         <v>1.5</v>
       </c>
       <c r="AP100">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.82</v>
@@ -21880,7 +21895,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22292,7 +22307,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22498,7 +22513,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22910,7 +22925,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23116,7 +23131,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23194,7 +23209,7 @@
         <v>1.71</v>
       </c>
       <c r="AP107">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ107">
         <v>1.82</v>
@@ -23322,7 +23337,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23403,7 +23418,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ108">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR108">
         <v>1.76</v>
@@ -23528,7 +23543,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -23812,7 +23827,7 @@
         <v>1.67</v>
       </c>
       <c r="AP110">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ110">
         <v>1.3</v>
@@ -24018,7 +24033,7 @@
         <v>1</v>
       </c>
       <c r="AP111">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ111">
         <v>0.6</v>
@@ -24433,7 +24448,7 @@
         <v>0.9</v>
       </c>
       <c r="AQ113">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR113">
         <v>1.3</v>
@@ -24970,7 +24985,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25257,7 +25272,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ117">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR117">
         <v>1.34</v>
@@ -25588,7 +25603,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -25669,7 +25684,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ119">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR119">
         <v>1.62</v>
@@ -26078,7 +26093,7 @@
         <v>1.86</v>
       </c>
       <c r="AP121">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ121">
         <v>1.55</v>
@@ -26206,7 +26221,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26490,10 +26505,10 @@
         <v>0.57</v>
       </c>
       <c r="AP123">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ123">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR123">
         <v>1.4</v>
@@ -26618,7 +26633,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26824,7 +26839,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27030,7 +27045,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27108,7 +27123,7 @@
         <v>2.29</v>
       </c>
       <c r="AP126">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ126">
         <v>2.3</v>
@@ -27236,7 +27251,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27442,7 +27457,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27520,7 +27535,7 @@
         <v>1.5</v>
       </c>
       <c r="AP128">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ128">
         <v>1.18</v>
@@ -27648,7 +27663,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27726,7 +27741,7 @@
         <v>0.86</v>
       </c>
       <c r="AP129">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ129">
         <v>0.6</v>
@@ -27854,7 +27869,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28141,7 +28156,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ131">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR131">
         <v>1.14</v>
@@ -28266,7 +28281,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28472,7 +28487,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -28553,7 +28568,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ133">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR133">
         <v>1.4</v>
@@ -28759,7 +28774,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ134">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR134">
         <v>1.56</v>
@@ -29296,7 +29311,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29708,7 +29723,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -29992,7 +30007,7 @@
         <v>1.44</v>
       </c>
       <c r="AP140">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ140">
         <v>1.27</v>
@@ -30120,7 +30135,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30407,7 +30422,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ142">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR142">
         <v>1.21</v>
@@ -30610,7 +30625,7 @@
         <v>0.89</v>
       </c>
       <c r="AP143">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ143">
         <v>0.73</v>
@@ -30816,7 +30831,7 @@
         <v>1.33</v>
       </c>
       <c r="AP144">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ144">
         <v>1.18</v>
@@ -31150,7 +31165,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31231,7 +31246,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ146">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR146">
         <v>1.16</v>
@@ -31356,7 +31371,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31768,7 +31783,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31974,7 +31989,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32055,7 +32070,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ150">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR150">
         <v>1.28</v>
@@ -32180,7 +32195,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32261,7 +32276,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ151">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR151">
         <v>1.34</v>
@@ -32592,7 +32607,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32670,10 +32685,10 @@
         <v>1.22</v>
       </c>
       <c r="AP153">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ153">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR153">
         <v>1.72</v>
@@ -32798,7 +32813,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -32876,7 +32891,7 @@
         <v>2.22</v>
       </c>
       <c r="AP154">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
         <v>2.3</v>
@@ -33004,7 +33019,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33085,7 +33100,7 @@
         <v>0.64</v>
       </c>
       <c r="AQ155">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR155">
         <v>1.03</v>
@@ -33622,7 +33637,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -33703,7 +33718,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ158">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AR158">
         <v>1.5</v>
@@ -33906,10 +33921,10 @@
         <v>0.5</v>
       </c>
       <c r="AP159">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ159">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR159">
         <v>1.42</v>
@@ -34112,7 +34127,7 @@
         <v>1.22</v>
       </c>
       <c r="AP160">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AQ160">
         <v>1.1</v>
@@ -34240,7 +34255,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34446,7 +34461,7 @@
         <v>192</v>
       </c>
       <c r="P162" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q162">
         <v>3.2</v>
@@ -35270,7 +35285,7 @@
         <v>195</v>
       </c>
       <c r="P166" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35476,7 +35491,7 @@
         <v>196</v>
       </c>
       <c r="P167" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="Q167">
         <v>2.75</v>
@@ -35838,6 +35853,830 @@
         <v>0</v>
       </c>
       <c r="BP168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:68">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>7484704</v>
+      </c>
+      <c r="C169" t="s">
+        <v>68</v>
+      </c>
+      <c r="D169" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F169">
+        <v>22</v>
+      </c>
+      <c r="G169" t="s">
+        <v>83</v>
+      </c>
+      <c r="H169" t="s">
+        <v>72</v>
+      </c>
+      <c r="I169">
+        <v>1</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169">
+        <v>1</v>
+      </c>
+      <c r="M169">
+        <v>3</v>
+      </c>
+      <c r="N169">
+        <v>4</v>
+      </c>
+      <c r="O169" t="s">
+        <v>198</v>
+      </c>
+      <c r="P169" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q169">
+        <v>2.88</v>
+      </c>
+      <c r="R169">
+        <v>2.2</v>
+      </c>
+      <c r="S169">
+        <v>3.25</v>
+      </c>
+      <c r="T169">
+        <v>1.36</v>
+      </c>
+      <c r="U169">
+        <v>3</v>
+      </c>
+      <c r="V169">
+        <v>2.75</v>
+      </c>
+      <c r="W169">
+        <v>1.4</v>
+      </c>
+      <c r="X169">
+        <v>6.5</v>
+      </c>
+      <c r="Y169">
+        <v>1.1</v>
+      </c>
+      <c r="Z169">
+        <v>2.3</v>
+      </c>
+      <c r="AA169">
+        <v>3.3</v>
+      </c>
+      <c r="AB169">
+        <v>2.88</v>
+      </c>
+      <c r="AC169">
+        <v>1.04</v>
+      </c>
+      <c r="AD169">
+        <v>9</v>
+      </c>
+      <c r="AE169">
+        <v>1.25</v>
+      </c>
+      <c r="AF169">
+        <v>3.6</v>
+      </c>
+      <c r="AG169">
+        <v>1.85</v>
+      </c>
+      <c r="AH169">
+        <v>1.95</v>
+      </c>
+      <c r="AI169">
+        <v>1.67</v>
+      </c>
+      <c r="AJ169">
+        <v>2.1</v>
+      </c>
+      <c r="AK169">
+        <v>1.4</v>
+      </c>
+      <c r="AL169">
+        <v>1.25</v>
+      </c>
+      <c r="AM169">
+        <v>1.57</v>
+      </c>
+      <c r="AN169">
+        <v>2.2</v>
+      </c>
+      <c r="AO169">
+        <v>0.5</v>
+      </c>
+      <c r="AP169">
+        <v>2</v>
+      </c>
+      <c r="AQ169">
+        <v>0.73</v>
+      </c>
+      <c r="AR169">
+        <v>1.67</v>
+      </c>
+      <c r="AS169">
+        <v>1.08</v>
+      </c>
+      <c r="AT169">
+        <v>2.75</v>
+      </c>
+      <c r="AU169">
+        <v>9</v>
+      </c>
+      <c r="AV169">
+        <v>6</v>
+      </c>
+      <c r="AW169">
+        <v>7</v>
+      </c>
+      <c r="AX169">
+        <v>8</v>
+      </c>
+      <c r="AY169">
+        <v>19</v>
+      </c>
+      <c r="AZ169">
+        <v>16</v>
+      </c>
+      <c r="BA169">
+        <v>7</v>
+      </c>
+      <c r="BB169">
+        <v>4</v>
+      </c>
+      <c r="BC169">
+        <v>11</v>
+      </c>
+      <c r="BD169">
+        <v>0</v>
+      </c>
+      <c r="BE169">
+        <v>0</v>
+      </c>
+      <c r="BF169">
+        <v>0</v>
+      </c>
+      <c r="BG169">
+        <v>0</v>
+      </c>
+      <c r="BH169">
+        <v>0</v>
+      </c>
+      <c r="BI169">
+        <v>0</v>
+      </c>
+      <c r="BJ169">
+        <v>0</v>
+      </c>
+      <c r="BK169">
+        <v>1.72</v>
+      </c>
+      <c r="BL169">
+        <v>2.07</v>
+      </c>
+      <c r="BM169">
+        <v>2.15</v>
+      </c>
+      <c r="BN169">
+        <v>1.67</v>
+      </c>
+      <c r="BO169">
+        <v>0</v>
+      </c>
+      <c r="BP169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:68">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>7484705</v>
+      </c>
+      <c r="C170" t="s">
+        <v>68</v>
+      </c>
+      <c r="D170" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F170">
+        <v>22</v>
+      </c>
+      <c r="G170" t="s">
+        <v>84</v>
+      </c>
+      <c r="H170" t="s">
+        <v>85</v>
+      </c>
+      <c r="I170">
+        <v>1</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170">
+        <v>1</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>1</v>
+      </c>
+      <c r="O170" t="s">
+        <v>199</v>
+      </c>
+      <c r="P170" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q170">
+        <v>3.1</v>
+      </c>
+      <c r="R170">
+        <v>2.3</v>
+      </c>
+      <c r="S170">
+        <v>2.88</v>
+      </c>
+      <c r="T170">
+        <v>1.3</v>
+      </c>
+      <c r="U170">
+        <v>3.4</v>
+      </c>
+      <c r="V170">
+        <v>2.38</v>
+      </c>
+      <c r="W170">
+        <v>1.53</v>
+      </c>
+      <c r="X170">
+        <v>5.5</v>
+      </c>
+      <c r="Y170">
+        <v>1.13</v>
+      </c>
+      <c r="Z170">
+        <v>2.63</v>
+      </c>
+      <c r="AA170">
+        <v>3.7</v>
+      </c>
+      <c r="AB170">
+        <v>2.35</v>
+      </c>
+      <c r="AC170">
+        <v>1.03</v>
+      </c>
+      <c r="AD170">
+        <v>10</v>
+      </c>
+      <c r="AE170">
+        <v>1.18</v>
+      </c>
+      <c r="AF170">
+        <v>4.5</v>
+      </c>
+      <c r="AG170">
+        <v>1.6</v>
+      </c>
+      <c r="AH170">
+        <v>2.3</v>
+      </c>
+      <c r="AI170">
+        <v>1.53</v>
+      </c>
+      <c r="AJ170">
+        <v>2.38</v>
+      </c>
+      <c r="AK170">
+        <v>1.57</v>
+      </c>
+      <c r="AL170">
+        <v>1.22</v>
+      </c>
+      <c r="AM170">
+        <v>1.45</v>
+      </c>
+      <c r="AN170">
+        <v>1.9</v>
+      </c>
+      <c r="AO170">
+        <v>1.7</v>
+      </c>
+      <c r="AP170">
+        <v>2</v>
+      </c>
+      <c r="AQ170">
+        <v>1.55</v>
+      </c>
+      <c r="AR170">
+        <v>1.79</v>
+      </c>
+      <c r="AS170">
+        <v>1.47</v>
+      </c>
+      <c r="AT170">
+        <v>3.26</v>
+      </c>
+      <c r="AU170">
+        <v>3</v>
+      </c>
+      <c r="AV170">
+        <v>4</v>
+      </c>
+      <c r="AW170">
+        <v>6</v>
+      </c>
+      <c r="AX170">
+        <v>13</v>
+      </c>
+      <c r="AY170">
+        <v>12</v>
+      </c>
+      <c r="AZ170">
+        <v>21</v>
+      </c>
+      <c r="BA170">
+        <v>3</v>
+      </c>
+      <c r="BB170">
+        <v>9</v>
+      </c>
+      <c r="BC170">
+        <v>12</v>
+      </c>
+      <c r="BD170">
+        <v>0</v>
+      </c>
+      <c r="BE170">
+        <v>0</v>
+      </c>
+      <c r="BF170">
+        <v>0</v>
+      </c>
+      <c r="BG170">
+        <v>0</v>
+      </c>
+      <c r="BH170">
+        <v>0</v>
+      </c>
+      <c r="BI170">
+        <v>0</v>
+      </c>
+      <c r="BJ170">
+        <v>0</v>
+      </c>
+      <c r="BK170">
+        <v>1.74</v>
+      </c>
+      <c r="BL170">
+        <v>2.05</v>
+      </c>
+      <c r="BM170">
+        <v>2.18</v>
+      </c>
+      <c r="BN170">
+        <v>1.65</v>
+      </c>
+      <c r="BO170">
+        <v>0</v>
+      </c>
+      <c r="BP170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:68">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>7484708</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F171">
+        <v>22</v>
+      </c>
+      <c r="G171" t="s">
+        <v>80</v>
+      </c>
+      <c r="H171" t="s">
+        <v>79</v>
+      </c>
+      <c r="I171">
+        <v>5</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>6</v>
+      </c>
+      <c r="L171">
+        <v>6</v>
+      </c>
+      <c r="M171">
+        <v>4</v>
+      </c>
+      <c r="N171">
+        <v>10</v>
+      </c>
+      <c r="O171" t="s">
+        <v>200</v>
+      </c>
+      <c r="P171" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q171">
+        <v>2.5</v>
+      </c>
+      <c r="R171">
+        <v>2.38</v>
+      </c>
+      <c r="S171">
+        <v>3.5</v>
+      </c>
+      <c r="T171">
+        <v>1.29</v>
+      </c>
+      <c r="U171">
+        <v>3.5</v>
+      </c>
+      <c r="V171">
+        <v>2.38</v>
+      </c>
+      <c r="W171">
+        <v>1.53</v>
+      </c>
+      <c r="X171">
+        <v>5</v>
+      </c>
+      <c r="Y171">
+        <v>1.14</v>
+      </c>
+      <c r="Z171">
+        <v>1.95</v>
+      </c>
+      <c r="AA171">
+        <v>4</v>
+      </c>
+      <c r="AB171">
+        <v>3.1</v>
+      </c>
+      <c r="AC171">
+        <v>1.03</v>
+      </c>
+      <c r="AD171">
+        <v>10</v>
+      </c>
+      <c r="AE171">
+        <v>1.17</v>
+      </c>
+      <c r="AF171">
+        <v>4.75</v>
+      </c>
+      <c r="AG171">
+        <v>1.57</v>
+      </c>
+      <c r="AH171">
+        <v>2.35</v>
+      </c>
+      <c r="AI171">
+        <v>1.53</v>
+      </c>
+      <c r="AJ171">
+        <v>2.38</v>
+      </c>
+      <c r="AK171">
+        <v>1.35</v>
+      </c>
+      <c r="AL171">
+        <v>1.2</v>
+      </c>
+      <c r="AM171">
+        <v>1.73</v>
+      </c>
+      <c r="AN171">
+        <v>1.6</v>
+      </c>
+      <c r="AO171">
+        <v>0.45</v>
+      </c>
+      <c r="AP171">
+        <v>1.73</v>
+      </c>
+      <c r="AQ171">
+        <v>0.42</v>
+      </c>
+      <c r="AR171">
+        <v>1.38</v>
+      </c>
+      <c r="AS171">
+        <v>1.32</v>
+      </c>
+      <c r="AT171">
+        <v>2.7</v>
+      </c>
+      <c r="AU171">
+        <v>7</v>
+      </c>
+      <c r="AV171">
+        <v>13</v>
+      </c>
+      <c r="AW171">
+        <v>6</v>
+      </c>
+      <c r="AX171">
+        <v>6</v>
+      </c>
+      <c r="AY171">
+        <v>15</v>
+      </c>
+      <c r="AZ171">
+        <v>21</v>
+      </c>
+      <c r="BA171">
+        <v>6</v>
+      </c>
+      <c r="BB171">
+        <v>6</v>
+      </c>
+      <c r="BC171">
+        <v>12</v>
+      </c>
+      <c r="BD171">
+        <v>0</v>
+      </c>
+      <c r="BE171">
+        <v>0</v>
+      </c>
+      <c r="BF171">
+        <v>0</v>
+      </c>
+      <c r="BG171">
+        <v>0</v>
+      </c>
+      <c r="BH171">
+        <v>0</v>
+      </c>
+      <c r="BI171">
+        <v>1.46</v>
+      </c>
+      <c r="BJ171">
+        <v>2.57</v>
+      </c>
+      <c r="BK171">
+        <v>1.81</v>
+      </c>
+      <c r="BL171">
+        <v>1.99</v>
+      </c>
+      <c r="BM171">
+        <v>2.23</v>
+      </c>
+      <c r="BN171">
+        <v>1.61</v>
+      </c>
+      <c r="BO171">
+        <v>0</v>
+      </c>
+      <c r="BP171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:68">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>7484709</v>
+      </c>
+      <c r="C172" t="s">
+        <v>68</v>
+      </c>
+      <c r="D172" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45751.54166666666</v>
+      </c>
+      <c r="F172">
+        <v>22</v>
+      </c>
+      <c r="G172" t="s">
+        <v>81</v>
+      </c>
+      <c r="H172" t="s">
+        <v>78</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+      <c r="L172">
+        <v>1</v>
+      </c>
+      <c r="M172">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172" t="s">
+        <v>201</v>
+      </c>
+      <c r="P172" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q172">
+        <v>1.83</v>
+      </c>
+      <c r="R172">
+        <v>2.4</v>
+      </c>
+      <c r="S172">
+        <v>6.5</v>
+      </c>
+      <c r="T172">
+        <v>1.3</v>
+      </c>
+      <c r="U172">
+        <v>3.4</v>
+      </c>
+      <c r="V172">
+        <v>2.5</v>
+      </c>
+      <c r="W172">
+        <v>1.5</v>
+      </c>
+      <c r="X172">
+        <v>5.5</v>
+      </c>
+      <c r="Y172">
+        <v>1.13</v>
+      </c>
+      <c r="Z172">
+        <v>1.36</v>
+      </c>
+      <c r="AA172">
+        <v>5</v>
+      </c>
+      <c r="AB172">
+        <v>6.5</v>
+      </c>
+      <c r="AC172">
+        <v>1.03</v>
+      </c>
+      <c r="AD172">
+        <v>10</v>
+      </c>
+      <c r="AE172">
+        <v>1.18</v>
+      </c>
+      <c r="AF172">
+        <v>4.5</v>
+      </c>
+      <c r="AG172">
+        <v>1.65</v>
+      </c>
+      <c r="AH172">
+        <v>2.2</v>
+      </c>
+      <c r="AI172">
+        <v>1.91</v>
+      </c>
+      <c r="AJ172">
+        <v>1.8</v>
+      </c>
+      <c r="AK172">
+        <v>1.05</v>
+      </c>
+      <c r="AL172">
+        <v>1.13</v>
+      </c>
+      <c r="AM172">
+        <v>2.95</v>
+      </c>
+      <c r="AN172">
+        <v>2.2</v>
+      </c>
+      <c r="AO172">
+        <v>1.1</v>
+      </c>
+      <c r="AP172">
+        <v>2.09</v>
+      </c>
+      <c r="AQ172">
+        <v>1.09</v>
+      </c>
+      <c r="AR172">
+        <v>1.46</v>
+      </c>
+      <c r="AS172">
+        <v>1.49</v>
+      </c>
+      <c r="AT172">
+        <v>2.95</v>
+      </c>
+      <c r="AU172">
+        <v>4</v>
+      </c>
+      <c r="AV172">
+        <v>3</v>
+      </c>
+      <c r="AW172">
+        <v>8</v>
+      </c>
+      <c r="AX172">
+        <v>7</v>
+      </c>
+      <c r="AY172">
+        <v>13</v>
+      </c>
+      <c r="AZ172">
+        <v>13</v>
+      </c>
+      <c r="BA172">
+        <v>5</v>
+      </c>
+      <c r="BB172">
+        <v>3</v>
+      </c>
+      <c r="BC172">
+        <v>8</v>
+      </c>
+      <c r="BD172">
+        <v>0</v>
+      </c>
+      <c r="BE172">
+        <v>0</v>
+      </c>
+      <c r="BF172">
+        <v>0</v>
+      </c>
+      <c r="BG172">
+        <v>0</v>
+      </c>
+      <c r="BH172">
+        <v>0</v>
+      </c>
+      <c r="BI172">
+        <v>0</v>
+      </c>
+      <c r="BJ172">
+        <v>0</v>
+      </c>
+      <c r="BK172">
+        <v>0</v>
+      </c>
+      <c r="BL172">
+        <v>0</v>
+      </c>
+      <c r="BM172">
+        <v>0</v>
+      </c>
+      <c r="BN172">
+        <v>0</v>
+      </c>
+      <c r="BO172">
+        <v>0</v>
+      </c>
+      <c r="BP172">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="292">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -885,6 +885,12 @@
   <si>
     <t>['24', '68', '84', '88']</t>
   </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['38', '90+2']</t>
+  </si>
 </sst>
 </file>
 
@@ -1245,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP172"/>
+  <dimension ref="A1:BP175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2197,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ5">
         <v>1.09</v>
@@ -2815,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8">
         <v>1.3</v>
@@ -3021,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ9">
         <v>1.82</v>
@@ -3436,7 +3442,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ11">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -4054,7 +4060,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4672,7 +4678,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ17">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5493,7 +5499,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ21">
         <v>2.27</v>
@@ -6111,7 +6117,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ24">
         <v>1.55</v>
@@ -6523,10 +6529,10 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ26">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR26">
         <v>1.49</v>
@@ -6732,7 +6738,7 @@
         <v>2</v>
       </c>
       <c r="AQ27">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR27">
         <v>1.73</v>
@@ -7762,7 +7768,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ32">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR32">
         <v>1.68</v>
@@ -9822,7 +9828,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ42">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR42">
         <v>1.18</v>
@@ -12085,7 +12091,7 @@
         <v>0.5</v>
       </c>
       <c r="AP53">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ53">
         <v>0.73</v>
@@ -12500,7 +12506,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ55">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR55">
         <v>1.49</v>
@@ -12703,7 +12709,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ56">
         <v>1.09</v>
@@ -12912,7 +12918,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ57">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR57">
         <v>1.02</v>
@@ -13527,7 +13533,7 @@
         <v>0.33</v>
       </c>
       <c r="AP60">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ60">
         <v>1.1</v>
@@ -13733,7 +13739,7 @@
         <v>0.33</v>
       </c>
       <c r="AP61">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ61">
         <v>0.42</v>
@@ -13942,7 +13948,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ62">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR62">
         <v>1.38</v>
@@ -14145,7 +14151,7 @@
         <v>1.33</v>
       </c>
       <c r="AP63">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ63">
         <v>1.55</v>
@@ -14766,7 +14772,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ66">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR66">
         <v>1.04</v>
@@ -16002,7 +16008,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ72">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR72">
         <v>1.63</v>
@@ -16208,7 +16214,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ73">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR73">
         <v>1.39</v>
@@ -16617,7 +16623,7 @@
         <v>1</v>
       </c>
       <c r="AP75">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ75">
         <v>1.18</v>
@@ -16823,7 +16829,7 @@
         <v>2</v>
       </c>
       <c r="AP76">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ76">
         <v>1.3</v>
@@ -18883,10 +18889,10 @@
         <v>3</v>
       </c>
       <c r="AP86">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ86">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19092,7 +19098,7 @@
         <v>2</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
         <v>1.6</v>
@@ -19295,7 +19301,7 @@
         <v>1.2</v>
       </c>
       <c r="AP88">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ88">
         <v>1.82</v>
@@ -19501,10 +19507,10 @@
         <v>1.75</v>
       </c>
       <c r="AP89">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ89">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR89">
         <v>1.41</v>
@@ -20328,7 +20334,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ93">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20943,7 +20949,7 @@
         <v>0.4</v>
       </c>
       <c r="AP96">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ96">
         <v>0.73</v>
@@ -21973,7 +21979,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ101">
         <v>0.73</v>
@@ -22182,7 +22188,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ102">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR102">
         <v>1.18</v>
@@ -22385,7 +22391,7 @@
         <v>2.17</v>
       </c>
       <c r="AP103">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ103">
         <v>2.27</v>
@@ -22594,7 +22600,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ104">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR104">
         <v>1.26</v>
@@ -23003,7 +23009,7 @@
         <v>0.83</v>
       </c>
       <c r="AP106">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106">
         <v>1.1</v>
@@ -24242,7 +24248,7 @@
         <v>2.36</v>
       </c>
       <c r="AQ112">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR112">
         <v>1.39</v>
@@ -24651,10 +24657,10 @@
         <v>2.5</v>
       </c>
       <c r="AP114">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ114">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR114">
         <v>1.14</v>
@@ -24860,7 +24866,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ115">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR115">
         <v>1.28</v>
@@ -25887,7 +25893,7 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ120">
         <v>0.73</v>
@@ -26920,7 +26926,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ125">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR125">
         <v>1.17</v>
@@ -27126,7 +27132,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ126">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR126">
         <v>1.27</v>
@@ -27332,7 +27338,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ127">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR127">
         <v>1.44</v>
@@ -28359,7 +28365,7 @@
         <v>1.63</v>
       </c>
       <c r="AP132">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ132">
         <v>1.55</v>
@@ -28977,7 +28983,7 @@
         <v>1.38</v>
       </c>
       <c r="AP135">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135">
         <v>1.09</v>
@@ -29183,7 +29189,7 @@
         <v>2.38</v>
       </c>
       <c r="AP136">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ136">
         <v>2.27</v>
@@ -29804,7 +29810,7 @@
         <v>0.6</v>
       </c>
       <c r="AQ139">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR139">
         <v>1.38</v>
@@ -30010,7 +30016,7 @@
         <v>2</v>
       </c>
       <c r="AQ140">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR140">
         <v>1.92</v>
@@ -30213,7 +30219,7 @@
         <v>1.38</v>
       </c>
       <c r="AP141">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ141">
         <v>1.1</v>
@@ -32067,7 +32073,7 @@
         <v>1.38</v>
       </c>
       <c r="AP150">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ150">
         <v>1.09</v>
@@ -32273,7 +32279,7 @@
         <v>2</v>
       </c>
       <c r="AP151">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ151">
         <v>1.55</v>
@@ -32894,7 +32900,7 @@
         <v>2</v>
       </c>
       <c r="AQ154">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AR154">
         <v>1.88</v>
@@ -33097,7 +33103,7 @@
         <v>0.44</v>
       </c>
       <c r="AP155">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AQ155">
         <v>0.73</v>
@@ -33303,10 +33309,10 @@
         <v>1.3</v>
       </c>
       <c r="AP156">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AQ156">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR156">
         <v>1.35</v>
@@ -33509,10 +33515,10 @@
         <v>1.63</v>
       </c>
       <c r="AP157">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AQ157">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AR157">
         <v>1.27</v>
@@ -36677,6 +36683,624 @@
         <v>0</v>
       </c>
       <c r="BP172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:68">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>7484711</v>
+      </c>
+      <c r="C173" t="s">
+        <v>68</v>
+      </c>
+      <c r="D173" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45752.39583333334</v>
+      </c>
+      <c r="F173">
+        <v>22</v>
+      </c>
+      <c r="G173" t="s">
+        <v>76</v>
+      </c>
+      <c r="H173" t="s">
+        <v>75</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>1</v>
+      </c>
+      <c r="O173" t="s">
+        <v>86</v>
+      </c>
+      <c r="P173" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q173">
+        <v>3.1</v>
+      </c>
+      <c r="R173">
+        <v>2.1</v>
+      </c>
+      <c r="S173">
+        <v>3.1</v>
+      </c>
+      <c r="T173">
+        <v>1.4</v>
+      </c>
+      <c r="U173">
+        <v>2.75</v>
+      </c>
+      <c r="V173">
+        <v>2.75</v>
+      </c>
+      <c r="W173">
+        <v>1.4</v>
+      </c>
+      <c r="X173">
+        <v>7</v>
+      </c>
+      <c r="Y173">
+        <v>1.08</v>
+      </c>
+      <c r="Z173">
+        <v>2.55</v>
+      </c>
+      <c r="AA173">
+        <v>3.4</v>
+      </c>
+      <c r="AB173">
+        <v>2.55</v>
+      </c>
+      <c r="AC173">
+        <v>1</v>
+      </c>
+      <c r="AD173">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AE173">
+        <v>3.59</v>
+      </c>
+      <c r="AF173">
+        <v>1.27</v>
+      </c>
+      <c r="AG173">
+        <v>1.95</v>
+      </c>
+      <c r="AH173">
+        <v>1.85</v>
+      </c>
+      <c r="AI173">
+        <v>1.73</v>
+      </c>
+      <c r="AJ173">
+        <v>2</v>
+      </c>
+      <c r="AK173">
+        <v>1.46</v>
+      </c>
+      <c r="AL173">
+        <v>1.32</v>
+      </c>
+      <c r="AM173">
+        <v>1.52</v>
+      </c>
+      <c r="AN173">
+        <v>1.8</v>
+      </c>
+      <c r="AO173">
+        <v>1.27</v>
+      </c>
+      <c r="AP173">
+        <v>1.64</v>
+      </c>
+      <c r="AQ173">
+        <v>1.42</v>
+      </c>
+      <c r="AR173">
+        <v>1.29</v>
+      </c>
+      <c r="AS173">
+        <v>1.21</v>
+      </c>
+      <c r="AT173">
+        <v>2.5</v>
+      </c>
+      <c r="AU173">
+        <v>4</v>
+      </c>
+      <c r="AV173">
+        <v>7</v>
+      </c>
+      <c r="AW173">
+        <v>9</v>
+      </c>
+      <c r="AX173">
+        <v>6</v>
+      </c>
+      <c r="AY173">
+        <v>14</v>
+      </c>
+      <c r="AZ173">
+        <v>15</v>
+      </c>
+      <c r="BA173">
+        <v>7</v>
+      </c>
+      <c r="BB173">
+        <v>10</v>
+      </c>
+      <c r="BC173">
+        <v>17</v>
+      </c>
+      <c r="BD173">
+        <v>2.12</v>
+      </c>
+      <c r="BE173">
+        <v>6.35</v>
+      </c>
+      <c r="BF173">
+        <v>2.1</v>
+      </c>
+      <c r="BG173">
+        <v>1.24</v>
+      </c>
+      <c r="BH173">
+        <v>3.34</v>
+      </c>
+      <c r="BI173">
+        <v>1.52</v>
+      </c>
+      <c r="BJ173">
+        <v>2.46</v>
+      </c>
+      <c r="BK173">
+        <v>1.91</v>
+      </c>
+      <c r="BL173">
+        <v>1.91</v>
+      </c>
+      <c r="BM173">
+        <v>2.41</v>
+      </c>
+      <c r="BN173">
+        <v>1.54</v>
+      </c>
+      <c r="BO173">
+        <v>3.14</v>
+      </c>
+      <c r="BP173">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="174" spans="1:68">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>7484706</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45752.39583333334</v>
+      </c>
+      <c r="F174">
+        <v>22</v>
+      </c>
+      <c r="G174" t="s">
+        <v>73</v>
+      </c>
+      <c r="H174" t="s">
+        <v>70</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>1</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>1</v>
+      </c>
+      <c r="O174" t="s">
+        <v>86</v>
+      </c>
+      <c r="P174" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q174">
+        <v>4.33</v>
+      </c>
+      <c r="R174">
+        <v>2.2</v>
+      </c>
+      <c r="S174">
+        <v>2.3</v>
+      </c>
+      <c r="T174">
+        <v>1.36</v>
+      </c>
+      <c r="U174">
+        <v>3</v>
+      </c>
+      <c r="V174">
+        <v>2.63</v>
+      </c>
+      <c r="W174">
+        <v>1.44</v>
+      </c>
+      <c r="X174">
+        <v>6.5</v>
+      </c>
+      <c r="Y174">
+        <v>1.1</v>
+      </c>
+      <c r="Z174">
+        <v>4</v>
+      </c>
+      <c r="AA174">
+        <v>3.8</v>
+      </c>
+      <c r="AB174">
+        <v>1.75</v>
+      </c>
+      <c r="AC174">
+        <v>0</v>
+      </c>
+      <c r="AD174">
+        <v>0</v>
+      </c>
+      <c r="AE174">
+        <v>1.15</v>
+      </c>
+      <c r="AF174">
+        <v>4.25</v>
+      </c>
+      <c r="AG174">
+        <v>1.8</v>
+      </c>
+      <c r="AH174">
+        <v>2</v>
+      </c>
+      <c r="AI174">
+        <v>1.73</v>
+      </c>
+      <c r="AJ174">
+        <v>2</v>
+      </c>
+      <c r="AK174">
+        <v>1.93</v>
+      </c>
+      <c r="AL174">
+        <v>1.27</v>
+      </c>
+      <c r="AM174">
+        <v>1.27</v>
+      </c>
+      <c r="AN174">
+        <v>0.64</v>
+      </c>
+      <c r="AO174">
+        <v>1.44</v>
+      </c>
+      <c r="AP174">
+        <v>0.58</v>
+      </c>
+      <c r="AQ174">
+        <v>1.6</v>
+      </c>
+      <c r="AR174">
+        <v>1.05</v>
+      </c>
+      <c r="AS174">
+        <v>1.42</v>
+      </c>
+      <c r="AT174">
+        <v>2.47</v>
+      </c>
+      <c r="AU174">
+        <v>0</v>
+      </c>
+      <c r="AV174">
+        <v>4</v>
+      </c>
+      <c r="AW174">
+        <v>4</v>
+      </c>
+      <c r="AX174">
+        <v>2</v>
+      </c>
+      <c r="AY174">
+        <v>5</v>
+      </c>
+      <c r="AZ174">
+        <v>7</v>
+      </c>
+      <c r="BA174">
+        <v>5</v>
+      </c>
+      <c r="BB174">
+        <v>7</v>
+      </c>
+      <c r="BC174">
+        <v>12</v>
+      </c>
+      <c r="BD174">
+        <v>2.74</v>
+      </c>
+      <c r="BE174">
+        <v>8.1</v>
+      </c>
+      <c r="BF174">
+        <v>1.62</v>
+      </c>
+      <c r="BG174">
+        <v>1.45</v>
+      </c>
+      <c r="BH174">
+        <v>2.63</v>
+      </c>
+      <c r="BI174">
+        <v>1.81</v>
+      </c>
+      <c r="BJ174">
+        <v>2</v>
+      </c>
+      <c r="BK174">
+        <v>2.28</v>
+      </c>
+      <c r="BL174">
+        <v>1.6</v>
+      </c>
+      <c r="BM174">
+        <v>2.53</v>
+      </c>
+      <c r="BN174">
+        <v>1.48</v>
+      </c>
+      <c r="BO174">
+        <v>4.15</v>
+      </c>
+      <c r="BP174">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="175" spans="1:68">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>7484707</v>
+      </c>
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45752.625</v>
+      </c>
+      <c r="F175">
+        <v>22</v>
+      </c>
+      <c r="G175" t="s">
+        <v>77</v>
+      </c>
+      <c r="H175" t="s">
+        <v>74</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>1</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175">
+        <v>1</v>
+      </c>
+      <c r="M175">
+        <v>2</v>
+      </c>
+      <c r="N175">
+        <v>3</v>
+      </c>
+      <c r="O175" t="s">
+        <v>177</v>
+      </c>
+      <c r="P175" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q175">
+        <v>5</v>
+      </c>
+      <c r="R175">
+        <v>1.95</v>
+      </c>
+      <c r="S175">
+        <v>2.5</v>
+      </c>
+      <c r="T175">
+        <v>1.53</v>
+      </c>
+      <c r="U175">
+        <v>2.38</v>
+      </c>
+      <c r="V175">
+        <v>3.5</v>
+      </c>
+      <c r="W175">
+        <v>1.29</v>
+      </c>
+      <c r="X175">
+        <v>8.5</v>
+      </c>
+      <c r="Y175">
+        <v>1.05</v>
+      </c>
+      <c r="Z175">
+        <v>4.5</v>
+      </c>
+      <c r="AA175">
+        <v>3.25</v>
+      </c>
+      <c r="AB175">
+        <v>1.8</v>
+      </c>
+      <c r="AC175">
+        <v>1.11</v>
+      </c>
+      <c r="AD175">
+        <v>6.7</v>
+      </c>
+      <c r="AE175">
+        <v>1.5</v>
+      </c>
+      <c r="AF175">
+        <v>2.37</v>
+      </c>
+      <c r="AG175">
+        <v>2.35</v>
+      </c>
+      <c r="AH175">
+        <v>1.57</v>
+      </c>
+      <c r="AI175">
+        <v>2.2</v>
+      </c>
+      <c r="AJ175">
+        <v>1.62</v>
+      </c>
+      <c r="AK175">
+        <v>1.88</v>
+      </c>
+      <c r="AL175">
+        <v>1.33</v>
+      </c>
+      <c r="AM175">
+        <v>1.24</v>
+      </c>
+      <c r="AN175">
+        <v>1.3</v>
+      </c>
+      <c r="AO175">
+        <v>2.3</v>
+      </c>
+      <c r="AP175">
+        <v>1.18</v>
+      </c>
+      <c r="AQ175">
+        <v>2.36</v>
+      </c>
+      <c r="AR175">
+        <v>1.3</v>
+      </c>
+      <c r="AS175">
+        <v>1.67</v>
+      </c>
+      <c r="AT175">
+        <v>2.97</v>
+      </c>
+      <c r="AU175">
+        <v>3</v>
+      </c>
+      <c r="AV175">
+        <v>5</v>
+      </c>
+      <c r="AW175">
+        <v>4</v>
+      </c>
+      <c r="AX175">
+        <v>4</v>
+      </c>
+      <c r="AY175">
+        <v>8</v>
+      </c>
+      <c r="AZ175">
+        <v>12</v>
+      </c>
+      <c r="BA175">
+        <v>4</v>
+      </c>
+      <c r="BB175">
+        <v>5</v>
+      </c>
+      <c r="BC175">
+        <v>9</v>
+      </c>
+      <c r="BD175">
+        <v>2.96</v>
+      </c>
+      <c r="BE175">
+        <v>6.35</v>
+      </c>
+      <c r="BF175">
+        <v>1.64</v>
+      </c>
+      <c r="BG175">
+        <v>1.52</v>
+      </c>
+      <c r="BH175">
+        <v>2.42</v>
+      </c>
+      <c r="BI175">
+        <v>1.93</v>
+      </c>
+      <c r="BJ175">
+        <v>1.86</v>
+      </c>
+      <c r="BK175">
+        <v>2.42</v>
+      </c>
+      <c r="BL175">
+        <v>1.52</v>
+      </c>
+      <c r="BM175">
+        <v>3.28</v>
+      </c>
+      <c r="BN175">
+        <v>1.25</v>
+      </c>
+      <c r="BO175">
+        <v>0</v>
+      </c>
+      <c r="BP175">
         <v>0</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="293">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -620,6 +620,9 @@
   </si>
   <si>
     <t>['25']</t>
+  </si>
+  <si>
+    <t>['45', '66', '78']</t>
   </si>
   <si>
     <t>['62']</t>
@@ -1251,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP175"/>
+  <dimension ref="A1:BP176"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1507,7 +1510,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q2">
         <v>2.75</v>
@@ -1713,7 +1716,7 @@
         <v>87</v>
       </c>
       <c r="P3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q3">
         <v>2.38</v>
@@ -1919,7 +1922,7 @@
         <v>86</v>
       </c>
       <c r="P4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q4">
         <v>6.5</v>
@@ -2125,7 +2128,7 @@
         <v>88</v>
       </c>
       <c r="P5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q5">
         <v>3.25</v>
@@ -3361,7 +3364,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q11">
         <v>3.75</v>
@@ -3567,7 +3570,7 @@
         <v>92</v>
       </c>
       <c r="P12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q12">
         <v>4</v>
@@ -4057,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ14">
         <v>1.42</v>
@@ -4266,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="AQ15">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4391,7 +4394,7 @@
         <v>95</v>
       </c>
       <c r="P16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4597,7 +4600,7 @@
         <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q17">
         <v>2.75</v>
@@ -4803,7 +4806,7 @@
         <v>96</v>
       </c>
       <c r="P18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q18">
         <v>2.2</v>
@@ -5009,7 +5012,7 @@
         <v>86</v>
       </c>
       <c r="P19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q19">
         <v>2.5</v>
@@ -5215,7 +5218,7 @@
         <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q20">
         <v>3.75</v>
@@ -5421,7 +5424,7 @@
         <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q21">
         <v>4.5</v>
@@ -5627,7 +5630,7 @@
         <v>98</v>
       </c>
       <c r="P22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q22">
         <v>2.3</v>
@@ -6039,7 +6042,7 @@
         <v>100</v>
       </c>
       <c r="P24" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q24">
         <v>3</v>
@@ -6245,7 +6248,7 @@
         <v>101</v>
       </c>
       <c r="P25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q25">
         <v>2.38</v>
@@ -6323,7 +6326,7 @@
         <v>3</v>
       </c>
       <c r="AP25">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ25">
         <v>1.09</v>
@@ -6451,7 +6454,7 @@
         <v>102</v>
       </c>
       <c r="P26" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q26">
         <v>4</v>
@@ -6657,7 +6660,7 @@
         <v>103</v>
       </c>
       <c r="P27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q27">
         <v>4.5</v>
@@ -7069,7 +7072,7 @@
         <v>105</v>
       </c>
       <c r="P29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q29">
         <v>2.05</v>
@@ -7275,7 +7278,7 @@
         <v>106</v>
       </c>
       <c r="P30" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q30">
         <v>2.75</v>
@@ -7481,7 +7484,7 @@
         <v>86</v>
       </c>
       <c r="P31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q31">
         <v>2.88</v>
@@ -7974,7 +7977,7 @@
         <v>2</v>
       </c>
       <c r="AQ33">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.76</v>
@@ -8099,7 +8102,7 @@
         <v>109</v>
       </c>
       <c r="P34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q34">
         <v>1.8</v>
@@ -8511,7 +8514,7 @@
         <v>111</v>
       </c>
       <c r="P36" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q36">
         <v>2.5</v>
@@ -8717,7 +8720,7 @@
         <v>87</v>
       </c>
       <c r="P37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -8923,7 +8926,7 @@
         <v>112</v>
       </c>
       <c r="P38" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q38">
         <v>2.75</v>
@@ -9335,7 +9338,7 @@
         <v>86</v>
       </c>
       <c r="P40" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -9541,7 +9544,7 @@
         <v>114</v>
       </c>
       <c r="P41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q41">
         <v>3</v>
@@ -9747,7 +9750,7 @@
         <v>86</v>
       </c>
       <c r="P42" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q42">
         <v>3.5</v>
@@ -10034,7 +10037,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ43">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.43</v>
@@ -10365,7 +10368,7 @@
         <v>86</v>
       </c>
       <c r="P45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q45">
         <v>2.75</v>
@@ -10571,7 +10574,7 @@
         <v>116</v>
       </c>
       <c r="P46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q46">
         <v>2.63</v>
@@ -10777,7 +10780,7 @@
         <v>86</v>
       </c>
       <c r="P47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q47">
         <v>3.6</v>
@@ -10983,7 +10986,7 @@
         <v>117</v>
       </c>
       <c r="P48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q48">
         <v>3.2</v>
@@ -11601,7 +11604,7 @@
         <v>119</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q51">
         <v>5.5</v>
@@ -11807,7 +11810,7 @@
         <v>86</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q52">
         <v>2.1</v>
@@ -12219,7 +12222,7 @@
         <v>121</v>
       </c>
       <c r="P54" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q54">
         <v>3.4</v>
@@ -12631,7 +12634,7 @@
         <v>122</v>
       </c>
       <c r="P56" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q56">
         <v>3.25</v>
@@ -12837,7 +12840,7 @@
         <v>86</v>
       </c>
       <c r="P57" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q57">
         <v>3.2</v>
@@ -13043,7 +13046,7 @@
         <v>123</v>
       </c>
       <c r="P58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q58">
         <v>1.8</v>
@@ -13327,7 +13330,7 @@
         <v>0.33</v>
       </c>
       <c r="AP59">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ59">
         <v>0.73</v>
@@ -13536,7 +13539,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ60">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.45</v>
@@ -13661,7 +13664,7 @@
         <v>125</v>
       </c>
       <c r="P61" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q61">
         <v>2</v>
@@ -13945,7 +13948,7 @@
         <v>3</v>
       </c>
       <c r="AP62">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ62">
         <v>2.36</v>
@@ -14073,7 +14076,7 @@
         <v>126</v>
       </c>
       <c r="P63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q63">
         <v>3.6</v>
@@ -14485,7 +14488,7 @@
         <v>128</v>
       </c>
       <c r="P65" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65">
         <v>2.5</v>
@@ -14691,7 +14694,7 @@
         <v>86</v>
       </c>
       <c r="P66" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q66">
         <v>5</v>
@@ -14897,7 +14900,7 @@
         <v>129</v>
       </c>
       <c r="P67" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q67">
         <v>2.25</v>
@@ -15103,7 +15106,7 @@
         <v>130</v>
       </c>
       <c r="P68" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68">
         <v>2.1</v>
@@ -15721,7 +15724,7 @@
         <v>133</v>
       </c>
       <c r="P71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q71">
         <v>2.1</v>
@@ -16211,7 +16214,7 @@
         <v>2</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ73">
         <v>1.6</v>
@@ -16545,7 +16548,7 @@
         <v>135</v>
       </c>
       <c r="P75" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75">
         <v>3.25</v>
@@ -16751,7 +16754,7 @@
         <v>136</v>
       </c>
       <c r="P76" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76">
         <v>2.75</v>
@@ -16957,7 +16960,7 @@
         <v>137</v>
       </c>
       <c r="P77" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q77">
         <v>3.1</v>
@@ -17038,7 +17041,7 @@
         <v>1.09</v>
       </c>
       <c r="AQ77">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.02</v>
@@ -17163,7 +17166,7 @@
         <v>86</v>
       </c>
       <c r="P78" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q78">
         <v>3.75</v>
@@ -17369,7 +17372,7 @@
         <v>138</v>
       </c>
       <c r="P79" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17781,7 +17784,7 @@
         <v>140</v>
       </c>
       <c r="P81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q81">
         <v>2.6</v>
@@ -18274,7 +18277,7 @@
         <v>1.91</v>
       </c>
       <c r="AQ83">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR83">
         <v>1.17</v>
@@ -18605,7 +18608,7 @@
         <v>144</v>
       </c>
       <c r="P85" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q85">
         <v>2</v>
@@ -18811,7 +18814,7 @@
         <v>145</v>
       </c>
       <c r="P86" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q86">
         <v>4</v>
@@ -19223,7 +19226,7 @@
         <v>146</v>
       </c>
       <c r="P88" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q88">
         <v>4.33</v>
@@ -19429,7 +19432,7 @@
         <v>86</v>
       </c>
       <c r="P89" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q89">
         <v>3.1</v>
@@ -19635,7 +19638,7 @@
         <v>86</v>
       </c>
       <c r="P90" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q90">
         <v>2.1</v>
@@ -19713,7 +19716,7 @@
         <v>1</v>
       </c>
       <c r="AP90">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ90">
         <v>1.18</v>
@@ -20047,7 +20050,7 @@
         <v>86</v>
       </c>
       <c r="P92" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q92">
         <v>2.5</v>
@@ -20253,7 +20256,7 @@
         <v>86</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q93">
         <v>3.4</v>
@@ -20459,7 +20462,7 @@
         <v>147</v>
       </c>
       <c r="P94" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q94">
         <v>2.63</v>
@@ -20665,7 +20668,7 @@
         <v>148</v>
       </c>
       <c r="P95" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q95">
         <v>2.6</v>
@@ -21077,7 +21080,7 @@
         <v>149</v>
       </c>
       <c r="P97" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q97">
         <v>3.2</v>
@@ -21489,7 +21492,7 @@
         <v>142</v>
       </c>
       <c r="P99" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q99">
         <v>3.2</v>
@@ -21695,7 +21698,7 @@
         <v>86</v>
       </c>
       <c r="P100" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q100">
         <v>3.2</v>
@@ -21901,7 +21904,7 @@
         <v>86</v>
       </c>
       <c r="P101" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q101">
         <v>4</v>
@@ -22313,7 +22316,7 @@
         <v>86</v>
       </c>
       <c r="P103" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q103">
         <v>4.5</v>
@@ -22519,7 +22522,7 @@
         <v>152</v>
       </c>
       <c r="P104" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q104">
         <v>4</v>
@@ -22931,7 +22934,7 @@
         <v>86</v>
       </c>
       <c r="P106" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q106">
         <v>2.88</v>
@@ -23012,7 +23015,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ106">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.34</v>
@@ -23137,7 +23140,7 @@
         <v>86</v>
       </c>
       <c r="P107" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23343,7 +23346,7 @@
         <v>153</v>
       </c>
       <c r="P108" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q108">
         <v>2.88</v>
@@ -23549,7 +23552,7 @@
         <v>86</v>
       </c>
       <c r="P109" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q109">
         <v>3.2</v>
@@ -24991,7 +24994,7 @@
         <v>157</v>
       </c>
       <c r="P116" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q116">
         <v>3.5</v>
@@ -25275,7 +25278,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ117">
         <v>0.42</v>
@@ -25609,7 +25612,7 @@
         <v>152</v>
       </c>
       <c r="P119" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q119">
         <v>2.63</v>
@@ -26227,7 +26230,7 @@
         <v>86</v>
       </c>
       <c r="P122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q122">
         <v>3</v>
@@ -26308,7 +26311,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ122">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.65</v>
@@ -26639,7 +26642,7 @@
         <v>161</v>
       </c>
       <c r="P124" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q124">
         <v>2.38</v>
@@ -26717,7 +26720,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ124">
         <v>0.73</v>
@@ -26845,7 +26848,7 @@
         <v>162</v>
       </c>
       <c r="P125" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q125">
         <v>3</v>
@@ -27051,7 +27054,7 @@
         <v>163</v>
       </c>
       <c r="P126" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q126">
         <v>5</v>
@@ -27257,7 +27260,7 @@
         <v>164</v>
       </c>
       <c r="P127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27463,7 +27466,7 @@
         <v>165</v>
       </c>
       <c r="P128" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q128">
         <v>2.75</v>
@@ -27669,7 +27672,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q129">
         <v>1.95</v>
@@ -27875,7 +27878,7 @@
         <v>86</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q130">
         <v>3.4</v>
@@ -28287,7 +28290,7 @@
         <v>153</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28493,7 +28496,7 @@
         <v>168</v>
       </c>
       <c r="P133" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q133">
         <v>2.5</v>
@@ -29317,7 +29320,7 @@
         <v>170</v>
       </c>
       <c r="P137" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q137">
         <v>2.75</v>
@@ -29729,7 +29732,7 @@
         <v>171</v>
       </c>
       <c r="P139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q139">
         <v>4.8</v>
@@ -30141,7 +30144,7 @@
         <v>173</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q141">
         <v>3.75</v>
@@ -30222,7 +30225,7 @@
         <v>0.58</v>
       </c>
       <c r="AQ141">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.04</v>
@@ -31171,7 +31174,7 @@
         <v>178</v>
       </c>
       <c r="P146" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q146">
         <v>2.5</v>
@@ -31377,7 +31380,7 @@
         <v>179</v>
       </c>
       <c r="P147" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q147">
         <v>2.36</v>
@@ -31455,7 +31458,7 @@
         <v>1.56</v>
       </c>
       <c r="AP147">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ147">
         <v>1.55</v>
@@ -31789,7 +31792,7 @@
         <v>181</v>
       </c>
       <c r="P149" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q149">
         <v>2.1</v>
@@ -31995,7 +31998,7 @@
         <v>182</v>
       </c>
       <c r="P150" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q150">
         <v>2.63</v>
@@ -32201,7 +32204,7 @@
         <v>183</v>
       </c>
       <c r="P151" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q151">
         <v>3.5</v>
@@ -32613,7 +32616,7 @@
         <v>185</v>
       </c>
       <c r="P153" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q153">
         <v>2.88</v>
@@ -32819,7 +32822,7 @@
         <v>86</v>
       </c>
       <c r="P154" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q154">
         <v>3.75</v>
@@ -33025,7 +33028,7 @@
         <v>186</v>
       </c>
       <c r="P155" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33643,7 +33646,7 @@
         <v>188</v>
       </c>
       <c r="P158" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q158">
         <v>2.4</v>
@@ -33721,7 +33724,7 @@
         <v>1.78</v>
       </c>
       <c r="AP158">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AQ158">
         <v>1.55</v>
@@ -34136,7 +34139,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ160">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AR160">
         <v>1.4</v>
@@ -34261,7 +34264,7 @@
         <v>191</v>
       </c>
       <c r="P161" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q161">
         <v>3</v>
@@ -34467,7 +34470,7 @@
         <v>192</v>
       </c>
       <c r="P162" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q162">
         <v>3.2</v>
@@ -35291,7 +35294,7 @@
         <v>195</v>
       </c>
       <c r="P166" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q166">
         <v>2.88</v>
@@ -35909,7 +35912,7 @@
         <v>198</v>
       </c>
       <c r="P169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36321,7 +36324,7 @@
         <v>200</v>
       </c>
       <c r="P171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q171">
         <v>2.5</v>
@@ -36733,7 +36736,7 @@
         <v>86</v>
       </c>
       <c r="P173" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q173">
         <v>3.1</v>
@@ -36939,7 +36942,7 @@
         <v>86</v>
       </c>
       <c r="P174" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37145,7 +37148,7 @@
         <v>177</v>
       </c>
       <c r="P175" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q175">
         <v>5</v>
@@ -37302,6 +37305,212 @@
       </c>
       <c r="BP175">
         <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:68">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>7484710</v>
+      </c>
+      <c r="C176" t="s">
+        <v>68</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45753.22916666666</v>
+      </c>
+      <c r="F176">
+        <v>22</v>
+      </c>
+      <c r="G176" t="s">
+        <v>82</v>
+      </c>
+      <c r="H176" t="s">
+        <v>71</v>
+      </c>
+      <c r="I176">
+        <v>1</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+      <c r="L176">
+        <v>3</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>3</v>
+      </c>
+      <c r="O176" t="s">
+        <v>202</v>
+      </c>
+      <c r="P176" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q176">
+        <v>2.5</v>
+      </c>
+      <c r="R176">
+        <v>2.1</v>
+      </c>
+      <c r="S176">
+        <v>4</v>
+      </c>
+      <c r="T176">
+        <v>1.4</v>
+      </c>
+      <c r="U176">
+        <v>2.75</v>
+      </c>
+      <c r="V176">
+        <v>2.75</v>
+      </c>
+      <c r="W176">
+        <v>1.4</v>
+      </c>
+      <c r="X176">
+        <v>7</v>
+      </c>
+      <c r="Y176">
+        <v>1.08</v>
+      </c>
+      <c r="Z176">
+        <v>1.85</v>
+      </c>
+      <c r="AA176">
+        <v>3.29</v>
+      </c>
+      <c r="AB176">
+        <v>4.45</v>
+      </c>
+      <c r="AC176">
+        <v>1.02</v>
+      </c>
+      <c r="AD176">
+        <v>7.8</v>
+      </c>
+      <c r="AE176">
+        <v>1.26</v>
+      </c>
+      <c r="AF176">
+        <v>3.22</v>
+      </c>
+      <c r="AG176">
+        <v>1.85</v>
+      </c>
+      <c r="AH176">
+        <v>1.93</v>
+      </c>
+      <c r="AI176">
+        <v>1.73</v>
+      </c>
+      <c r="AJ176">
+        <v>2</v>
+      </c>
+      <c r="AK176">
+        <v>1.24</v>
+      </c>
+      <c r="AL176">
+        <v>1.32</v>
+      </c>
+      <c r="AM176">
+        <v>1.8</v>
+      </c>
+      <c r="AN176">
+        <v>1.4</v>
+      </c>
+      <c r="AO176">
+        <v>1.1</v>
+      </c>
+      <c r="AP176">
+        <v>1.55</v>
+      </c>
+      <c r="AQ176">
+        <v>1</v>
+      </c>
+      <c r="AR176">
+        <v>1.55</v>
+      </c>
+      <c r="AS176">
+        <v>1.57</v>
+      </c>
+      <c r="AT176">
+        <v>3.12</v>
+      </c>
+      <c r="AU176">
+        <v>8</v>
+      </c>
+      <c r="AV176">
+        <v>3</v>
+      </c>
+      <c r="AW176">
+        <v>11</v>
+      </c>
+      <c r="AX176">
+        <v>8</v>
+      </c>
+      <c r="AY176">
+        <v>24</v>
+      </c>
+      <c r="AZ176">
+        <v>13</v>
+      </c>
+      <c r="BA176">
+        <v>10</v>
+      </c>
+      <c r="BB176">
+        <v>7</v>
+      </c>
+      <c r="BC176">
+        <v>17</v>
+      </c>
+      <c r="BD176">
+        <v>1.78</v>
+      </c>
+      <c r="BE176">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF176">
+        <v>2.36</v>
+      </c>
+      <c r="BG176">
+        <v>1.23</v>
+      </c>
+      <c r="BH176">
+        <v>3.42</v>
+      </c>
+      <c r="BI176">
+        <v>1.5</v>
+      </c>
+      <c r="BJ176">
+        <v>2.51</v>
+      </c>
+      <c r="BK176">
+        <v>1.84</v>
+      </c>
+      <c r="BL176">
+        <v>1.95</v>
+      </c>
+      <c r="BM176">
+        <v>2.31</v>
+      </c>
+      <c r="BN176">
+        <v>1.58</v>
+      </c>
+      <c r="BO176">
+        <v>3.08</v>
+      </c>
+      <c r="BP176">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -11401,73 +11401,73 @@
         <v>86</v>
       </c>
       <c r="Q50">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH50">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI50">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ50">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AL50">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AM50">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AN50">
         <v>1</v>
@@ -11539,7 +11539,7 @@
         <v>0</v>
       </c>
       <c r="BK50">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BL50">
         <v>0</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Austria 2. Liga_20242025.xlsx
@@ -31086,19 +31086,19 @@
         <v>10</v>
       </c>
       <c r="AV144">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW144">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX144">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AY144">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ144">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA144">
         <v>6</v>
@@ -33134,13 +33134,13 @@
         <v>1.2</v>
       </c>
       <c r="AR154">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AS154">
         <v>1.44</v>
       </c>
       <c r="AT154">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="AU154">
         <v>5</v>
@@ -33961,10 +33961,10 @@
         <v>1.27</v>
       </c>
       <c r="AS158">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AT158">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AU158">
         <v>5</v>
@@ -36430,13 +36430,13 @@
         <v>0.87</v>
       </c>
       <c r="AR170">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AS170">
         <v>1.08</v>
       </c>
       <c r="AT170">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AU170">
         <v>9</v>
@@ -41168,13 +41168,13 @@
         <v>1.07</v>
       </c>
       <c r="AR193">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS193">
         <v>1.18</v>
       </c>
       <c r="AT193">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AU193">
         <v>5</v>
@@ -44670,13 +44670,13 @@
         <v>1</v>
       </c>
       <c r="AR210">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AS210">
         <v>1.45</v>
       </c>
       <c r="AT210">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="AU210">
         <v>4</v>
@@ -49408,13 +49408,13 @@
         <v>2.27</v>
       </c>
       <c r="AR233">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AS233">
         <v>1.66</v>
       </c>
       <c r="AT233">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="AU233">
         <v>5</v>
